--- a/data/Recruitment_Requisition.xlsx
+++ b/data/Recruitment_Requisition.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
-  <workbookPr hidePivotFieldList="1" defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30327"/>
+  <workbookPr hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://kubotagroup-my.sharepoint.com/personal/lapat_j_kubota_com/Documents/Documents/Recruitment Tools/Dashboard Data Report/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3296" documentId="8_{4185217D-4006-4629-AD3A-0737CE05813A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{32273D18-F13F-4EEA-ADBA-95BFDC1C9C85}"/>
+  <xr:revisionPtr revIDLastSave="3303" documentId="8_{4185217D-4006-4629-AD3A-0737CE05813A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5AF964BA-FED1-4E9F-A839-E441780488FD}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{5982D4A9-2AD8-4F8A-AE0B-0D729A27807E}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{5982D4A9-2AD8-4F8A-AE0B-0D729A27807E}"/>
   </bookViews>
   <sheets>
     <sheet name="Recruitment" sheetId="2" r:id="rId1"/>
@@ -21,7 +21,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Recruitment!$V$127:$V$127</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -152,7 +152,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1817" uniqueCount="590">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1821" uniqueCount="590">
   <si>
     <t>Year</t>
   </si>
@@ -2649,7 +2649,7 @@
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="160">
+  <cellXfs count="171">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3118,6 +3118,39 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment readingOrder="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="187" fontId="7" fillId="2" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="7" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="190" fontId="7" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="7" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="187" fontId="7" fillId="2" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -3125,93 +3158,6 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="63">
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="7" tint="0.59999389629810485"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="3" tint="0.89999084444715716"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="1" tint="0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -4893,6 +4839,93 @@
         <bottom/>
       </border>
     </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="7" tint="0.59999389629810485"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="3" tint="0.89999084444715716"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="1" tint="0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -4912,25 +4945,25 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2A626EEB-FDFE-42FC-817A-963B6C771FE3}" name="Master" displayName="Master" ref="A1:AI119" totalsRowShown="0" headerRowDxfId="62" dataDxfId="61" tableBorderDxfId="60">
-  <autoFilter ref="A1:AI119" xr:uid="{2A626EEB-FDFE-42FC-817A-963B6C771FE3}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2A626EEB-FDFE-42FC-817A-963B6C771FE3}" name="Master" displayName="Master" ref="A1:AI120" totalsRowShown="0" headerRowDxfId="53" dataDxfId="52" tableBorderDxfId="51">
+  <autoFilter ref="A1:AI120" xr:uid="{2A626EEB-FDFE-42FC-817A-963B6C771FE3}"/>
   <tableColumns count="35">
-    <tableColumn id="1" xr3:uid="{FF1CE6B1-DB01-49DC-BA43-064CD949FF4D}" name="Year" dataDxfId="59"/>
-    <tableColumn id="2" xr3:uid="{7F3A3465-03B1-4D22-80CE-2DF0F09BDF7E}" name="Month" dataDxfId="58">
+    <tableColumn id="1" xr3:uid="{FF1CE6B1-DB01-49DC-BA43-064CD949FF4D}" name="Year" dataDxfId="50"/>
+    <tableColumn id="2" xr3:uid="{7F3A3465-03B1-4D22-80CE-2DF0F09BDF7E}" name="Month" dataDxfId="49">
       <calculatedColumnFormula>IF(M2="", "", TEXT(M2, "[$-en-US]mmmm"))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{A2440747-CD3B-4669-ADF2-9F1CFEF7F3CD}" name="Location" dataDxfId="57"/>
-    <tableColumn id="4" xr3:uid="{3A370C0B-3F07-4F40-9C8A-74B066E4B831}" name="Position_Request" dataDxfId="56"/>
-    <tableColumn id="5" xr3:uid="{EB078B5D-0D69-4818-99C8-D6E68D752B4E}" name="Position_Announce" dataDxfId="55"/>
-    <tableColumn id="6" xr3:uid="{3F127422-0ABD-4AAF-8809-8BBE66B85179}" name="Division" dataDxfId="54"/>
-    <tableColumn id="7" xr3:uid="{E002CC14-16CD-4A5B-9C19-21F733EBD1E4}" name="Dept" dataDxfId="53"/>
-    <tableColumn id="8" xr3:uid="{29F07533-A51F-4912-9E03-6F726DBCFC9C}" name="Work Unit" dataDxfId="52"/>
-    <tableColumn id="9" xr3:uid="{32FCFA25-C37A-4783-A3B2-126CAC832954}" name="Type" dataDxfId="51"/>
-    <tableColumn id="10" xr3:uid="{9AD246F5-95E1-4522-997B-12E3A0B09065}" name="Memo Status" dataDxfId="50"/>
-    <tableColumn id="11" xr3:uid="{2AE93E46-B5B7-4299-B18C-93970D71B544}" name="Inter/Exter" dataDxfId="49"/>
-    <tableColumn id="12" xr3:uid="{7C57089A-6E18-4556-9430-87C32D050DDB}" name="Recruitment Status" dataDxfId="48"/>
-    <tableColumn id="13" xr3:uid="{C2F77F35-83CD-4E36-A33E-290B84C04D98}" name="Approved_Date" dataDxfId="47"/>
-    <tableColumn id="14" xr3:uid="{52AE79A9-73D6-43D5-8E9F-760888E3DE25}" name="Target_Date" dataDxfId="46">
+    <tableColumn id="3" xr3:uid="{A2440747-CD3B-4669-ADF2-9F1CFEF7F3CD}" name="Location" dataDxfId="48"/>
+    <tableColumn id="4" xr3:uid="{3A370C0B-3F07-4F40-9C8A-74B066E4B831}" name="Position_Request" dataDxfId="47"/>
+    <tableColumn id="5" xr3:uid="{EB078B5D-0D69-4818-99C8-D6E68D752B4E}" name="Position_Announce" dataDxfId="46"/>
+    <tableColumn id="6" xr3:uid="{3F127422-0ABD-4AAF-8809-8BBE66B85179}" name="Division" dataDxfId="45"/>
+    <tableColumn id="7" xr3:uid="{E002CC14-16CD-4A5B-9C19-21F733EBD1E4}" name="Dept" dataDxfId="44"/>
+    <tableColumn id="8" xr3:uid="{29F07533-A51F-4912-9E03-6F726DBCFC9C}" name="Work Unit" dataDxfId="43"/>
+    <tableColumn id="9" xr3:uid="{32FCFA25-C37A-4783-A3B2-126CAC832954}" name="Type" dataDxfId="42"/>
+    <tableColumn id="10" xr3:uid="{9AD246F5-95E1-4522-997B-12E3A0B09065}" name="Memo Status" dataDxfId="41"/>
+    <tableColumn id="11" xr3:uid="{2AE93E46-B5B7-4299-B18C-93970D71B544}" name="Inter/Exter" dataDxfId="40"/>
+    <tableColumn id="12" xr3:uid="{7C57089A-6E18-4556-9430-87C32D050DDB}" name="Recruitment Status" dataDxfId="39"/>
+    <tableColumn id="13" xr3:uid="{C2F77F35-83CD-4E36-A33E-290B84C04D98}" name="Approved_Date" dataDxfId="38"/>
+    <tableColumn id="14" xr3:uid="{52AE79A9-73D6-43D5-8E9F-760888E3DE25}" name="Target_Date" dataDxfId="37">
       <calculatedColumnFormula>IF(M2="",                                                                                                                                                                                                  "",
    WORKDAY(
       M2,
@@ -4940,8 +4973,8 @@
    )
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{9D7BFBDF-A805-4573-8724-696BD4DE55FC}" name="Final Date" dataDxfId="45"/>
-    <tableColumn id="16" xr3:uid="{AEF87AE4-B425-478E-B70E-5B935C739E8F}" name="Diff Date" dataDxfId="44">
+    <tableColumn id="15" xr3:uid="{9D7BFBDF-A805-4573-8724-696BD4DE55FC}" name="Final Date" dataDxfId="36"/>
+    <tableColumn id="16" xr3:uid="{AEF87AE4-B425-478E-B70E-5B935C739E8F}" name="Diff Date" dataDxfId="35">
       <calculatedColumnFormula>IF(M2="",                                                                                                                                                                                                   "",
    NETWORKDAYS(
       M2,
@@ -4950,7 +4983,7 @@
    )
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{77DA1B66-9D49-4273-AF86-193D0808B330}" name="KPI" dataDxfId="43">
+    <tableColumn id="17" xr3:uid="{77DA1B66-9D49-4273-AF86-193D0808B330}" name="KPI" dataDxfId="34">
       <calculatedColumnFormula>IF(P2="",                                                                                                                                                                                                   "",
    IF(OR(I2="O-General",                                                                                                                                                                                                   I2="S-General"),
       IF(P2&lt;=30,                                                                                                                                                                                                   "ON KPI",                                                                                                                                                                                                   "OVER KPI"),
@@ -4961,47 +4994,47 @@
    )
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="23" xr3:uid="{F7FE7E4D-8884-4507-8915-672581B1A2EE}" name="Propose As" dataDxfId="42"/>
-    <tableColumn id="18" xr3:uid="{9C93B32A-3262-498B-8E32-2D7BC990E59A}" name="ID (Being Replaced)" dataDxfId="41"/>
-    <tableColumn id="19" xr3:uid="{A61748A5-F711-42D2-BB1A-6DA213D2B3AD}" name="Name (being replaced)" dataDxfId="40"/>
-    <tableColumn id="21" xr3:uid="{730663BB-D195-4833-B4DA-C7592858B43E}" name="ID New Employee" dataDxfId="39"/>
-    <tableColumn id="22" xr3:uid="{D1F0078F-697F-4186-991F-F3A0FEE3C762}" name="Name New Employee" dataDxfId="38"/>
-    <tableColumn id="34" xr3:uid="{9EC82B84-A07C-4040-A4C3-B6A5BEE858A1}" name="Join Date" dataDxfId="37"/>
-    <tableColumn id="33" xr3:uid="{F69EB419-2824-4BC1-9AAF-FC48B485B353}" name="Probation Status" dataDxfId="36"/>
-    <tableColumn id="24" xr3:uid="{0A660594-4051-4127-BD9E-2C601C5CC781}" name="Start Date" dataDxfId="35"/>
-    <tableColumn id="25" xr3:uid="{93F5B910-1CF2-464B-8C92-806BA9BF0DE7}" name="Recruitment Channel" dataDxfId="34"/>
-    <tableColumn id="26" xr3:uid="{ADFCA5A2-EA66-4841-AA3C-3470C585FA51}" name="Remark" dataDxfId="33"/>
-    <tableColumn id="28" xr3:uid="{4EA54873-5BBE-4914-8C9A-B48E9C4983D5}" name="Notes Qualification" dataDxfId="32"/>
-    <tableColumn id="30" xr3:uid="{4D08EC1B-0A3A-4A94-B31A-24A8052CFC9F}" name="Applied Profile" dataDxfId="31" dataCellStyle="Comma"/>
-    <tableColumn id="31" xr3:uid="{7446C0AF-09AA-4A23-82C1-17EF8B161C36}" name="First" dataDxfId="30" dataCellStyle="Comma"/>
-    <tableColumn id="32" xr3:uid="{038EFFC9-6E6F-41CB-8C8A-F6B0D0F714F0}" name="Final" dataDxfId="29" dataCellStyle="Comma"/>
-    <tableColumn id="38" xr3:uid="{28E86828-3972-47EE-AB17-9FE941222406}" name="Offer" dataDxfId="28" dataCellStyle="Comma"/>
-    <tableColumn id="39" xr3:uid="{C672E10F-6CBC-4EBA-BFE1-BFDADEAA1116}" name="Reject Offer" dataDxfId="27" dataCellStyle="Comma"/>
-    <tableColumn id="35" xr3:uid="{531E9309-515F-44A6-A2FD-1822E3AF3610}" name="hired" dataDxfId="26"/>
-    <tableColumn id="37" xr3:uid="{436C193C-97DC-41B6-AE40-7FE868949069}" name="Link to Jd" dataDxfId="25"/>
+    <tableColumn id="23" xr3:uid="{F7FE7E4D-8884-4507-8915-672581B1A2EE}" name="Propose As" dataDxfId="33"/>
+    <tableColumn id="18" xr3:uid="{9C93B32A-3262-498B-8E32-2D7BC990E59A}" name="ID (Being Replaced)" dataDxfId="32"/>
+    <tableColumn id="19" xr3:uid="{A61748A5-F711-42D2-BB1A-6DA213D2B3AD}" name="Name (being replaced)" dataDxfId="31"/>
+    <tableColumn id="21" xr3:uid="{730663BB-D195-4833-B4DA-C7592858B43E}" name="ID New Employee" dataDxfId="30"/>
+    <tableColumn id="22" xr3:uid="{D1F0078F-697F-4186-991F-F3A0FEE3C762}" name="Name New Employee" dataDxfId="29"/>
+    <tableColumn id="34" xr3:uid="{9EC82B84-A07C-4040-A4C3-B6A5BEE858A1}" name="Join Date" dataDxfId="28"/>
+    <tableColumn id="33" xr3:uid="{F69EB419-2824-4BC1-9AAF-FC48B485B353}" name="Probation Status" dataDxfId="27"/>
+    <tableColumn id="24" xr3:uid="{0A660594-4051-4127-BD9E-2C601C5CC781}" name="Start Date" dataDxfId="26"/>
+    <tableColumn id="25" xr3:uid="{93F5B910-1CF2-464B-8C92-806BA9BF0DE7}" name="Recruitment Channel" dataDxfId="25"/>
+    <tableColumn id="26" xr3:uid="{ADFCA5A2-EA66-4841-AA3C-3470C585FA51}" name="Remark" dataDxfId="24"/>
+    <tableColumn id="28" xr3:uid="{4EA54873-5BBE-4914-8C9A-B48E9C4983D5}" name="Notes Qualification" dataDxfId="23"/>
+    <tableColumn id="30" xr3:uid="{4D08EC1B-0A3A-4A94-B31A-24A8052CFC9F}" name="Applied Profile" dataDxfId="22" dataCellStyle="Comma"/>
+    <tableColumn id="31" xr3:uid="{7446C0AF-09AA-4A23-82C1-17EF8B161C36}" name="First" dataDxfId="21" dataCellStyle="Comma"/>
+    <tableColumn id="32" xr3:uid="{038EFFC9-6E6F-41CB-8C8A-F6B0D0F714F0}" name="Final" dataDxfId="20" dataCellStyle="Comma"/>
+    <tableColumn id="38" xr3:uid="{28E86828-3972-47EE-AB17-9FE941222406}" name="Offer" dataDxfId="19" dataCellStyle="Comma"/>
+    <tableColumn id="39" xr3:uid="{C672E10F-6CBC-4EBA-BFE1-BFDADEAA1116}" name="Reject Offer" dataDxfId="18" dataCellStyle="Comma"/>
+    <tableColumn id="35" xr3:uid="{531E9309-515F-44A6-A2FD-1822E3AF3610}" name="hired" dataDxfId="17"/>
+    <tableColumn id="37" xr3:uid="{436C193C-97DC-41B6-AE40-7FE868949069}" name="Link to Jd" dataDxfId="16"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{9C58A6E7-1F6C-4A9C-AF1C-94E69FBBAB9F}" name="Table2" displayName="Table2" ref="A1:N1048576" totalsRowShown="0" headerRowDxfId="24" dataDxfId="23">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{9C58A6E7-1F6C-4A9C-AF1C-94E69FBBAB9F}" name="Table2" displayName="Table2" ref="A1:N1048576" totalsRowShown="0" headerRowDxfId="15" dataDxfId="14">
   <autoFilter ref="A1:N1048576" xr:uid="{9C58A6E7-1F6C-4A9C-AF1C-94E69FBBAB9F}"/>
   <tableColumns count="14">
-    <tableColumn id="1" xr3:uid="{C4193DF0-9CE7-4180-ABDC-36145D403167}" name="Holidays" dataDxfId="22"/>
-    <tableColumn id="5" xr3:uid="{B19B46CB-5054-4CC5-A61A-8BBACDF4439F}" name="Type" dataDxfId="21"/>
-    <tableColumn id="6" xr3:uid="{BC3FD27E-0D84-4B1C-9569-EF6AFA629FA1}" name="Recruit Status" dataDxfId="20"/>
-    <tableColumn id="7" xr3:uid="{B272A2F8-FD98-477E-8A86-67395E430DAB}" name="Branch" dataDxfId="19"/>
-    <tableColumn id="8" xr3:uid="{A720D319-55D0-4FD3-8256-6F13AE0FDC3B}" name="Prioritize" dataDxfId="18"/>
-    <tableColumn id="9" xr3:uid="{472EDD7A-7457-494B-B4F2-F3384C125D45}" name="Channels" dataDxfId="17"/>
-    <tableColumn id="10" xr3:uid="{1BD2545C-E119-472F-9242-F3F597824223}" name="Internal" dataDxfId="16"/>
-    <tableColumn id="11" xr3:uid="{0B54F1A7-F5B4-46E2-935C-0BAD5FD0E017}" name="Probation" dataDxfId="15"/>
-    <tableColumn id="12" xr3:uid="{4A889E20-3FAA-4375-A85C-ED8F79BA3E8E}" name="Memo Status" dataDxfId="14"/>
-    <tableColumn id="13" xr3:uid="{552F7BC3-8053-4350-BC3A-7EA550CF9142}" name="Division2" dataDxfId="13"/>
-    <tableColumn id="14" xr3:uid="{8EFA9A74-9A81-4C0C-A73D-C62F83024972}" name="Department2" dataDxfId="12"/>
-    <tableColumn id="15" xr3:uid="{2146B206-AB03-439A-8BEF-22CB50E6537A}" name="Work Unit2" dataDxfId="11"/>
-    <tableColumn id="2" xr3:uid="{A2285670-202B-48CF-BFBE-A59C12D7AFF5}" name="Probation Status" dataDxfId="10"/>
-    <tableColumn id="3" xr3:uid="{9952BC8D-49A3-43D8-BD7E-4887BC16DFFF}" name="Column1" dataDxfId="9"/>
+    <tableColumn id="1" xr3:uid="{C4193DF0-9CE7-4180-ABDC-36145D403167}" name="Holidays" dataDxfId="13"/>
+    <tableColumn id="5" xr3:uid="{B19B46CB-5054-4CC5-A61A-8BBACDF4439F}" name="Type" dataDxfId="12"/>
+    <tableColumn id="6" xr3:uid="{BC3FD27E-0D84-4B1C-9569-EF6AFA629FA1}" name="Recruit Status" dataDxfId="11"/>
+    <tableColumn id="7" xr3:uid="{B272A2F8-FD98-477E-8A86-67395E430DAB}" name="Branch" dataDxfId="10"/>
+    <tableColumn id="8" xr3:uid="{A720D319-55D0-4FD3-8256-6F13AE0FDC3B}" name="Prioritize" dataDxfId="9"/>
+    <tableColumn id="9" xr3:uid="{472EDD7A-7457-494B-B4F2-F3384C125D45}" name="Channels" dataDxfId="8"/>
+    <tableColumn id="10" xr3:uid="{1BD2545C-E119-472F-9242-F3F597824223}" name="Internal" dataDxfId="7"/>
+    <tableColumn id="11" xr3:uid="{0B54F1A7-F5B4-46E2-935C-0BAD5FD0E017}" name="Probation" dataDxfId="6"/>
+    <tableColumn id="12" xr3:uid="{4A889E20-3FAA-4375-A85C-ED8F79BA3E8E}" name="Memo Status" dataDxfId="5"/>
+    <tableColumn id="13" xr3:uid="{552F7BC3-8053-4350-BC3A-7EA550CF9142}" name="Division2" dataDxfId="4"/>
+    <tableColumn id="14" xr3:uid="{8EFA9A74-9A81-4C0C-A73D-C62F83024972}" name="Department2" dataDxfId="3"/>
+    <tableColumn id="15" xr3:uid="{2146B206-AB03-439A-8BEF-22CB50E6537A}" name="Work Unit2" dataDxfId="2"/>
+    <tableColumn id="2" xr3:uid="{A2285670-202B-48CF-BFBE-A59C12D7AFF5}" name="Probation Status" dataDxfId="1"/>
+    <tableColumn id="3" xr3:uid="{9952BC8D-49A3-43D8-BD7E-4887BC16DFFF}" name="Column1" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -5324,44 +5357,44 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{817CD080-0396-428F-B39B-215D57916061}">
-  <dimension ref="A1:AI119"/>
+  <dimension ref="A1:AI120"/>
   <sheetFormatPr defaultColWidth="14" defaultRowHeight="20.25" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="9.59765625" style="78" customWidth="1"/>
+    <col min="1" max="1" width="9.625" style="78" customWidth="1"/>
     <col min="2" max="2" width="9" style="79" customWidth="1"/>
-    <col min="3" max="3" width="9.59765625" style="79" customWidth="1"/>
-    <col min="4" max="4" width="45.3984375" style="79" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.625" style="79" customWidth="1"/>
+    <col min="4" max="4" width="45.375" style="79" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="56.5" style="50" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="58.59765625" style="50" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="81.3984375" style="50" customWidth="1"/>
-    <col min="8" max="8" width="48.09765625" style="50" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="58.625" style="50" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="81.375" style="50" customWidth="1"/>
+    <col min="8" max="8" width="48.125" style="50" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="12" style="50" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.69921875" style="50" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.3984375" style="50" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="24.09765625" style="50" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="16.19921875" style="48" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="16.69921875" style="47" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="17.3984375" style="48" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.3984375" style="50" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="11.09765625" style="50" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="11.09765625" style="50" customWidth="1"/>
-    <col min="19" max="19" width="19.19921875" style="50" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="21.69921875" style="50" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="17.59765625" style="50" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="20.19921875" style="117" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="13.8984375" style="48" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="22.09765625" style="50" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.75" style="50" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.375" style="50" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="24.125" style="50" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="16.25" style="48" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="16.75" style="47" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="17.375" style="48" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.375" style="50" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="11.125" style="50" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="11.125" style="50" customWidth="1"/>
+    <col min="19" max="19" width="19.25" style="50" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="21.75" style="50" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="17.625" style="50" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="20.25" style="117" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="13.875" style="48" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="22.125" style="50" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="14.5" style="80" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="22.69921875" style="50" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="11.69921875" style="50" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="63.3984375" style="50" customWidth="1"/>
+    <col min="26" max="26" width="22.75" style="50" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="11.75" style="50" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="63.375" style="50" customWidth="1"/>
     <col min="29" max="29" width="21.5" style="49" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="9.3984375" style="49" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="9.8984375" style="49" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="10.3984375" style="49" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="17.8984375" style="49" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="9.375" style="49" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="9.875" style="49" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="10.375" style="49" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="17.875" style="49" bestFit="1" customWidth="1"/>
     <col min="34" max="34" width="9" style="50" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="40.19921875" style="51" customWidth="1"/>
+    <col min="35" max="35" width="40.25" style="51" customWidth="1"/>
     <col min="36" max="16384" width="14" style="52"/>
   </cols>
   <sheetData>
@@ -5472,7 +5505,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="2" spans="1:35" s="9" customFormat="1" ht="41.4" customHeight="1">
+    <row r="2" spans="1:35" s="9" customFormat="1" ht="41.45" customHeight="1">
       <c r="A2" s="19">
         <v>2024</v>
       </c>
@@ -5570,7 +5603,7 @@
       <c r="AH2" s="12"/>
       <c r="AI2" s="8"/>
     </row>
-    <row r="3" spans="1:35" s="9" customFormat="1" ht="41.4" customHeight="1">
+    <row r="3" spans="1:35" s="9" customFormat="1" ht="41.45" customHeight="1">
       <c r="A3" s="19">
         <v>2024</v>
       </c>
@@ -5662,7 +5695,7 @@
       <c r="AH3" s="12"/>
       <c r="AI3" s="8"/>
     </row>
-    <row r="4" spans="1:35" s="9" customFormat="1" ht="41.4" customHeight="1">
+    <row r="4" spans="1:35" s="9" customFormat="1" ht="41.45" customHeight="1">
       <c r="A4" s="19">
         <v>2024</v>
       </c>
@@ -5750,7 +5783,7 @@
       <c r="AH4" s="12"/>
       <c r="AI4" s="8"/>
     </row>
-    <row r="5" spans="1:35" s="9" customFormat="1" ht="41.4" customHeight="1">
+    <row r="5" spans="1:35" s="9" customFormat="1" ht="41.45" customHeight="1">
       <c r="A5" s="19">
         <v>2024</v>
       </c>
@@ -5840,7 +5873,7 @@
       <c r="AH5" s="12"/>
       <c r="AI5" s="8"/>
     </row>
-    <row r="6" spans="1:35" s="9" customFormat="1" ht="41.4" customHeight="1">
+    <row r="6" spans="1:35" s="9" customFormat="1" ht="41.45" customHeight="1">
       <c r="A6" s="19">
         <v>2024</v>
       </c>
@@ -5928,7 +5961,7 @@
       <c r="AH6" s="12"/>
       <c r="AI6" s="8"/>
     </row>
-    <row r="7" spans="1:35" s="9" customFormat="1" ht="41.4" customHeight="1">
+    <row r="7" spans="1:35" s="9" customFormat="1" ht="41.45" customHeight="1">
       <c r="A7" s="19">
         <v>2024</v>
       </c>
@@ -6016,7 +6049,7 @@
       <c r="AH7" s="12"/>
       <c r="AI7" s="8"/>
     </row>
-    <row r="8" spans="1:35" s="9" customFormat="1" ht="41.4" customHeight="1">
+    <row r="8" spans="1:35" s="9" customFormat="1" ht="41.45" customHeight="1">
       <c r="A8" s="19">
         <v>2024</v>
       </c>
@@ -6108,7 +6141,7 @@
       <c r="AH8" s="12"/>
       <c r="AI8" s="8"/>
     </row>
-    <row r="9" spans="1:35" s="9" customFormat="1" ht="41.4" customHeight="1">
+    <row r="9" spans="1:35" s="9" customFormat="1" ht="41.45" customHeight="1">
       <c r="A9" s="19">
         <v>2024</v>
       </c>
@@ -6194,7 +6227,7 @@
       <c r="AH9" s="12"/>
       <c r="AI9" s="8"/>
     </row>
-    <row r="10" spans="1:35" s="9" customFormat="1" ht="41.4" customHeight="1">
+    <row r="10" spans="1:35" s="9" customFormat="1" ht="41.45" customHeight="1">
       <c r="A10" s="19">
         <v>2024</v>
       </c>
@@ -6282,7 +6315,7 @@
       <c r="AH10" s="12"/>
       <c r="AI10" s="8"/>
     </row>
-    <row r="11" spans="1:35" s="9" customFormat="1" ht="41.4" customHeight="1">
+    <row r="11" spans="1:35" s="9" customFormat="1" ht="41.45" customHeight="1">
       <c r="A11" s="19">
         <v>2024</v>
       </c>
@@ -6372,7 +6405,7 @@
       <c r="AH11" s="12"/>
       <c r="AI11" s="8"/>
     </row>
-    <row r="12" spans="1:35" s="9" customFormat="1" ht="41.4" customHeight="1">
+    <row r="12" spans="1:35" s="9" customFormat="1" ht="41.45" customHeight="1">
       <c r="A12" s="19">
         <v>2024</v>
       </c>
@@ -6460,7 +6493,7 @@
       <c r="AH12" s="12"/>
       <c r="AI12" s="8"/>
     </row>
-    <row r="13" spans="1:35" s="9" customFormat="1" ht="41.4" customHeight="1">
+    <row r="13" spans="1:35" s="9" customFormat="1" ht="41.45" customHeight="1">
       <c r="A13" s="19">
         <v>2024</v>
       </c>
@@ -6550,7 +6583,7 @@
       <c r="AH13" s="12"/>
       <c r="AI13" s="8"/>
     </row>
-    <row r="14" spans="1:35" s="9" customFormat="1" ht="41.4" customHeight="1">
+    <row r="14" spans="1:35" s="9" customFormat="1" ht="41.45" customHeight="1">
       <c r="A14" s="19">
         <v>2024</v>
       </c>
@@ -6640,7 +6673,7 @@
       <c r="AH14" s="12"/>
       <c r="AI14" s="8"/>
     </row>
-    <row r="15" spans="1:35" s="9" customFormat="1" ht="41.4" customHeight="1">
+    <row r="15" spans="1:35" s="9" customFormat="1" ht="41.45" customHeight="1">
       <c r="A15" s="19">
         <v>2024</v>
       </c>
@@ -6728,7 +6761,7 @@
       <c r="AH15" s="12"/>
       <c r="AI15" s="8"/>
     </row>
-    <row r="16" spans="1:35" s="9" customFormat="1" ht="41.4" customHeight="1">
+    <row r="16" spans="1:35" s="9" customFormat="1" ht="41.45" customHeight="1">
       <c r="A16" s="19">
         <v>2024</v>
       </c>
@@ -6818,7 +6851,7 @@
       <c r="AH16" s="12"/>
       <c r="AI16" s="8"/>
     </row>
-    <row r="17" spans="1:35" s="9" customFormat="1" ht="41.4" customHeight="1">
+    <row r="17" spans="1:35" s="9" customFormat="1" ht="41.45" customHeight="1">
       <c r="A17" s="19">
         <v>2024</v>
       </c>
@@ -6906,7 +6939,7 @@
       <c r="AH17" s="12"/>
       <c r="AI17" s="8"/>
     </row>
-    <row r="18" spans="1:35" s="9" customFormat="1" ht="41.4" customHeight="1">
+    <row r="18" spans="1:35" s="9" customFormat="1" ht="41.45" customHeight="1">
       <c r="A18" s="19">
         <v>2024</v>
       </c>
@@ -6996,7 +7029,7 @@
       <c r="AH18" s="12"/>
       <c r="AI18" s="8"/>
     </row>
-    <row r="19" spans="1:35" s="9" customFormat="1" ht="41.4" customHeight="1">
+    <row r="19" spans="1:35" s="9" customFormat="1" ht="41.45" customHeight="1">
       <c r="A19" s="19">
         <v>2024</v>
       </c>
@@ -7086,7 +7119,7 @@
       <c r="AH19" s="12"/>
       <c r="AI19" s="8"/>
     </row>
-    <row r="20" spans="1:35" s="9" customFormat="1" ht="41.4" customHeight="1">
+    <row r="20" spans="1:35" s="9" customFormat="1" ht="41.45" customHeight="1">
       <c r="A20" s="19">
         <v>2024</v>
       </c>
@@ -7176,7 +7209,7 @@
       <c r="AH20" s="12"/>
       <c r="AI20" s="8"/>
     </row>
-    <row r="21" spans="1:35" s="9" customFormat="1" ht="41.4" customHeight="1">
+    <row r="21" spans="1:35" s="9" customFormat="1" ht="41.45" customHeight="1">
       <c r="A21" s="46">
         <v>2025</v>
       </c>
@@ -7266,7 +7299,7 @@
       <c r="AH21" s="12"/>
       <c r="AI21" s="8"/>
     </row>
-    <row r="22" spans="1:35" s="9" customFormat="1" ht="41.4" customHeight="1">
+    <row r="22" spans="1:35" s="9" customFormat="1" ht="41.45" customHeight="1">
       <c r="A22" s="46">
         <v>2025</v>
       </c>
@@ -7358,7 +7391,7 @@
       <c r="AH22" s="12"/>
       <c r="AI22" s="8"/>
     </row>
-    <row r="23" spans="1:35" s="9" customFormat="1" ht="41.4" customHeight="1">
+    <row r="23" spans="1:35" s="9" customFormat="1" ht="41.45" customHeight="1">
       <c r="A23" s="46">
         <v>2025</v>
       </c>
@@ -7450,7 +7483,7 @@
       <c r="AH23" s="12"/>
       <c r="AI23" s="8"/>
     </row>
-    <row r="24" spans="1:35" s="9" customFormat="1" ht="41.4" customHeight="1">
+    <row r="24" spans="1:35" s="9" customFormat="1" ht="41.45" customHeight="1">
       <c r="A24" s="46">
         <v>2025</v>
       </c>
@@ -7542,7 +7575,7 @@
       <c r="AH24" s="12"/>
       <c r="AI24" s="8"/>
     </row>
-    <row r="25" spans="1:35" s="9" customFormat="1" ht="41.4" customHeight="1">
+    <row r="25" spans="1:35" s="9" customFormat="1" ht="41.45" customHeight="1">
       <c r="A25" s="46">
         <v>2025</v>
       </c>
@@ -7634,7 +7667,7 @@
       <c r="AH25" s="12"/>
       <c r="AI25" s="8"/>
     </row>
-    <row r="26" spans="1:35" s="9" customFormat="1" ht="41.4" customHeight="1">
+    <row r="26" spans="1:35" s="9" customFormat="1" ht="41.45" customHeight="1">
       <c r="A26" s="46">
         <v>2025</v>
       </c>
@@ -7726,7 +7759,7 @@
       <c r="AH26" s="12"/>
       <c r="AI26" s="8"/>
     </row>
-    <row r="27" spans="1:35" s="9" customFormat="1" ht="41.4" customHeight="1">
+    <row r="27" spans="1:35" s="9" customFormat="1" ht="41.45" customHeight="1">
       <c r="A27" s="46">
         <v>2025</v>
       </c>
@@ -7816,7 +7849,7 @@
       <c r="AH27" s="12"/>
       <c r="AI27" s="8"/>
     </row>
-    <row r="28" spans="1:35" s="9" customFormat="1" ht="41.4" customHeight="1">
+    <row r="28" spans="1:35" s="9" customFormat="1" ht="41.45" customHeight="1">
       <c r="A28" s="46">
         <v>2025</v>
       </c>
@@ -7908,7 +7941,7 @@
       <c r="AH28" s="12"/>
       <c r="AI28" s="8"/>
     </row>
-    <row r="29" spans="1:35" s="9" customFormat="1" ht="41.4" customHeight="1">
+    <row r="29" spans="1:35" s="9" customFormat="1" ht="41.45" customHeight="1">
       <c r="A29" s="46">
         <v>2025</v>
       </c>
@@ -7998,7 +8031,7 @@
       <c r="AH29" s="12"/>
       <c r="AI29" s="8"/>
     </row>
-    <row r="30" spans="1:35" s="9" customFormat="1" ht="41.4" customHeight="1">
+    <row r="30" spans="1:35" s="9" customFormat="1" ht="41.45" customHeight="1">
       <c r="A30" s="46">
         <v>2025</v>
       </c>
@@ -8090,7 +8123,7 @@
       <c r="AH30" s="12"/>
       <c r="AI30" s="8"/>
     </row>
-    <row r="31" spans="1:35" s="9" customFormat="1" ht="41.4" customHeight="1">
+    <row r="31" spans="1:35" s="9" customFormat="1" ht="41.45" customHeight="1">
       <c r="A31" s="46">
         <v>2025</v>
       </c>
@@ -8182,7 +8215,7 @@
       <c r="AH31" s="12"/>
       <c r="AI31" s="8"/>
     </row>
-    <row r="32" spans="1:35" s="9" customFormat="1" ht="41.4" customHeight="1">
+    <row r="32" spans="1:35" s="9" customFormat="1" ht="41.45" customHeight="1">
       <c r="A32" s="46">
         <v>2025</v>
       </c>
@@ -8274,7 +8307,7 @@
       <c r="AH32" s="12"/>
       <c r="AI32" s="8"/>
     </row>
-    <row r="33" spans="1:35" s="9" customFormat="1" ht="41.4" customHeight="1">
+    <row r="33" spans="1:35" s="9" customFormat="1" ht="41.45" customHeight="1">
       <c r="A33" s="46">
         <v>2025</v>
       </c>
@@ -8364,7 +8397,7 @@
       <c r="AH33" s="12"/>
       <c r="AI33" s="8"/>
     </row>
-    <row r="34" spans="1:35" s="9" customFormat="1" ht="41.4" customHeight="1">
+    <row r="34" spans="1:35" s="9" customFormat="1" ht="41.45" customHeight="1">
       <c r="A34" s="46">
         <v>2025</v>
       </c>
@@ -8462,7 +8495,7 @@
       <c r="AH34" s="12"/>
       <c r="AI34" s="8"/>
     </row>
-    <row r="35" spans="1:35" s="9" customFormat="1" ht="41.4" customHeight="1">
+    <row r="35" spans="1:35" s="9" customFormat="1" ht="41.45" customHeight="1">
       <c r="A35" s="46">
         <v>2025</v>
       </c>
@@ -8554,7 +8587,7 @@
       <c r="AH35" s="12"/>
       <c r="AI35" s="8"/>
     </row>
-    <row r="36" spans="1:35" s="9" customFormat="1" ht="41.4" customHeight="1">
+    <row r="36" spans="1:35" s="9" customFormat="1" ht="41.45" customHeight="1">
       <c r="A36" s="46">
         <v>2025</v>
       </c>
@@ -8646,7 +8679,7 @@
       <c r="AH36" s="12"/>
       <c r="AI36" s="8"/>
     </row>
-    <row r="37" spans="1:35" s="9" customFormat="1" ht="41.4" customHeight="1">
+    <row r="37" spans="1:35" s="9" customFormat="1" ht="41.45" customHeight="1">
       <c r="A37" s="46">
         <v>2025</v>
       </c>
@@ -8705,7 +8738,7 @@
       Dropdown!$A$2:$A$100
    )
 )</f>
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="Q37" s="13" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -8730,7 +8763,7 @@
       <c r="AH37" s="12"/>
       <c r="AI37" s="8"/>
     </row>
-    <row r="38" spans="1:35" s="9" customFormat="1" ht="41.4" customHeight="1">
+    <row r="38" spans="1:35" s="9" customFormat="1" ht="41.45" customHeight="1">
       <c r="A38" s="46">
         <v>2025</v>
       </c>
@@ -8822,7 +8855,7 @@
       <c r="AH38" s="12"/>
       <c r="AI38" s="8"/>
     </row>
-    <row r="39" spans="1:35" s="9" customFormat="1" ht="41.4" customHeight="1">
+    <row r="39" spans="1:35" s="9" customFormat="1" ht="41.45" customHeight="1">
       <c r="A39" s="46">
         <v>2025</v>
       </c>
@@ -8912,7 +8945,7 @@
       <c r="AH39" s="12"/>
       <c r="AI39" s="8"/>
     </row>
-    <row r="40" spans="1:35" s="9" customFormat="1" ht="41.4" customHeight="1">
+    <row r="40" spans="1:35" s="9" customFormat="1" ht="41.45" customHeight="1">
       <c r="A40" s="46">
         <v>2025</v>
       </c>
@@ -9002,7 +9035,7 @@
       <c r="AH40" s="12"/>
       <c r="AI40" s="8"/>
     </row>
-    <row r="41" spans="1:35" s="9" customFormat="1" ht="41.4" customHeight="1">
+    <row r="41" spans="1:35" s="9" customFormat="1" ht="41.45" customHeight="1">
       <c r="A41" s="46">
         <v>2025</v>
       </c>
@@ -9094,7 +9127,7 @@
       <c r="AH41" s="12"/>
       <c r="AI41" s="8"/>
     </row>
-    <row r="42" spans="1:35" s="9" customFormat="1" ht="41.4" customHeight="1">
+    <row r="42" spans="1:35" s="9" customFormat="1" ht="41.45" customHeight="1">
       <c r="A42" s="46">
         <v>2025</v>
       </c>
@@ -9186,7 +9219,7 @@
       <c r="AH42" s="12"/>
       <c r="AI42" s="8"/>
     </row>
-    <row r="43" spans="1:35" s="9" customFormat="1" ht="41.4" customHeight="1">
+    <row r="43" spans="1:35" s="9" customFormat="1" ht="41.45" customHeight="1">
       <c r="A43" s="46">
         <v>2025</v>
       </c>
@@ -9276,7 +9309,7 @@
       <c r="AH43" s="12"/>
       <c r="AI43" s="8"/>
     </row>
-    <row r="44" spans="1:35" s="9" customFormat="1" ht="41.4" customHeight="1">
+    <row r="44" spans="1:35" s="9" customFormat="1" ht="41.45" customHeight="1">
       <c r="A44" s="46">
         <v>2025</v>
       </c>
@@ -9366,7 +9399,7 @@
       <c r="AH44" s="12"/>
       <c r="AI44" s="8"/>
     </row>
-    <row r="45" spans="1:35" s="9" customFormat="1" ht="41.4" customHeight="1">
+    <row r="45" spans="1:35" s="9" customFormat="1" ht="41.45" customHeight="1">
       <c r="A45" s="46">
         <v>2025</v>
       </c>
@@ -9456,7 +9489,7 @@
       <c r="AH45" s="12"/>
       <c r="AI45" s="8"/>
     </row>
-    <row r="46" spans="1:35" s="9" customFormat="1" ht="41.4" customHeight="1">
+    <row r="46" spans="1:35" s="9" customFormat="1" ht="41.45" customHeight="1">
       <c r="A46" s="46">
         <v>2025</v>
       </c>
@@ -9546,7 +9579,7 @@
       <c r="AH46" s="12"/>
       <c r="AI46" s="8"/>
     </row>
-    <row r="47" spans="1:35" s="9" customFormat="1" ht="41.4" customHeight="1">
+    <row r="47" spans="1:35" s="9" customFormat="1" ht="41.45" customHeight="1">
       <c r="A47" s="46">
         <v>2025</v>
       </c>
@@ -9634,7 +9667,7 @@
       <c r="AH47" s="12"/>
       <c r="AI47" s="8"/>
     </row>
-    <row r="48" spans="1:35" s="9" customFormat="1" ht="41.4" customHeight="1">
+    <row r="48" spans="1:35" s="9" customFormat="1" ht="41.45" customHeight="1">
       <c r="A48" s="46">
         <v>2025</v>
       </c>
@@ -9726,7 +9759,7 @@
       <c r="AH48" s="12"/>
       <c r="AI48" s="8"/>
     </row>
-    <row r="49" spans="1:35" s="9" customFormat="1" ht="41.4" customHeight="1">
+    <row r="49" spans="1:35" s="9" customFormat="1" ht="41.45" customHeight="1">
       <c r="A49" s="46">
         <v>2025</v>
       </c>
@@ -9818,7 +9851,7 @@
       <c r="AH49" s="12"/>
       <c r="AI49" s="8"/>
     </row>
-    <row r="50" spans="1:35" s="9" customFormat="1" ht="41.4" customHeight="1">
+    <row r="50" spans="1:35" s="9" customFormat="1" ht="41.45" customHeight="1">
       <c r="A50" s="46">
         <v>2025</v>
       </c>
@@ -9908,7 +9941,7 @@
       <c r="AH50" s="12"/>
       <c r="AI50" s="8"/>
     </row>
-    <row r="51" spans="1:35" s="9" customFormat="1" ht="41.4" customHeight="1">
+    <row r="51" spans="1:35" s="9" customFormat="1" ht="41.45" customHeight="1">
       <c r="A51" s="46">
         <v>2025</v>
       </c>
@@ -9998,7 +10031,7 @@
       <c r="AH51" s="12"/>
       <c r="AI51" s="8"/>
     </row>
-    <row r="52" spans="1:35" s="9" customFormat="1" ht="41.4" customHeight="1">
+    <row r="52" spans="1:35" s="9" customFormat="1" ht="41.45" customHeight="1">
       <c r="A52" s="46">
         <v>2025</v>
       </c>
@@ -10088,7 +10121,7 @@
       <c r="AH52" s="12"/>
       <c r="AI52" s="8"/>
     </row>
-    <row r="53" spans="1:35" s="9" customFormat="1" ht="41.4" customHeight="1">
+    <row r="53" spans="1:35" s="9" customFormat="1" ht="41.45" customHeight="1">
       <c r="A53" s="46">
         <v>2025</v>
       </c>
@@ -10178,7 +10211,7 @@
       <c r="AH53" s="12"/>
       <c r="AI53" s="8"/>
     </row>
-    <row r="54" spans="1:35" s="9" customFormat="1" ht="41.4" customHeight="1">
+    <row r="54" spans="1:35" s="9" customFormat="1" ht="41.45" customHeight="1">
       <c r="A54" s="46">
         <v>2025</v>
       </c>
@@ -10268,7 +10301,7 @@
       <c r="AH54" s="12"/>
       <c r="AI54" s="8"/>
     </row>
-    <row r="55" spans="1:35" s="9" customFormat="1" ht="41.4" customHeight="1">
+    <row r="55" spans="1:35" s="9" customFormat="1" ht="41.45" customHeight="1">
       <c r="A55" s="46">
         <v>2025</v>
       </c>
@@ -10358,7 +10391,7 @@
       <c r="AH55" s="12"/>
       <c r="AI55" s="8"/>
     </row>
-    <row r="56" spans="1:35" s="9" customFormat="1" ht="41.4" customHeight="1">
+    <row r="56" spans="1:35" s="9" customFormat="1" ht="41.45" customHeight="1">
       <c r="A56" s="46">
         <v>2025</v>
       </c>
@@ -10444,7 +10477,7 @@
       <c r="AH56" s="12"/>
       <c r="AI56" s="8"/>
     </row>
-    <row r="57" spans="1:35" s="9" customFormat="1" ht="41.4" customHeight="1">
+    <row r="57" spans="1:35" s="9" customFormat="1" ht="41.45" customHeight="1">
       <c r="A57" s="46">
         <v>2025</v>
       </c>
@@ -10532,7 +10565,7 @@
       <c r="AH57" s="12"/>
       <c r="AI57" s="8"/>
     </row>
-    <row r="58" spans="1:35" s="9" customFormat="1" ht="41.4" customHeight="1">
+    <row r="58" spans="1:35" s="9" customFormat="1" ht="41.45" customHeight="1">
       <c r="A58" s="46">
         <v>2025</v>
       </c>
@@ -10622,7 +10655,7 @@
       <c r="AH58" s="12"/>
       <c r="AI58" s="8"/>
     </row>
-    <row r="59" spans="1:35" s="9" customFormat="1" ht="41.4" customHeight="1">
+    <row r="59" spans="1:35" s="9" customFormat="1" ht="41.45" customHeight="1">
       <c r="A59" s="46">
         <v>2025</v>
       </c>
@@ -10714,7 +10747,7 @@
       <c r="AH59" s="12"/>
       <c r="AI59" s="8"/>
     </row>
-    <row r="60" spans="1:35" s="9" customFormat="1" ht="41.4" customHeight="1">
+    <row r="60" spans="1:35" s="9" customFormat="1" ht="41.45" customHeight="1">
       <c r="A60" s="46">
         <v>2025</v>
       </c>
@@ -10806,7 +10839,7 @@
       <c r="AH60" s="12"/>
       <c r="AI60" s="8"/>
     </row>
-    <row r="61" spans="1:35" s="9" customFormat="1" ht="41.4" customHeight="1">
+    <row r="61" spans="1:35" s="9" customFormat="1" ht="41.45" customHeight="1">
       <c r="A61" s="46">
         <v>2025</v>
       </c>
@@ -10896,7 +10929,7 @@
       <c r="AH61" s="12"/>
       <c r="AI61" s="8"/>
     </row>
-    <row r="62" spans="1:35" s="9" customFormat="1" ht="41.4" customHeight="1">
+    <row r="62" spans="1:35" s="9" customFormat="1" ht="41.45" customHeight="1">
       <c r="A62" s="46">
         <v>2025</v>
       </c>
@@ -10986,7 +11019,7 @@
       <c r="AH62" s="12"/>
       <c r="AI62" s="8"/>
     </row>
-    <row r="63" spans="1:35" s="9" customFormat="1" ht="41.4" customHeight="1">
+    <row r="63" spans="1:35" s="9" customFormat="1" ht="41.45" customHeight="1">
       <c r="A63" s="46">
         <v>2025</v>
       </c>
@@ -11076,7 +11109,7 @@
       <c r="AH63" s="12"/>
       <c r="AI63" s="8"/>
     </row>
-    <row r="64" spans="1:35" s="9" customFormat="1" ht="41.4" customHeight="1">
+    <row r="64" spans="1:35" s="9" customFormat="1" ht="41.45" customHeight="1">
       <c r="A64" s="46">
         <v>2025</v>
       </c>
@@ -11168,7 +11201,7 @@
       <c r="AH64" s="12"/>
       <c r="AI64" s="8"/>
     </row>
-    <row r="65" spans="1:35" s="9" customFormat="1" ht="41.4" customHeight="1">
+    <row r="65" spans="1:35" s="9" customFormat="1" ht="41.45" customHeight="1">
       <c r="A65" s="46">
         <v>2025</v>
       </c>
@@ -11260,7 +11293,7 @@
       <c r="AH65" s="12"/>
       <c r="AI65" s="8"/>
     </row>
-    <row r="66" spans="1:35" s="9" customFormat="1" ht="41.4" customHeight="1">
+    <row r="66" spans="1:35" s="9" customFormat="1" ht="41.45" customHeight="1">
       <c r="A66" s="46">
         <v>2025</v>
       </c>
@@ -11360,7 +11393,7 @@
       <c r="AH66" s="12"/>
       <c r="AI66" s="8"/>
     </row>
-    <row r="67" spans="1:35" s="9" customFormat="1" ht="41.4" customHeight="1">
+    <row r="67" spans="1:35" s="9" customFormat="1" ht="41.45" customHeight="1">
       <c r="A67" s="46">
         <v>2025</v>
       </c>
@@ -11450,7 +11483,7 @@
       <c r="AH67" s="12"/>
       <c r="AI67" s="8"/>
     </row>
-    <row r="68" spans="1:35" s="9" customFormat="1" ht="41.4" customHeight="1">
+    <row r="68" spans="1:35" s="9" customFormat="1" ht="41.45" customHeight="1">
       <c r="A68" s="46">
         <v>2025</v>
       </c>
@@ -11540,7 +11573,7 @@
       <c r="AH68" s="12"/>
       <c r="AI68" s="8"/>
     </row>
-    <row r="69" spans="1:35" s="9" customFormat="1" ht="41.4" customHeight="1">
+    <row r="69" spans="1:35" s="9" customFormat="1" ht="41.45" customHeight="1">
       <c r="A69" s="46">
         <v>2025</v>
       </c>
@@ -11632,7 +11665,7 @@
       <c r="AH69" s="12"/>
       <c r="AI69" s="8"/>
     </row>
-    <row r="70" spans="1:35" s="9" customFormat="1" ht="41.4" customHeight="1">
+    <row r="70" spans="1:35" s="9" customFormat="1" ht="41.45" customHeight="1">
       <c r="A70" s="46">
         <v>2025</v>
       </c>
@@ -11693,7 +11726,7 @@
       Dropdown!$A$2:$A$100
    )
 )</f>
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q70" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -11722,7 +11755,7 @@
       <c r="AH70" s="12"/>
       <c r="AI70" s="8"/>
     </row>
-    <row r="71" spans="1:35" s="9" customFormat="1" ht="41.4" customHeight="1">
+    <row r="71" spans="1:35" s="9" customFormat="1" ht="41.45" customHeight="1">
       <c r="A71" s="46">
         <v>2025</v>
       </c>
@@ -11814,7 +11847,7 @@
       <c r="AH71" s="12"/>
       <c r="AI71" s="8"/>
     </row>
-    <row r="72" spans="1:35" s="9" customFormat="1" ht="41.4" customHeight="1">
+    <row r="72" spans="1:35" s="9" customFormat="1" ht="41.45" customHeight="1">
       <c r="A72" s="46">
         <v>2025</v>
       </c>
@@ -11906,7 +11939,7 @@
       <c r="AH72" s="12"/>
       <c r="AI72" s="8"/>
     </row>
-    <row r="73" spans="1:35" s="9" customFormat="1" ht="41.4" customHeight="1">
+    <row r="73" spans="1:35" s="9" customFormat="1" ht="41.45" customHeight="1">
       <c r="A73" s="46">
         <v>2025</v>
       </c>
@@ -11998,7 +12031,7 @@
       <c r="AH73" s="12"/>
       <c r="AI73" s="8"/>
     </row>
-    <row r="74" spans="1:35" s="9" customFormat="1" ht="41.4" customHeight="1">
+    <row r="74" spans="1:35" s="9" customFormat="1" ht="41.45" customHeight="1">
       <c r="A74" s="46">
         <v>2025</v>
       </c>
@@ -12090,7 +12123,7 @@
       <c r="AH74" s="12"/>
       <c r="AI74" s="8"/>
     </row>
-    <row r="75" spans="1:35" s="9" customFormat="1" ht="41.4" customHeight="1">
+    <row r="75" spans="1:35" s="9" customFormat="1" ht="41.45" customHeight="1">
       <c r="A75" s="46">
         <v>2025</v>
       </c>
@@ -12184,7 +12217,7 @@
       <c r="AH75" s="12"/>
       <c r="AI75" s="8"/>
     </row>
-    <row r="76" spans="1:35" s="9" customFormat="1" ht="41.4" customHeight="1">
+    <row r="76" spans="1:35" s="9" customFormat="1" ht="41.45" customHeight="1">
       <c r="A76" s="46">
         <v>2025</v>
       </c>
@@ -12276,7 +12309,7 @@
       <c r="AH76" s="17"/>
       <c r="AI76" s="8"/>
     </row>
-    <row r="77" spans="1:35" s="9" customFormat="1" ht="41.4" customHeight="1">
+    <row r="77" spans="1:35" s="9" customFormat="1" ht="41.45" customHeight="1">
       <c r="A77" s="46">
         <v>2025</v>
       </c>
@@ -12368,7 +12401,7 @@
       <c r="AH77" s="17"/>
       <c r="AI77" s="8"/>
     </row>
-    <row r="78" spans="1:35" s="11" customFormat="1" ht="41.4" customHeight="1">
+    <row r="78" spans="1:35" s="11" customFormat="1" ht="41.45" customHeight="1">
       <c r="A78" s="46">
         <v>2025</v>
       </c>
@@ -12466,7 +12499,7 @@
       <c r="AH78" s="12"/>
       <c r="AI78" s="8"/>
     </row>
-    <row r="79" spans="1:35" s="11" customFormat="1" ht="41.4" customHeight="1">
+    <row r="79" spans="1:35" s="11" customFormat="1" ht="41.45" customHeight="1">
       <c r="A79" s="46">
         <v>2025</v>
       </c>
@@ -12554,7 +12587,7 @@
       <c r="AH79" s="12"/>
       <c r="AI79" s="8"/>
     </row>
-    <row r="80" spans="1:35" s="11" customFormat="1" ht="41.4" customHeight="1">
+    <row r="80" spans="1:35" s="11" customFormat="1" ht="41.45" customHeight="1">
       <c r="A80" s="46">
         <v>2025</v>
       </c>
@@ -12646,7 +12679,7 @@
       <c r="AH80" s="17"/>
       <c r="AI80" s="8"/>
     </row>
-    <row r="81" spans="1:35" s="11" customFormat="1" ht="41.4" customHeight="1">
+    <row r="81" spans="1:35" s="11" customFormat="1" ht="41.45" customHeight="1">
       <c r="A81" s="46">
         <v>2025</v>
       </c>
@@ -12738,7 +12771,7 @@
       <c r="AH81" s="12"/>
       <c r="AI81" s="8"/>
     </row>
-    <row r="82" spans="1:35" s="11" customFormat="1" ht="41.4" customHeight="1">
+    <row r="82" spans="1:35" s="11" customFormat="1" ht="41.45" customHeight="1">
       <c r="A82" s="46">
         <v>2025</v>
       </c>
@@ -12826,7 +12859,7 @@
       <c r="AH82" s="17"/>
       <c r="AI82" s="8"/>
     </row>
-    <row r="83" spans="1:35" s="11" customFormat="1" ht="41.4" customHeight="1">
+    <row r="83" spans="1:35" s="11" customFormat="1" ht="41.45" customHeight="1">
       <c r="A83" s="46">
         <v>2025</v>
       </c>
@@ -12918,7 +12951,7 @@
       <c r="AH83" s="17"/>
       <c r="AI83" s="8"/>
     </row>
-    <row r="84" spans="1:35" s="11" customFormat="1" ht="41.4" customHeight="1">
+    <row r="84" spans="1:35" s="11" customFormat="1" ht="41.45" customHeight="1">
       <c r="A84" s="46">
         <v>2025</v>
       </c>
@@ -13010,7 +13043,7 @@
       <c r="AH84" s="17"/>
       <c r="AI84" s="8"/>
     </row>
-    <row r="85" spans="1:35" s="11" customFormat="1" ht="41.4" customHeight="1">
+    <row r="85" spans="1:35" s="11" customFormat="1" ht="41.45" customHeight="1">
       <c r="A85" s="46">
         <v>2025</v>
       </c>
@@ -13102,7 +13135,7 @@
       <c r="AH85" s="17"/>
       <c r="AI85" s="8"/>
     </row>
-    <row r="86" spans="1:35" s="11" customFormat="1" ht="41.4" customHeight="1">
+    <row r="86" spans="1:35" s="11" customFormat="1" ht="41.45" customHeight="1">
       <c r="A86" s="46">
         <v>2025</v>
       </c>
@@ -13194,7 +13227,7 @@
       <c r="AH86" s="17"/>
       <c r="AI86" s="8"/>
     </row>
-    <row r="87" spans="1:35" s="11" customFormat="1" ht="41.4" customHeight="1">
+    <row r="87" spans="1:35" s="11" customFormat="1" ht="41.45" customHeight="1">
       <c r="A87" s="46">
         <v>2025</v>
       </c>
@@ -13286,7 +13319,7 @@
       <c r="AH87" s="17"/>
       <c r="AI87" s="8"/>
     </row>
-    <row r="88" spans="1:35" s="11" customFormat="1" ht="41.4" customHeight="1">
+    <row r="88" spans="1:35" s="11" customFormat="1" ht="41.45" customHeight="1">
       <c r="A88" s="46">
         <v>2025</v>
       </c>
@@ -13378,7 +13411,7 @@
       <c r="AH88" s="17"/>
       <c r="AI88" s="8"/>
     </row>
-    <row r="89" spans="1:35" s="11" customFormat="1" ht="41.4" customHeight="1">
+    <row r="89" spans="1:35" s="11" customFormat="1" ht="41.45" customHeight="1">
       <c r="A89" s="46">
         <v>2025</v>
       </c>
@@ -13470,7 +13503,7 @@
       <c r="AH89" s="17"/>
       <c r="AI89" s="8"/>
     </row>
-    <row r="90" spans="1:35" s="11" customFormat="1" ht="41.4" customHeight="1">
+    <row r="90" spans="1:35" s="11" customFormat="1" ht="41.45" customHeight="1">
       <c r="A90" s="46">
         <v>2025</v>
       </c>
@@ -13562,7 +13595,7 @@
       <c r="AH90" s="17"/>
       <c r="AI90" s="8"/>
     </row>
-    <row r="91" spans="1:35" s="11" customFormat="1" ht="41.4" customHeight="1">
+    <row r="91" spans="1:35" s="11" customFormat="1" ht="41.45" customHeight="1">
       <c r="A91" s="46">
         <v>2025</v>
       </c>
@@ -13652,7 +13685,7 @@
       <c r="AH91" s="17"/>
       <c r="AI91" s="8"/>
     </row>
-    <row r="92" spans="1:35" s="11" customFormat="1" ht="41.4" customHeight="1">
+    <row r="92" spans="1:35" s="11" customFormat="1" ht="41.45" customHeight="1">
       <c r="A92" s="46">
         <v>2025</v>
       </c>
@@ -13713,7 +13746,7 @@
       Dropdown!$A$2:$A$100
    )
 )</f>
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q92" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -13742,7 +13775,7 @@
       <c r="AH92" s="17"/>
       <c r="AI92" s="8"/>
     </row>
-    <row r="93" spans="1:35" s="11" customFormat="1" ht="41.4" customHeight="1">
+    <row r="93" spans="1:35" s="11" customFormat="1" ht="41.45" customHeight="1">
       <c r="A93" s="46">
         <v>2025</v>
       </c>
@@ -13830,7 +13863,7 @@
       <c r="AH93" s="17"/>
       <c r="AI93" s="8"/>
     </row>
-    <row r="94" spans="1:35" s="11" customFormat="1" ht="41.4" customHeight="1">
+    <row r="94" spans="1:35" s="11" customFormat="1" ht="41.45" customHeight="1">
       <c r="A94" s="46">
         <v>2025</v>
       </c>
@@ -13922,7 +13955,7 @@
       <c r="AH94" s="17"/>
       <c r="AI94" s="8"/>
     </row>
-    <row r="95" spans="1:35" s="11" customFormat="1" ht="41.4" customHeight="1">
+    <row r="95" spans="1:35" s="11" customFormat="1" ht="41.45" customHeight="1">
       <c r="A95" s="46">
         <v>2025</v>
       </c>
@@ -14014,7 +14047,7 @@
       <c r="AH95" s="17"/>
       <c r="AI95" s="8"/>
     </row>
-    <row r="96" spans="1:35" s="11" customFormat="1" ht="41.4" customHeight="1">
+    <row r="96" spans="1:35" s="11" customFormat="1" ht="41.45" customHeight="1">
       <c r="A96" s="46">
         <v>2025</v>
       </c>
@@ -14073,7 +14106,7 @@
       Dropdown!$A$2:$A$100
    )
 )</f>
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q96" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -14102,7 +14135,7 @@
       <c r="AH96" s="17"/>
       <c r="AI96" s="8"/>
     </row>
-    <row r="97" spans="1:35" s="11" customFormat="1" ht="41.4" customHeight="1">
+    <row r="97" spans="1:35" s="11" customFormat="1" ht="41.45" customHeight="1">
       <c r="A97" s="46">
         <v>2025</v>
       </c>
@@ -14163,7 +14196,7 @@
       Dropdown!$A$2:$A$100
    )
 )</f>
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q97" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -14190,7 +14223,7 @@
       <c r="AH97" s="17"/>
       <c r="AI97" s="8"/>
     </row>
-    <row r="98" spans="1:35" s="11" customFormat="1" ht="41.4" customHeight="1">
+    <row r="98" spans="1:35" s="11" customFormat="1" ht="41.45" customHeight="1">
       <c r="A98" s="46">
         <v>2025</v>
       </c>
@@ -16140,7 +16173,7 @@
       Dropdown!$A$2:$A$100
    )
 )</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q117" s="96" t="str">
         <f t="shared" ca="1" si="6"/>
@@ -16234,7 +16267,7 @@
       Dropdown!$A$2:$A$100
    )
 )</f>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q118" s="96" t="str">
         <f t="shared" ca="1" si="6"/>
@@ -16369,45 +16402,127 @@
         <v>390</v>
       </c>
     </row>
+    <row r="120" spans="1:35" ht="20.25" customHeight="1">
+      <c r="A120" s="162">
+        <v>2026</v>
+      </c>
+      <c r="B120" s="160" t="str">
+        <f>IF(M120="", "", TEXT(M120, "[$-en-US]mmmm"))</f>
+        <v>July</v>
+      </c>
+      <c r="C120" s="160"/>
+      <c r="D120" s="163" t="s">
+        <v>370</v>
+      </c>
+      <c r="E120" s="163"/>
+      <c r="F120" s="163"/>
+      <c r="G120" s="163"/>
+      <c r="H120" s="163"/>
+      <c r="I120" s="160" t="s">
+        <v>41</v>
+      </c>
+      <c r="J120" s="160" t="s">
+        <v>42</v>
+      </c>
+      <c r="K120" s="163"/>
+      <c r="L120" s="160" t="s">
+        <v>381</v>
+      </c>
+      <c r="M120" s="98">
+        <v>46217</v>
+      </c>
+      <c r="N120" s="164">
+        <f>IF(M120="",                                                                                                                                                                                                  "",
+   WORKDAY(
+      M120,
+      IF(I120="S-Special",                                                                                                                                                                                                   45,
+         IF(OR(I120="O-General",                                                                                                                                                                                                   I120="S-General"),                                                                                                                                                                                                   30,                                                                                                                                                                                                   0)),
+      Dropdown!$A$2:$A$100
+   )
+)</f>
+        <v>46265</v>
+      </c>
+      <c r="O120" s="165"/>
+      <c r="P120" s="166">
+        <f ca="1">IF(M120="",                                                                                                                                                                                                   "",
+   NETWORKDAYS(
+      M120,
+      IF(O120&lt;&gt;"",                                                                                                                                                                                                   O120,                                                                                                                                                                                                   TODAY()),
+      Dropdown!$A$2:$A$100
+   )
+)</f>
+        <v>13</v>
+      </c>
+      <c r="Q120" s="166" t="str">
+        <f ca="1">IF(P120="",                                                                                                                                                                                                   "",
+   IF(OR(I120="O-General",                                                                                                                                                                                                   I120="S-General"),
+      IF(P120&lt;=30,                                                                                                                                                                                                   "ON KPI",                                                                                                                                                                                                   "OVER KPI"),
+      IF(I120="S-Special",
+         IF(P120&lt;=45,                                                                                                                                                                                                   "ON KPI",                                                                                                                                                                                                   "OVER KPI"),
+         "Check Type"
+      )
+   )
+)</f>
+        <v>ON KPI</v>
+      </c>
+      <c r="R120" s="160"/>
+      <c r="S120" s="163"/>
+      <c r="T120" s="163"/>
+      <c r="U120" s="163"/>
+      <c r="V120" s="163"/>
+      <c r="W120" s="165"/>
+      <c r="X120" s="163"/>
+      <c r="Y120" s="167"/>
+      <c r="Z120" s="160"/>
+      <c r="AA120" s="163"/>
+      <c r="AB120" s="163"/>
+      <c r="AC120" s="168"/>
+      <c r="AD120" s="168"/>
+      <c r="AE120" s="168"/>
+      <c r="AF120" s="161"/>
+      <c r="AG120" s="161"/>
+      <c r="AH120" s="169"/>
+      <c r="AI120" s="170"/>
+    </row>
   </sheetData>
   <autoFilter ref="V127" xr:uid="{817CD080-0396-428F-B39B-215D57916061}"/>
   <phoneticPr fontId="5" type="noConversion"/>
   <conditionalFormatting sqref="I1:I1048576">
-    <cfRule type="containsText" dxfId="8" priority="3" operator="containsText" text="Special">
+    <cfRule type="containsText" dxfId="62" priority="3" operator="containsText" text="Special">
       <formula>NOT(ISERROR(SEARCH("Special",I1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J1:J1048576">
-    <cfRule type="containsText" dxfId="7" priority="2" operator="containsText" text="Approved">
+    <cfRule type="containsText" dxfId="61" priority="2" operator="containsText" text="Approved">
       <formula>NOT(ISERROR(SEARCH("Approved",J1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K1:K1048576">
-    <cfRule type="containsText" dxfId="6" priority="6" operator="containsText" text="Hold">
+    <cfRule type="containsText" dxfId="60" priority="6" operator="containsText" text="Hold">
       <formula>NOT(ISERROR(SEARCH("Hold",K1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L1:L1048576">
-    <cfRule type="containsText" dxfId="5" priority="1" operator="containsText" text="Final Interview">
+    <cfRule type="containsText" dxfId="59" priority="1" operator="containsText" text="Final Interview">
       <formula>NOT(ISERROR(SEARCH("Final Interview",L1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="4" priority="7" operator="containsText" text="Effective">
+    <cfRule type="containsText" dxfId="58" priority="7" operator="containsText" text="Effective">
       <formula>NOT(ISERROR(SEARCH("Effective",L1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="3" priority="8" operator="containsText" text="Wait to Join">
+    <cfRule type="containsText" dxfId="57" priority="8" operator="containsText" text="Wait to Join">
       <formula>NOT(ISERROR(SEARCH("Wait to Join",L1)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L119">
-    <cfRule type="containsText" dxfId="2" priority="9" operator="containsText" text="Effective">
+  <conditionalFormatting sqref="L2:L120">
+    <cfRule type="containsText" dxfId="56" priority="9" operator="containsText" text="Effective">
       <formula>NOT(ISERROR(SEARCH("Effective",L2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q1:R1048576">
-    <cfRule type="containsText" dxfId="1" priority="4" operator="containsText" text="OVER KPI">
+    <cfRule type="containsText" dxfId="55" priority="4" operator="containsText" text="OVER KPI">
       <formula>NOT(ISERROR(SEARCH("OVER KPI",Q1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="5" operator="containsText" text="ON KPI">
+    <cfRule type="containsText" dxfId="54" priority="5" operator="containsText" text="ON KPI">
       <formula>NOT(ISERROR(SEARCH("ON KPI",Q1)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -16455,7 +16570,7 @@
           <x14:formula1>
             <xm:f>Dropdown!$B$2:$B$4</xm:f>
           </x14:formula1>
-          <xm:sqref>I2:I119</xm:sqref>
+          <xm:sqref>I2:I120</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{38F39922-C8D8-44DD-A2D9-454996D8D019}">
           <x14:formula1>
@@ -16514,18 +16629,18 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10D5335D-9F7C-4ABD-A50B-EC31212444DC}">
   <dimension ref="A1:N1000"/>
-  <sheetFormatPr defaultColWidth="13.09765625" defaultRowHeight="21"/>
+  <sheetFormatPr defaultColWidth="13.125" defaultRowHeight="21"/>
   <cols>
-    <col min="1" max="1" width="13.19921875" style="4" customWidth="1"/>
-    <col min="2" max="2" width="17.09765625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="18.3984375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="17.69921875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="9.19921875" style="1" customWidth="1"/>
-    <col min="6" max="6" width="26.3984375" style="1" customWidth="1"/>
-    <col min="7" max="7" width="10.8984375" style="1" customWidth="1"/>
-    <col min="8" max="8" width="9.3984375" style="1" customWidth="1"/>
-    <col min="9" max="1256" width="13.09765625" style="1" customWidth="1"/>
-    <col min="1257" max="16384" width="13.09765625" style="1"/>
+    <col min="1" max="1" width="13.25" style="4" customWidth="1"/>
+    <col min="2" max="2" width="17.125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="18.375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="17.75" style="1" customWidth="1"/>
+    <col min="5" max="5" width="9.25" style="1" customWidth="1"/>
+    <col min="6" max="6" width="26.375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="10.875" style="1" customWidth="1"/>
+    <col min="8" max="8" width="9.375" style="1" customWidth="1"/>
+    <col min="9" max="1256" width="13.125" style="1" customWidth="1"/>
+    <col min="1257" max="16384" width="13.125" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14">
@@ -22635,9 +22750,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D1A6C64-69F4-4545-BE72-A6524BCDF0E8}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
-    <col min="3" max="3" width="12.19921875" customWidth="1"/>
+    <col min="3" max="3" width="12.25" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -22707,16 +22822,16 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1604666B-AC1B-411C-B2FA-DEDBF24279BE}">
   <dimension ref="A1:AD1010"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="25.8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="25.9"/>
   <cols>
-    <col min="1" max="1" width="37.09765625" style="124" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.19921875" style="124" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.59765625" style="124" customWidth="1"/>
-    <col min="4" max="4" width="13.59765625" style="124" customWidth="1"/>
+    <col min="1" max="1" width="37.125" style="124" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.25" style="124" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.625" style="124" customWidth="1"/>
+    <col min="4" max="4" width="13.625" style="124" customWidth="1"/>
     <col min="5" max="7" width="9" style="124"/>
-    <col min="8" max="8" width="22.09765625" style="124" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="22.125" style="124" bestFit="1" customWidth="1"/>
     <col min="9" max="11" width="9" style="124"/>
-    <col min="12" max="12" width="9.8984375" style="124" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.875" style="124" bestFit="1" customWidth="1"/>
     <col min="13" max="16384" width="9" style="124"/>
   </cols>
   <sheetData>

--- a/data/Recruitment_Requisition.xlsx
+++ b/data/Recruitment_Requisition.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30327"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30417"/>
   <workbookPr hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://kubotagroup-my.sharepoint.com/personal/lapat_j_kubota_com/Documents/Documents/Recruitment Tools/Dashboard Data Report/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3399" documentId="8_{4185217D-4006-4629-AD3A-0737CE05813A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A59A39FE-34CA-41BC-9C2A-C77665FFA6F6}"/>
+  <xr:revisionPtr revIDLastSave="3544" documentId="8_{4185217D-4006-4629-AD3A-0737CE05813A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5DF28699-D34E-44BB-8FC4-5471B5FF98C6}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{5982D4A9-2AD8-4F8A-AE0B-0D729A27807E}"/>
   </bookViews>
@@ -19,7 +19,7 @@
     <sheet name="Cost Per Hire" sheetId="13" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Recruitment!$V$127:$V$127</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Recruitment!$D$129:$D$129</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -77,7 +77,7 @@
             <scheme val="minor"/>
           </rPr>
           <t>Suchat Sermsaiprasit (Sermsaiprasit Suchat):
-หมด JDB, Form</t>
+มข พอได้ - Option รอง</t>
         </r>
       </text>
     </comment>
@@ -95,22 +95,6 @@
           <t xml:space="preserve">Suchat Sermsaiprasit (Sermsaiprasit Suchat):
 ส่งเพิ่ม 2 29/6/26
 หมดเว็บ เหลือ JDB
-</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="M117" authorId="1" shapeId="0" xr:uid="{5A08EBA2-79DB-446F-82F3-697F602812CA}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-            <charset val="222"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t xml:space="preserve">Lapat Jitwongwai (Jitwongwai Lapat):Memo เดิมใช้ของ Service creativity 11/6/2026 มีโยกย้ายและเปลี่ยนมาสรรหาตำแหน่งทีมพี่หน่องแทน
 </t>
         </r>
       </text>
@@ -158,9 +142,9 @@
             <charset val="222"/>
             <scheme val="minor"/>
           </rPr>
-          <t>Lapat Jitwongwai (Jitwongwai Lapat):
-รอพี่แวนเฟิร์มว่าลงตรงไหน 
-หลักๆอยากได้ผู้ชาย</t>
+          <t xml:space="preserve">Lapat Jitwongwai (Jitwongwai Lapat):
+ติดต่อกุนซือ - สนใจ - รุ่นพี่
+</t>
         </r>
       </text>
     </comment>
@@ -169,7 +153,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1882" uniqueCount="592">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1911" uniqueCount="605">
   <si>
     <t>Year</t>
   </si>
@@ -621,6 +605,9 @@
     <t>New Product Inspection</t>
   </si>
   <si>
+    <t>ศวัสกร ปทีปนำพาผล</t>
+  </si>
+  <si>
     <t>Resign</t>
   </si>
   <si>
@@ -966,6 +953,9 @@
     <t>Maintenance</t>
   </si>
   <si>
+    <t>พิเชษฐ์ ปาลรัตน์</t>
+  </si>
+  <si>
     <t>Software Developer</t>
   </si>
   <si>
@@ -978,6 +968,9 @@
     <t>System Developer</t>
   </si>
   <si>
+    <t>พีรพัฒน์ ภักดีพงษ์</t>
+  </si>
+  <si>
     <t>Amata City Environment</t>
   </si>
   <si>
@@ -1011,6 +1004,9 @@
     <t xml:space="preserve"> Carbon Neutrality</t>
   </si>
   <si>
+    <t>นวชัย กลับบ้านเกาะ</t>
+  </si>
+  <si>
     <t>Overseas Smart Contact Center and Privilege Executive</t>
   </si>
   <si>
@@ -1266,7 +1262,10 @@
     <t>Budget Management</t>
   </si>
   <si>
-    <t>Final Interview</t>
+    <t>Screening</t>
+  </si>
+  <si>
+    <t>ไฟนอลวันที่ 13/8</t>
   </si>
   <si>
     <t>มี Lot นึง</t>
@@ -1278,7 +1277,7 @@
     <t>ณัฐนิชา สุภาสืบ</t>
   </si>
   <si>
-    <t>Aug 16,2026</t>
+    <t>Sep 1,2026</t>
   </si>
   <si>
     <t>ทำระบบสำหรับการเก็บข้อมูล เพื่อให้ทาง Data Analyst นำไปวิเคราะห์อีกที - เน้น Coding ต้องรู้โครงสร้างของระบบ, เคยทำ Data Warehouse, Pipeline - 0</t>
@@ -1320,7 +1319,9 @@
     <t>Communication Strategy</t>
   </si>
   <si>
-    <t>Screening</t>
+    <t>ไฟนอล 1 Sep มี can แล้ว 2 คน ให้ส่งเพิ่ม 
+*ปสก. 1-4 ยังพอได้
+*เคย Deal กับ agency</t>
   </si>
   <si>
     <r>
@@ -1349,6 +1350,9 @@
     <t>https://kubotagroup-my.sharepoint.com/:p:/g/personal/sopicha_p_kubota_com/IQC5U4NeJoqtTp54_1oiR2KoAUQFW18kzy5euvdtwGkyYeY?email=lapat.j%40kubota.com&amp;wdExp=TEAMS-TREATMENT&amp;web=1&amp;TeamsCID=f5692ebc-edb5-4e7a-b85e-ccf204ef4d18&amp;isSPOFile=1&amp;ovuser=cdf09dce-c865-4f42-901d-32d3d8d3f60f%2Clapat.j%40kubota.com&amp;clickparams=eyJBcHBOYW1lIjoiVGVhbXMtRGVza3RvcCIsIkFwcFZlcnNpb24iOiI0OS8yNjA2MTExODIxNiIsIkhhc0ZlZGVyYXRlZFVzZXIiOmZhbHNlfQ%3D%3D</t>
   </si>
   <si>
+    <t>สิริมงคล รักอิสระ</t>
+  </si>
+  <si>
     <t xml:space="preserve">จบใหม่ได้, เน้น TU CU, Eng ดีๆ เวลาร่างคอนแทรคต้องใช้ คุยเอเจนซี </t>
   </si>
   <si>
@@ -1362,6 +1366,9 @@
   </si>
   <si>
     <t>อภิชญา ปิยะปราโมทย์</t>
+  </si>
+  <si>
+    <t>ณัฐฑิตา สุวิทย์สกุลวงศ์</t>
   </si>
   <si>
     <t>พัฒนาชิ้นส่วนอะไหล่ของ TR SKC วางแผนพัฒนาชิ้นส่วนทั้งหมด อันไหนควรพัฒนาเอง โคงานเยอะกับทางฝั่งทั้ง QA CS Supplier ทั้งบริษัทการลดต้นทุน
@@ -1374,52 +1381,79 @@
     <t>https://kubotagroup.sharepoint.com/:b:/r/sites/SKC-0AAFVK4bNBX3wUk9PVA/Shared%20Documents/(1)%20HRM/Recruitment/JD/Parts/JD/JD-Strategic%20Parts%20Planning%20%26%20Localization.pdf?csf=1&amp;web=1&amp;e=PizvdD</t>
   </si>
   <si>
-    <t>Engineer(Dealers Sales Development)</t>
+    <t>Human Resources Development Officer</t>
+  </si>
+  <si>
+    <t>Human Resources Development</t>
+  </si>
+  <si>
+    <t>Marketing / Engineer</t>
+  </si>
+  <si>
+    <t>Overseas Service Creativity</t>
+  </si>
+  <si>
+    <t>Overseas &amp; Service Operation Department</t>
+  </si>
+  <si>
+    <t>Overseas service Creativity</t>
+  </si>
+  <si>
+    <t>Scholarship</t>
+  </si>
+  <si>
+    <t>อัมพวา ธรรมอุดมพร</t>
+  </si>
+  <si>
+    <t>พัฒนาโปรแกรมบริการ,วิเคราะห์ข้อมูลและตลาด,ทำงานร่วมกับทีมท้องถิ่นและพาร์ตเนอร์ เพื่อปรับใช้แผนการตลาด</t>
+  </si>
+  <si>
+    <t>https://kubotagroup.sharepoint.com/:w:/s/SKC-0AAFVK4bNBX3wUk9PVA/IQDfjJoQAPbrSrWGoNI732mZAewJ79VOxDSN3tbrIy3K3zA?email=suchat.s%40kubota.com&amp;e=Iwu7Xz</t>
+  </si>
+  <si>
+    <t>Holidays</t>
+  </si>
+  <si>
+    <t>Recruit Status</t>
+  </si>
+  <si>
+    <t>Branch</t>
+  </si>
+  <si>
+    <t>Prioritize</t>
+  </si>
+  <si>
+    <t>Channels</t>
+  </si>
+  <si>
+    <t>Probation</t>
+  </si>
+  <si>
+    <t>Division2</t>
+  </si>
+  <si>
+    <t>Department2</t>
+  </si>
+  <si>
+    <t>Work Unit2</t>
+  </si>
+  <si>
+    <t>Column1</t>
+  </si>
+  <si>
+    <t>Production Line - Assembling</t>
+  </si>
+  <si>
+    <t>Second</t>
   </si>
   <si>
     <t>On Process</t>
   </si>
   <si>
-    <t>Holidays</t>
-  </si>
-  <si>
-    <t>Recruit Status</t>
-  </si>
-  <si>
-    <t>Branch</t>
-  </si>
-  <si>
-    <t>Prioritize</t>
-  </si>
-  <si>
-    <t>Channels</t>
-  </si>
-  <si>
-    <t>Probation</t>
-  </si>
-  <si>
-    <t>Division2</t>
-  </si>
-  <si>
-    <t>Department2</t>
-  </si>
-  <si>
-    <t>Work Unit2</t>
-  </si>
-  <si>
-    <t>Column1</t>
-  </si>
-  <si>
-    <t>Production Line - Assembling</t>
-  </si>
-  <si>
-    <t>Second</t>
-  </si>
-  <si>
     <t>Production Line</t>
   </si>
   <si>
-    <t>Scholarship</t>
+    <t>Final Interview</t>
   </si>
   <si>
     <t>Thrid</t>
@@ -1717,9 +1751,6 @@
   </si>
   <si>
     <t>Data Driven Business</t>
-  </si>
-  <si>
-    <t>Human Resources Development</t>
   </si>
   <si>
     <t>Production Development - Assembly</t>
@@ -1738,9 +1769,6 @@
 Development</t>
   </si>
   <si>
-    <t>Overseas &amp; Service Operation Department</t>
-  </si>
-  <si>
     <t>Digital Enterprise System</t>
   </si>
   <si>
@@ -1757,9 +1785,6 @@
   </si>
   <si>
     <t>Service Operation excellence</t>
-  </si>
-  <si>
-    <t>Overseas service Creativity</t>
   </si>
   <si>
     <t>Overseas Network Management</t>
@@ -1984,7 +2009,7 @@
     <numFmt numFmtId="189" formatCode="B1d\-mmm\-yy"/>
     <numFmt numFmtId="190" formatCode="d/mm/yyyy;@"/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2120,6 +2145,18 @@
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Century Gothic"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Display"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Display"/>
+      <scheme val="major"/>
     </font>
   </fonts>
   <fills count="13">
@@ -2672,7 +2709,7 @@
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="171">
+  <cellXfs count="182">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3135,6 +3172,40 @@
     <xf numFmtId="188" fontId="7" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="12" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="190" fontId="8" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="188" fontId="9" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="9" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="20" fillId="10" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" readingOrder="1"/>
     </xf>
@@ -3170,9 +3241,6 @@
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -4970,24 +5038,9 @@
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2A626EEB-FDFE-42FC-817A-963B6C771FE3}" name="Master" displayName="Master" ref="A1:AI122" totalsRowShown="0" headerRowDxfId="53" dataDxfId="52" tableBorderDxfId="51">
   <autoFilter ref="A1:AI122" xr:uid="{2A626EEB-FDFE-42FC-817A-963B6C771FE3}">
-    <filterColumn colId="0">
+    <filterColumn colId="23">
       <filters>
-        <filter val="2026"/>
-      </filters>
-    </filterColumn>
-    <filterColumn colId="2">
-      <filters>
-        <filter val="SKCN"/>
-      </filters>
-    </filterColumn>
-    <filterColumn colId="25">
-      <filters blank="1">
-        <filter val="Internship"/>
-        <filter val="Jobdb"/>
-        <filter val="JobTopGun"/>
-        <filter val="KOSEN"/>
-        <filter val="Subcontract"/>
-        <filter val="suggestion"/>
+        <filter val="Resign"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -5402,16 +5455,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{817CD080-0396-428F-B39B-215D57916061}">
   <dimension ref="A1:AI122"/>
-  <sheetFormatPr defaultColWidth="14" defaultRowHeight="20.25" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="20.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="9.625" style="78" customWidth="1"/>
     <col min="2" max="2" width="9" style="79" customWidth="1"/>
     <col min="3" max="3" width="9.625" style="79" customWidth="1"/>
     <col min="4" max="4" width="45.375" style="79" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="56.5" style="50" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="58.625" style="50" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="58.625" style="50" customWidth="1"/>
     <col min="7" max="7" width="81.375" style="50" customWidth="1"/>
-    <col min="8" max="8" width="48.125" style="50" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="48.125" style="50" customWidth="1"/>
     <col min="9" max="9" width="12" style="50" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="17.75" style="50" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="15.375" style="50" bestFit="1" customWidth="1"/>
@@ -5421,16 +5474,16 @@
     <col min="15" max="15" width="17.375" style="48" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="13.375" style="50" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="11.125" style="50" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="11.125" style="50" customWidth="1"/>
+    <col min="18" max="18" width="12.875" style="50" customWidth="1"/>
     <col min="19" max="19" width="19.25" style="50" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="21.75" style="50" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="17.625" style="50" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="20.375" style="50" customWidth="1"/>
     <col min="22" max="22" width="20.25" style="116" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="13.875" style="48" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="22.125" style="50" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="14.5" style="80" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="22.75" style="50" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="11.75" style="50" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="38.5" style="50" customWidth="1"/>
     <col min="28" max="28" width="63.375" style="50" customWidth="1"/>
     <col min="29" max="29" width="21.5" style="49" bestFit="1" customWidth="1"/>
     <col min="30" max="30" width="9.375" style="49" bestFit="1" customWidth="1"/>
@@ -5439,10 +5492,10 @@
     <col min="33" max="33" width="17.875" style="49" bestFit="1" customWidth="1"/>
     <col min="34" max="34" width="9" style="50" bestFit="1" customWidth="1"/>
     <col min="35" max="35" width="40.25" style="51" customWidth="1"/>
-    <col min="36" max="16384" width="14" style="52"/>
+    <col min="36" max="16384" width="0" style="52" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" s="91" customFormat="1" ht="20.25" customHeight="1">
+    <row r="1" spans="1:35" s="91" customFormat="1" ht="30" customHeight="1">
       <c r="A1" s="81" t="s">
         <v>0</v>
       </c>
@@ -5549,8 +5602,8 @@
         <v>34</v>
       </c>
     </row>
-    <row r="2" spans="1:35" s="9" customFormat="1" ht="41.45" hidden="1" customHeight="1">
-      <c r="A2" s="19">
+    <row r="2" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
+      <c r="A2" s="46">
         <v>2024</v>
       </c>
       <c r="B2" s="19" t="str">
@@ -5647,8 +5700,8 @@
       <c r="AH2" s="12"/>
       <c r="AI2" s="8"/>
     </row>
-    <row r="3" spans="1:35" s="9" customFormat="1" ht="41.45" hidden="1" customHeight="1">
-      <c r="A3" s="19">
+    <row r="3" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
+      <c r="A3" s="46">
         <v>2024</v>
       </c>
       <c r="B3" s="19" t="str">
@@ -5739,8 +5792,8 @@
       <c r="AH3" s="12"/>
       <c r="AI3" s="8"/>
     </row>
-    <row r="4" spans="1:35" s="9" customFormat="1" ht="41.45" hidden="1" customHeight="1">
-      <c r="A4" s="19">
+    <row r="4" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
+      <c r="A4" s="46">
         <v>2024</v>
       </c>
       <c r="B4" s="19" t="str">
@@ -5827,8 +5880,8 @@
       <c r="AH4" s="12"/>
       <c r="AI4" s="8"/>
     </row>
-    <row r="5" spans="1:35" s="9" customFormat="1" ht="41.45" hidden="1" customHeight="1">
-      <c r="A5" s="19">
+    <row r="5" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
+      <c r="A5" s="46">
         <v>2024</v>
       </c>
       <c r="B5" s="19" t="str">
@@ -5917,8 +5970,8 @@
       <c r="AH5" s="12"/>
       <c r="AI5" s="8"/>
     </row>
-    <row r="6" spans="1:35" s="9" customFormat="1" ht="41.45" hidden="1" customHeight="1">
-      <c r="A6" s="19">
+    <row r="6" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
+      <c r="A6" s="46">
         <v>2024</v>
       </c>
       <c r="B6" s="19" t="str">
@@ -6005,8 +6058,8 @@
       <c r="AH6" s="12"/>
       <c r="AI6" s="8"/>
     </row>
-    <row r="7" spans="1:35" s="9" customFormat="1" ht="41.45" hidden="1" customHeight="1">
-      <c r="A7" s="19">
+    <row r="7" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
+      <c r="A7" s="46">
         <v>2024</v>
       </c>
       <c r="B7" s="19" t="str">
@@ -6093,8 +6146,8 @@
       <c r="AH7" s="12"/>
       <c r="AI7" s="8"/>
     </row>
-    <row r="8" spans="1:35" s="9" customFormat="1" ht="41.45" hidden="1" customHeight="1">
-      <c r="A8" s="19">
+    <row r="8" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
+      <c r="A8" s="46">
         <v>2024</v>
       </c>
       <c r="B8" s="19" t="str">
@@ -6185,8 +6238,8 @@
       <c r="AH8" s="12"/>
       <c r="AI8" s="8"/>
     </row>
-    <row r="9" spans="1:35" s="9" customFormat="1" ht="41.45" hidden="1" customHeight="1">
-      <c r="A9" s="19">
+    <row r="9" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
+      <c r="A9" s="46">
         <v>2024</v>
       </c>
       <c r="B9" s="19" t="str">
@@ -6271,8 +6324,8 @@
       <c r="AH9" s="12"/>
       <c r="AI9" s="8"/>
     </row>
-    <row r="10" spans="1:35" s="9" customFormat="1" ht="41.45" hidden="1" customHeight="1">
-      <c r="A10" s="19">
+    <row r="10" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
+      <c r="A10" s="46">
         <v>2024</v>
       </c>
       <c r="B10" s="19" t="str">
@@ -6359,8 +6412,8 @@
       <c r="AH10" s="12"/>
       <c r="AI10" s="8"/>
     </row>
-    <row r="11" spans="1:35" s="9" customFormat="1" ht="41.45" hidden="1" customHeight="1">
-      <c r="A11" s="19">
+    <row r="11" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
+      <c r="A11" s="46">
         <v>2024</v>
       </c>
       <c r="B11" s="19" t="str">
@@ -6449,8 +6502,8 @@
       <c r="AH11" s="12"/>
       <c r="AI11" s="8"/>
     </row>
-    <row r="12" spans="1:35" s="9" customFormat="1" ht="41.45" hidden="1" customHeight="1">
-      <c r="A12" s="19">
+    <row r="12" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
+      <c r="A12" s="46">
         <v>2024</v>
       </c>
       <c r="B12" s="19" t="str">
@@ -6537,8 +6590,8 @@
       <c r="AH12" s="12"/>
       <c r="AI12" s="8"/>
     </row>
-    <row r="13" spans="1:35" s="9" customFormat="1" ht="41.45" hidden="1" customHeight="1">
-      <c r="A13" s="19">
+    <row r="13" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
+      <c r="A13" s="46">
         <v>2024</v>
       </c>
       <c r="B13" s="19" t="str">
@@ -6627,8 +6680,8 @@
       <c r="AH13" s="12"/>
       <c r="AI13" s="8"/>
     </row>
-    <row r="14" spans="1:35" s="9" customFormat="1" ht="41.45" hidden="1" customHeight="1">
-      <c r="A14" s="19">
+    <row r="14" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
+      <c r="A14" s="46">
         <v>2024</v>
       </c>
       <c r="B14" s="19" t="str">
@@ -6717,8 +6770,8 @@
       <c r="AH14" s="12"/>
       <c r="AI14" s="8"/>
     </row>
-    <row r="15" spans="1:35" s="9" customFormat="1" ht="41.45" hidden="1" customHeight="1">
-      <c r="A15" s="19">
+    <row r="15" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
+      <c r="A15" s="46">
         <v>2024</v>
       </c>
       <c r="B15" s="19" t="str">
@@ -6805,8 +6858,8 @@
       <c r="AH15" s="12"/>
       <c r="AI15" s="8"/>
     </row>
-    <row r="16" spans="1:35" s="9" customFormat="1" ht="41.45" hidden="1" customHeight="1">
-      <c r="A16" s="19">
+    <row r="16" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
+      <c r="A16" s="46">
         <v>2024</v>
       </c>
       <c r="B16" s="19" t="str">
@@ -6895,8 +6948,8 @@
       <c r="AH16" s="12"/>
       <c r="AI16" s="8"/>
     </row>
-    <row r="17" spans="1:35" s="9" customFormat="1" ht="41.45" hidden="1" customHeight="1">
-      <c r="A17" s="19">
+    <row r="17" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
+      <c r="A17" s="46">
         <v>2024</v>
       </c>
       <c r="B17" s="19" t="str">
@@ -6983,8 +7036,8 @@
       <c r="AH17" s="12"/>
       <c r="AI17" s="8"/>
     </row>
-    <row r="18" spans="1:35" s="9" customFormat="1" ht="41.45" hidden="1" customHeight="1">
-      <c r="A18" s="19">
+    <row r="18" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
+      <c r="A18" s="46">
         <v>2024</v>
       </c>
       <c r="B18" s="19" t="str">
@@ -7073,8 +7126,8 @@
       <c r="AH18" s="12"/>
       <c r="AI18" s="8"/>
     </row>
-    <row r="19" spans="1:35" s="9" customFormat="1" ht="41.45" hidden="1" customHeight="1">
-      <c r="A19" s="19">
+    <row r="19" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
+      <c r="A19" s="46">
         <v>2024</v>
       </c>
       <c r="B19" s="19" t="str">
@@ -7163,8 +7216,8 @@
       <c r="AH19" s="12"/>
       <c r="AI19" s="8"/>
     </row>
-    <row r="20" spans="1:35" s="9" customFormat="1" ht="41.45" hidden="1" customHeight="1">
-      <c r="A20" s="19">
+    <row r="20" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
+      <c r="A20" s="46">
         <v>2024</v>
       </c>
       <c r="B20" s="19" t="str">
@@ -7253,7 +7306,7 @@
       <c r="AH20" s="12"/>
       <c r="AI20" s="8"/>
     </row>
-    <row r="21" spans="1:35" s="9" customFormat="1" ht="41.45" hidden="1" customHeight="1">
+    <row r="21" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A21" s="46">
         <v>2025</v>
       </c>
@@ -7345,7 +7398,7 @@
       <c r="AH21" s="12"/>
       <c r="AI21" s="8"/>
     </row>
-    <row r="22" spans="1:35" s="9" customFormat="1" ht="41.45" hidden="1" customHeight="1">
+    <row r="22" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A22" s="46">
         <v>2025</v>
       </c>
@@ -7437,7 +7490,7 @@
       <c r="AH22" s="12"/>
       <c r="AI22" s="8"/>
     </row>
-    <row r="23" spans="1:35" s="9" customFormat="1" ht="41.45" hidden="1" customHeight="1">
+    <row r="23" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A23" s="46">
         <v>2025</v>
       </c>
@@ -7529,7 +7582,7 @@
       <c r="AH23" s="12"/>
       <c r="AI23" s="8"/>
     </row>
-    <row r="24" spans="1:35" s="9" customFormat="1" ht="41.45" hidden="1" customHeight="1">
+    <row r="24" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A24" s="46">
         <v>2025</v>
       </c>
@@ -7621,7 +7674,7 @@
       <c r="AH24" s="12"/>
       <c r="AI24" s="8"/>
     </row>
-    <row r="25" spans="1:35" s="9" customFormat="1" ht="41.45" hidden="1" customHeight="1">
+    <row r="25" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A25" s="46">
         <v>2025</v>
       </c>
@@ -7713,7 +7766,7 @@
       <c r="AH25" s="12"/>
       <c r="AI25" s="8"/>
     </row>
-    <row r="26" spans="1:35" s="9" customFormat="1" ht="41.45" hidden="1" customHeight="1">
+    <row r="26" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A26" s="46">
         <v>2025</v>
       </c>
@@ -7805,7 +7858,7 @@
       <c r="AH26" s="12"/>
       <c r="AI26" s="8"/>
     </row>
-    <row r="27" spans="1:35" s="9" customFormat="1" ht="41.45" hidden="1" customHeight="1">
+    <row r="27" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A27" s="46">
         <v>2025</v>
       </c>
@@ -7897,7 +7950,7 @@
       <c r="AH27" s="12"/>
       <c r="AI27" s="8"/>
     </row>
-    <row r="28" spans="1:35" s="9" customFormat="1" ht="41.45" hidden="1" customHeight="1">
+    <row r="28" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A28" s="46">
         <v>2025</v>
       </c>
@@ -7991,7 +8044,7 @@
       <c r="AH28" s="12"/>
       <c r="AI28" s="8"/>
     </row>
-    <row r="29" spans="1:35" s="9" customFormat="1" ht="41.45" hidden="1" customHeight="1">
+    <row r="29" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A29" s="46">
         <v>2025</v>
       </c>
@@ -8083,7 +8136,7 @@
       <c r="AH29" s="12"/>
       <c r="AI29" s="8"/>
     </row>
-    <row r="30" spans="1:35" s="9" customFormat="1" ht="41.45" hidden="1" customHeight="1">
+    <row r="30" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A30" s="46">
         <v>2025</v>
       </c>
@@ -8177,7 +8230,7 @@
       <c r="AH30" s="12"/>
       <c r="AI30" s="8"/>
     </row>
-    <row r="31" spans="1:35" s="9" customFormat="1" ht="41.45" hidden="1" customHeight="1">
+    <row r="31" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A31" s="46">
         <v>2025</v>
       </c>
@@ -8249,13 +8302,17 @@
       <c r="R31" s="13"/>
       <c r="S31" s="12"/>
       <c r="T31" s="12"/>
-      <c r="U31" s="12"/>
-      <c r="V31" s="12"/>
+      <c r="U31" s="164">
+        <v>16672</v>
+      </c>
+      <c r="V31" s="164" t="s">
+        <v>150</v>
+      </c>
       <c r="W31" s="10">
         <v>45658</v>
       </c>
       <c r="X31" s="12" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Y31" s="12"/>
       <c r="Z31" s="29" t="s">
@@ -8271,7 +8328,7 @@
       <c r="AH31" s="12"/>
       <c r="AI31" s="8"/>
     </row>
-    <row r="32" spans="1:35" s="9" customFormat="1" ht="41.45" hidden="1" customHeight="1">
+    <row r="32" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A32" s="46">
         <v>2025</v>
       </c>
@@ -8283,16 +8340,16 @@
         <v>35</v>
       </c>
       <c r="D32" s="19" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E32" s="13" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F32" s="13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="G32" s="13" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H32" s="13" t="s">
         <v>69</v>
@@ -8365,7 +8422,7 @@
       <c r="AH32" s="12"/>
       <c r="AI32" s="8"/>
     </row>
-    <row r="33" spans="1:35" s="9" customFormat="1" ht="41.45" hidden="1" customHeight="1">
+    <row r="33" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A33" s="46">
         <v>2025</v>
       </c>
@@ -8377,10 +8434,10 @@
         <v>35</v>
       </c>
       <c r="D33" s="19" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F33" s="13" t="s">
         <v>66</v>
@@ -8389,7 +8446,7 @@
         <v>141</v>
       </c>
       <c r="H33" s="13" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="I33" s="12" t="s">
         <v>41</v>
@@ -8457,7 +8514,7 @@
       <c r="AH33" s="12"/>
       <c r="AI33" s="8"/>
     </row>
-    <row r="34" spans="1:35" s="9" customFormat="1" ht="41.45" hidden="1" customHeight="1">
+    <row r="34" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A34" s="46">
         <v>2025</v>
       </c>
@@ -8469,19 +8526,19 @@
         <v>35</v>
       </c>
       <c r="D34" s="19" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E34" s="13" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F34" s="13" t="s">
         <v>90</v>
       </c>
       <c r="G34" s="13" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H34" s="13" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="I34" s="12" t="s">
         <v>51</v>
@@ -8557,7 +8614,7 @@
       <c r="AH34" s="12"/>
       <c r="AI34" s="8"/>
     </row>
-    <row r="35" spans="1:35" s="9" customFormat="1" ht="41.45" hidden="1" customHeight="1">
+    <row r="35" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A35" s="46">
         <v>2025</v>
       </c>
@@ -8569,10 +8626,10 @@
         <v>35</v>
       </c>
       <c r="D35" s="19" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E35" s="13" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F35" s="13" t="s">
         <v>48</v>
@@ -8581,7 +8638,7 @@
         <v>97</v>
       </c>
       <c r="H35" s="13" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I35" s="12" t="s">
         <v>51</v>
@@ -8639,7 +8696,7 @@
       </c>
       <c r="Y35" s="12"/>
       <c r="Z35" s="29" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AA35" s="12"/>
       <c r="AB35" s="12"/>
@@ -8651,7 +8708,7 @@
       <c r="AH35" s="12"/>
       <c r="AI35" s="8"/>
     </row>
-    <row r="36" spans="1:35" s="9" customFormat="1" ht="41.45" hidden="1" customHeight="1">
+    <row r="36" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A36" s="46">
         <v>2025</v>
       </c>
@@ -8663,10 +8720,10 @@
         <v>35</v>
       </c>
       <c r="D36" s="19" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E36" s="13" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F36" s="13" t="s">
         <v>38</v>
@@ -8675,7 +8732,7 @@
         <v>144</v>
       </c>
       <c r="H36" s="13" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="I36" s="12" t="s">
         <v>82</v>
@@ -8745,7 +8802,7 @@
       <c r="AH36" s="12"/>
       <c r="AI36" s="8"/>
     </row>
-    <row r="37" spans="1:35" s="9" customFormat="1" ht="41.45" hidden="1" customHeight="1">
+    <row r="37" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A37" s="46">
         <v>2025</v>
       </c>
@@ -8757,10 +8814,10 @@
         <v>54</v>
       </c>
       <c r="D37" s="19" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E37" s="13" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F37" s="13" t="s">
         <v>54</v>
@@ -8804,7 +8861,7 @@
       Dropdown!$A$2:$A$100
    )
 )</f>
-        <v>364</v>
+        <v>380</v>
       </c>
       <c r="Q37" s="13" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -8829,7 +8886,7 @@
       <c r="AH37" s="12"/>
       <c r="AI37" s="8"/>
     </row>
-    <row r="38" spans="1:35" s="9" customFormat="1" ht="41.45" hidden="1" customHeight="1">
+    <row r="38" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A38" s="46">
         <v>2025</v>
       </c>
@@ -8841,19 +8898,19 @@
         <v>45</v>
       </c>
       <c r="D38" s="19" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E38" s="13" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F38" s="13" t="s">
         <v>111</v>
       </c>
       <c r="G38" s="13" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H38" s="13" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="I38" s="12" t="s">
         <v>51</v>
@@ -8921,7 +8978,7 @@
       <c r="AH38" s="12"/>
       <c r="AI38" s="8"/>
     </row>
-    <row r="39" spans="1:35" s="9" customFormat="1" ht="41.45" hidden="1" customHeight="1">
+    <row r="39" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A39" s="46">
         <v>2025</v>
       </c>
@@ -8936,13 +8993,13 @@
         <v>46</v>
       </c>
       <c r="E39" s="13" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F39" s="13" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="G39" s="13" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H39" s="13" t="s">
         <v>81</v>
@@ -8999,7 +9056,7 @@
       <c r="X39" s="12"/>
       <c r="Y39" s="12"/>
       <c r="Z39" s="28" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AA39" s="12"/>
       <c r="AB39" s="12"/>
@@ -9011,7 +9068,7 @@
       <c r="AH39" s="12"/>
       <c r="AI39" s="8"/>
     </row>
-    <row r="40" spans="1:35" s="9" customFormat="1" ht="41.45" hidden="1" customHeight="1">
+    <row r="40" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A40" s="46">
         <v>2025</v>
       </c>
@@ -9023,19 +9080,19 @@
         <v>45</v>
       </c>
       <c r="D40" s="19" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E40" s="13" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F40" s="13" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="G40" s="13" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H40" s="13" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="I40" s="12" t="s">
         <v>82</v>
@@ -9101,7 +9158,7 @@
       <c r="AH40" s="12"/>
       <c r="AI40" s="8"/>
     </row>
-    <row r="41" spans="1:35" s="9" customFormat="1" ht="41.45" hidden="1" customHeight="1">
+    <row r="41" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A41" s="46">
         <v>2025</v>
       </c>
@@ -9119,13 +9176,13 @@
         <v>119</v>
       </c>
       <c r="F41" s="13" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="G41" s="13" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H41" s="13" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="I41" s="12" t="s">
         <v>41</v>
@@ -9181,7 +9238,7 @@
       <c r="X41" s="12"/>
       <c r="Y41" s="12"/>
       <c r="Z41" s="28" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AA41" s="12"/>
       <c r="AB41" s="12"/>
@@ -9193,7 +9250,7 @@
       <c r="AH41" s="12"/>
       <c r="AI41" s="8"/>
     </row>
-    <row r="42" spans="1:35" s="9" customFormat="1" ht="41.45" hidden="1" customHeight="1">
+    <row r="42" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A42" s="46">
         <v>2025</v>
       </c>
@@ -9205,19 +9262,19 @@
         <v>45</v>
       </c>
       <c r="D42" s="19" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E42" s="13" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F42" s="13" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="G42" s="13" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H42" s="13" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I42" s="12" t="s">
         <v>41</v>
@@ -9285,7 +9342,7 @@
       <c r="AH42" s="12"/>
       <c r="AI42" s="8"/>
     </row>
-    <row r="43" spans="1:35" s="9" customFormat="1" ht="41.45" hidden="1" customHeight="1">
+    <row r="43" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A43" s="46">
         <v>2025</v>
       </c>
@@ -9297,10 +9354,10 @@
         <v>35</v>
       </c>
       <c r="D43" s="19" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E43" s="13" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F43" s="13" t="s">
         <v>66</v>
@@ -9361,7 +9418,7 @@
       <c r="V43" s="12"/>
       <c r="W43" s="10"/>
       <c r="X43" s="12" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Y43" s="12"/>
       <c r="Z43" s="28" t="s">
@@ -9377,7 +9434,7 @@
       <c r="AH43" s="12"/>
       <c r="AI43" s="8"/>
     </row>
-    <row r="44" spans="1:35" s="9" customFormat="1" ht="41.45" hidden="1" customHeight="1">
+    <row r="44" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A44" s="46">
         <v>2025</v>
       </c>
@@ -9389,19 +9446,19 @@
         <v>35</v>
       </c>
       <c r="D44" s="19" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E44" s="13" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F44" s="13" t="s">
         <v>111</v>
       </c>
       <c r="G44" s="13" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H44" s="13" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="I44" s="12" t="s">
         <v>51</v>
@@ -9469,7 +9526,7 @@
       <c r="AH44" s="12"/>
       <c r="AI44" s="8"/>
     </row>
-    <row r="45" spans="1:35" s="9" customFormat="1" ht="41.45" hidden="1" customHeight="1">
+    <row r="45" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A45" s="46">
         <v>2025</v>
       </c>
@@ -9484,14 +9541,14 @@
         <v>46</v>
       </c>
       <c r="E45" s="13" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F45" s="13" t="s">
         <v>87</v>
       </c>
       <c r="G45" s="13"/>
       <c r="H45" s="13" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="I45" s="12" t="s">
         <v>41</v>
@@ -9561,7 +9618,7 @@
       <c r="AH45" s="12"/>
       <c r="AI45" s="8"/>
     </row>
-    <row r="46" spans="1:35" s="9" customFormat="1" ht="41.45" hidden="1" customHeight="1">
+    <row r="46" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A46" s="46">
         <v>2025</v>
       </c>
@@ -9573,19 +9630,19 @@
         <v>35</v>
       </c>
       <c r="D46" s="19" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E46" s="13" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F46" s="13" t="s">
         <v>87</v>
       </c>
       <c r="G46" s="13" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H46" s="13" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="I46" s="12" t="s">
         <v>41</v>
@@ -9653,7 +9710,7 @@
       <c r="AH46" s="12"/>
       <c r="AI46" s="8"/>
     </row>
-    <row r="47" spans="1:35" s="9" customFormat="1" ht="41.45" hidden="1" customHeight="1">
+    <row r="47" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A47" s="46">
         <v>2025</v>
       </c>
@@ -9665,19 +9722,19 @@
         <v>35</v>
       </c>
       <c r="D47" s="19" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E47" s="13" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F47" s="13" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="G47" s="13" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H47" s="13" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="I47" s="12" t="s">
         <v>82</v>
@@ -9741,7 +9798,7 @@
       <c r="AH47" s="12"/>
       <c r="AI47" s="8"/>
     </row>
-    <row r="48" spans="1:35" s="9" customFormat="1" ht="41.45" hidden="1" customHeight="1">
+    <row r="48" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A48" s="46">
         <v>2025</v>
       </c>
@@ -9753,19 +9810,19 @@
         <v>35</v>
       </c>
       <c r="D48" s="19" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E48" s="13" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F48" s="13" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="G48" s="13" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H48" s="13" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="I48" s="12" t="s">
         <v>82</v>
@@ -9819,11 +9876,11 @@
         <v>46143</v>
       </c>
       <c r="X48" s="12" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Y48" s="12"/>
       <c r="Z48" s="28" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AA48" s="12"/>
       <c r="AB48" s="12"/>
@@ -9835,7 +9892,7 @@
       <c r="AH48" s="12"/>
       <c r="AI48" s="8"/>
     </row>
-    <row r="49" spans="1:35" s="9" customFormat="1" ht="41.45" hidden="1" customHeight="1">
+    <row r="49" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A49" s="46">
         <v>2025</v>
       </c>
@@ -9847,10 +9904,10 @@
         <v>35</v>
       </c>
       <c r="D49" s="19" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E49" s="13" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F49" s="13" t="s">
         <v>75</v>
@@ -9859,7 +9916,7 @@
         <v>76</v>
       </c>
       <c r="H49" s="13" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="I49" s="12" t="s">
         <v>41</v>
@@ -9929,7 +9986,7 @@
       <c r="AH49" s="12"/>
       <c r="AI49" s="8"/>
     </row>
-    <row r="50" spans="1:35" s="9" customFormat="1" ht="41.45" hidden="1" customHeight="1">
+    <row r="50" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A50" s="46">
         <v>2025</v>
       </c>
@@ -9941,19 +9998,19 @@
         <v>35</v>
       </c>
       <c r="D50" s="19" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E50" s="13" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F50" s="13" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="G50" s="13" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H50" s="13" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="I50" s="12" t="s">
         <v>41</v>
@@ -10021,7 +10078,7 @@
       <c r="AH50" s="12"/>
       <c r="AI50" s="8"/>
     </row>
-    <row r="51" spans="1:35" s="9" customFormat="1" ht="41.45" hidden="1" customHeight="1">
+    <row r="51" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A51" s="46">
         <v>2025</v>
       </c>
@@ -10033,19 +10090,19 @@
         <v>35</v>
       </c>
       <c r="D51" s="19" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E51" s="13" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F51" s="13" t="s">
         <v>38</v>
       </c>
       <c r="G51" s="13" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H51" s="13" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I51" s="12" t="s">
         <v>41</v>
@@ -10113,7 +10170,7 @@
       <c r="AH51" s="12"/>
       <c r="AI51" s="8"/>
     </row>
-    <row r="52" spans="1:35" s="9" customFormat="1" ht="41.45" hidden="1" customHeight="1">
+    <row r="52" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A52" s="46">
         <v>2025</v>
       </c>
@@ -10125,10 +10182,10 @@
         <v>35</v>
       </c>
       <c r="D52" s="19" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E52" s="13" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F52" s="13" t="s">
         <v>61</v>
@@ -10137,7 +10194,7 @@
         <v>94</v>
       </c>
       <c r="H52" s="13" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="I52" s="12" t="s">
         <v>82</v>
@@ -10205,7 +10262,7 @@
       <c r="AH52" s="12"/>
       <c r="AI52" s="8"/>
     </row>
-    <row r="53" spans="1:35" s="9" customFormat="1" ht="41.45" hidden="1" customHeight="1">
+    <row r="53" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A53" s="46">
         <v>2025</v>
       </c>
@@ -10217,19 +10274,19 @@
         <v>35</v>
       </c>
       <c r="D53" s="19" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E53" s="13" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F53" s="13" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="G53" s="13" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H53" s="13" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="I53" s="12" t="s">
         <v>82</v>
@@ -10293,7 +10350,7 @@
       <c r="AH53" s="12"/>
       <c r="AI53" s="8"/>
     </row>
-    <row r="54" spans="1:35" s="9" customFormat="1" ht="41.45" hidden="1" customHeight="1">
+    <row r="54" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A54" s="46">
         <v>2025</v>
       </c>
@@ -10317,7 +10374,7 @@
         <v>129</v>
       </c>
       <c r="H54" s="13" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I54" s="12" t="s">
         <v>41</v>
@@ -10371,7 +10428,7 @@
       <c r="X54" s="12"/>
       <c r="Y54" s="12"/>
       <c r="Z54" s="29" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AA54" s="12"/>
       <c r="AB54" s="12"/>
@@ -10383,7 +10440,7 @@
       <c r="AH54" s="12"/>
       <c r="AI54" s="8"/>
     </row>
-    <row r="55" spans="1:35" s="9" customFormat="1" ht="41.45" hidden="1" customHeight="1">
+    <row r="55" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A55" s="46">
         <v>2025</v>
       </c>
@@ -10404,10 +10461,10 @@
         <v>128</v>
       </c>
       <c r="G55" s="13" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H55" s="13" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="I55" s="12" t="s">
         <v>41</v>
@@ -10461,7 +10518,7 @@
       <c r="X55" s="12"/>
       <c r="Y55" s="12"/>
       <c r="Z55" s="29" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AA55" s="12"/>
       <c r="AB55" s="12"/>
@@ -10473,7 +10530,7 @@
       <c r="AH55" s="12"/>
       <c r="AI55" s="8"/>
     </row>
-    <row r="56" spans="1:35" s="9" customFormat="1" ht="41.45" hidden="1" customHeight="1">
+    <row r="56" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A56" s="46">
         <v>2025</v>
       </c>
@@ -10485,7 +10542,7 @@
         <v>35</v>
       </c>
       <c r="D56" s="19" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E56" s="13" t="s">
         <v>140</v>
@@ -10549,7 +10606,7 @@
       </c>
       <c r="Y56" s="12"/>
       <c r="Z56" s="29" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AA56" s="12"/>
       <c r="AB56" s="12"/>
@@ -10561,7 +10618,7 @@
       <c r="AH56" s="12"/>
       <c r="AI56" s="8"/>
     </row>
-    <row r="57" spans="1:35" s="9" customFormat="1" ht="41.45" hidden="1" customHeight="1">
+    <row r="57" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A57" s="46">
         <v>2025</v>
       </c>
@@ -10573,10 +10630,10 @@
         <v>35</v>
       </c>
       <c r="D57" s="19" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E57" s="13" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F57" s="13" t="s">
         <v>79</v>
@@ -10585,7 +10642,7 @@
         <v>80</v>
       </c>
       <c r="H57" s="13" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="I57" s="12" t="s">
         <v>82</v>
@@ -10649,7 +10706,7 @@
       <c r="AH57" s="12"/>
       <c r="AI57" s="8"/>
     </row>
-    <row r="58" spans="1:35" s="9" customFormat="1" ht="41.45" hidden="1" customHeight="1">
+    <row r="58" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A58" s="46">
         <v>2025</v>
       </c>
@@ -10661,19 +10718,19 @@
         <v>35</v>
       </c>
       <c r="D58" s="19" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E58" s="13" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F58" s="13" t="s">
         <v>79</v>
       </c>
       <c r="G58" s="13" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H58" s="13" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I58" s="12" t="s">
         <v>82</v>
@@ -10725,11 +10782,11 @@
       <c r="V58" s="12"/>
       <c r="W58" s="10"/>
       <c r="X58" s="12" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Y58" s="12"/>
       <c r="Z58" s="30" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AA58" s="12"/>
       <c r="AB58" s="12"/>
@@ -10741,7 +10798,7 @@
       <c r="AH58" s="12"/>
       <c r="AI58" s="8"/>
     </row>
-    <row r="59" spans="1:35" s="9" customFormat="1" ht="41.45" hidden="1" customHeight="1">
+    <row r="59" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A59" s="46">
         <v>2025</v>
       </c>
@@ -10765,7 +10822,7 @@
         <v>112</v>
       </c>
       <c r="H59" s="13" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="I59" s="12" t="s">
         <v>51</v>
@@ -10823,7 +10880,7 @@
       </c>
       <c r="Y59" s="8"/>
       <c r="Z59" s="31" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AA59" s="23"/>
       <c r="AB59" s="12"/>
@@ -10835,7 +10892,7 @@
       <c r="AH59" s="12"/>
       <c r="AI59" s="8"/>
     </row>
-    <row r="60" spans="1:35" s="9" customFormat="1" ht="41.45" hidden="1" customHeight="1">
+    <row r="60" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A60" s="46">
         <v>2025</v>
       </c>
@@ -10847,10 +10904,10 @@
         <v>35</v>
       </c>
       <c r="D60" s="19" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E60" s="13" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F60" s="13" t="s">
         <v>87</v>
@@ -10859,7 +10916,7 @@
         <v>99</v>
       </c>
       <c r="H60" s="13" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="I60" s="12" t="s">
         <v>82</v>
@@ -10917,7 +10974,7 @@
       </c>
       <c r="Y60" s="8"/>
       <c r="Z60" s="31" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AA60" s="23"/>
       <c r="AB60" s="12"/>
@@ -10929,7 +10986,7 @@
       <c r="AH60" s="12"/>
       <c r="AI60" s="8"/>
     </row>
-    <row r="61" spans="1:35" s="9" customFormat="1" ht="41.45" hidden="1" customHeight="1">
+    <row r="61" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A61" s="46">
         <v>2025</v>
       </c>
@@ -10944,16 +11001,16 @@
         <v>46</v>
       </c>
       <c r="E61" s="13" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F61" s="13" t="s">
         <v>128</v>
       </c>
       <c r="G61" s="13" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H61" s="13" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="I61" s="12" t="s">
         <v>41</v>
@@ -11019,7 +11076,7 @@
       <c r="AH61" s="12"/>
       <c r="AI61" s="8"/>
     </row>
-    <row r="62" spans="1:35" s="9" customFormat="1" ht="41.45" hidden="1" customHeight="1">
+    <row r="62" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A62" s="46">
         <v>2025</v>
       </c>
@@ -11043,7 +11100,7 @@
         <v>121</v>
       </c>
       <c r="H62" s="13" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="I62" s="12" t="s">
         <v>41</v>
@@ -11109,7 +11166,7 @@
       <c r="AH62" s="12"/>
       <c r="AI62" s="8"/>
     </row>
-    <row r="63" spans="1:35" s="9" customFormat="1" ht="41.45" hidden="1" customHeight="1">
+    <row r="63" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A63" s="46">
         <v>2025</v>
       </c>
@@ -11121,19 +11178,19 @@
         <v>45</v>
       </c>
       <c r="D63" s="19" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E63" s="13" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F63" s="13" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="G63" s="13" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="H63" s="13" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="I63" s="12" t="s">
         <v>41</v>
@@ -11199,7 +11256,7 @@
       <c r="AH63" s="12"/>
       <c r="AI63" s="8"/>
     </row>
-    <row r="64" spans="1:35" s="9" customFormat="1" ht="41.45" hidden="1" customHeight="1">
+    <row r="64" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A64" s="46">
         <v>2025</v>
       </c>
@@ -11211,19 +11268,19 @@
         <v>35</v>
       </c>
       <c r="D64" s="19" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E64" s="13" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F64" s="13" t="s">
         <v>87</v>
       </c>
       <c r="G64" s="13" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H64" s="13" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="I64" s="12" t="s">
         <v>41</v>
@@ -11293,7 +11350,7 @@
       <c r="AH64" s="12"/>
       <c r="AI64" s="8"/>
     </row>
-    <row r="65" spans="1:35" s="9" customFormat="1" ht="41.45" hidden="1" customHeight="1">
+    <row r="65" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A65" s="46">
         <v>2025</v>
       </c>
@@ -11305,19 +11362,19 @@
         <v>35</v>
       </c>
       <c r="D65" s="19" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E65" s="13" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F65" s="13" t="s">
         <v>61</v>
       </c>
       <c r="G65" s="13" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H65" s="13" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="I65" s="12" t="s">
         <v>41</v>
@@ -11387,7 +11444,7 @@
       <c r="AH65" s="12"/>
       <c r="AI65" s="8"/>
     </row>
-    <row r="66" spans="1:35" s="9" customFormat="1" ht="41.45" hidden="1" customHeight="1">
+    <row r="66" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A66" s="46">
         <v>2025</v>
       </c>
@@ -11399,10 +11456,10 @@
         <v>35</v>
       </c>
       <c r="D66" s="19" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E66" s="13" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F66" s="13" t="s">
         <v>48</v>
@@ -11411,7 +11468,7 @@
         <v>97</v>
       </c>
       <c r="H66" s="13" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="I66" s="12" t="s">
         <v>51</v>
@@ -11489,7 +11546,7 @@
       <c r="AH66" s="12"/>
       <c r="AI66" s="8"/>
     </row>
-    <row r="67" spans="1:35" s="9" customFormat="1" ht="41.45" hidden="1" customHeight="1">
+    <row r="67" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A67" s="46">
         <v>2025</v>
       </c>
@@ -11501,10 +11558,10 @@
         <v>35</v>
       </c>
       <c r="D67" s="19" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="E67" s="13" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F67" s="13" t="s">
         <v>87</v>
@@ -11513,7 +11570,7 @@
         <v>99</v>
       </c>
       <c r="H67" s="13" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="I67" s="12" t="s">
         <v>82</v>
@@ -11581,7 +11638,7 @@
       <c r="AH67" s="12"/>
       <c r="AI67" s="8"/>
     </row>
-    <row r="68" spans="1:35" s="9" customFormat="1" ht="41.45" hidden="1" customHeight="1">
+    <row r="68" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A68" s="46">
         <v>2025</v>
       </c>
@@ -11593,10 +11650,10 @@
         <v>35</v>
       </c>
       <c r="D68" s="19" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E68" s="13" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F68" s="13" t="s">
         <v>61</v>
@@ -11605,7 +11662,7 @@
         <v>94</v>
       </c>
       <c r="H68" s="13" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="I68" s="12" t="s">
         <v>82</v>
@@ -11673,7 +11730,7 @@
       <c r="AH68" s="12"/>
       <c r="AI68" s="8"/>
     </row>
-    <row r="69" spans="1:35" s="9" customFormat="1" ht="41.45" hidden="1" customHeight="1">
+    <row r="69" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A69" s="46">
         <v>2025</v>
       </c>
@@ -11685,19 +11742,19 @@
         <v>45</v>
       </c>
       <c r="D69" s="19" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E69" s="13" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F69" s="13" t="s">
         <v>111</v>
       </c>
       <c r="G69" s="13" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H69" s="13" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="I69" s="12" t="s">
         <v>51</v>
@@ -11765,7 +11822,7 @@
       <c r="AH69" s="12"/>
       <c r="AI69" s="8"/>
     </row>
-    <row r="70" spans="1:35" s="9" customFormat="1" ht="41.45" hidden="1" customHeight="1">
+    <row r="70" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A70" s="46">
         <v>2025</v>
       </c>
@@ -11777,19 +11834,19 @@
         <v>45</v>
       </c>
       <c r="D70" s="19" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E70" s="13" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F70" s="13" t="s">
         <v>111</v>
       </c>
       <c r="G70" s="13" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H70" s="13" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="I70" s="12" t="s">
         <v>51</v>
@@ -11826,7 +11883,7 @@
       Dropdown!$A$2:$A$100
    )
 )</f>
-        <v>306</v>
+        <v>322</v>
       </c>
       <c r="Q70" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -11838,12 +11895,12 @@
       <c r="U70" s="12"/>
       <c r="V70" s="12"/>
       <c r="W70" s="10" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="X70" s="12"/>
       <c r="Y70" s="8"/>
       <c r="Z70" s="31" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AA70" s="23"/>
       <c r="AB70" s="12"/>
@@ -11855,7 +11912,7 @@
       <c r="AH70" s="12"/>
       <c r="AI70" s="8"/>
     </row>
-    <row r="71" spans="1:35" s="9" customFormat="1" ht="41.45" hidden="1" customHeight="1">
+    <row r="71" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A71" s="46">
         <v>2025</v>
       </c>
@@ -11867,19 +11924,19 @@
         <v>35</v>
       </c>
       <c r="D71" s="19" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E71" s="13" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="F71" s="13" t="s">
         <v>90</v>
       </c>
       <c r="G71" s="13" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H71" s="13" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="I71" s="12" t="s">
         <v>51</v>
@@ -11933,7 +11990,7 @@
         <v>45977</v>
       </c>
       <c r="X71" s="12" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Y71" s="8"/>
       <c r="Z71" s="12" t="s">
@@ -11949,7 +12006,7 @@
       <c r="AH71" s="12"/>
       <c r="AI71" s="8"/>
     </row>
-    <row r="72" spans="1:35" s="9" customFormat="1" ht="41.45" hidden="1" customHeight="1">
+    <row r="72" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A72" s="46">
         <v>2025</v>
       </c>
@@ -11964,7 +12021,7 @@
         <v>46</v>
       </c>
       <c r="E72" s="13" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F72" s="13" t="s">
         <v>61</v>
@@ -11973,7 +12030,7 @@
         <v>104</v>
       </c>
       <c r="H72" s="13" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="I72" s="12" t="s">
         <v>41</v>
@@ -12027,11 +12084,11 @@
         <v>45946</v>
       </c>
       <c r="X72" s="12" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Y72" s="12"/>
       <c r="Z72" s="32" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AA72" s="12"/>
       <c r="AB72" s="12"/>
@@ -12043,7 +12100,7 @@
       <c r="AH72" s="12"/>
       <c r="AI72" s="8"/>
     </row>
-    <row r="73" spans="1:35" s="9" customFormat="1" ht="41.45" hidden="1" customHeight="1">
+    <row r="73" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A73" s="46">
         <v>2025</v>
       </c>
@@ -12055,19 +12112,19 @@
         <v>35</v>
       </c>
       <c r="D73" s="19" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E73" s="13" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F73" s="13" t="s">
         <v>38</v>
       </c>
       <c r="G73" s="13" t="s">
+        <v>258</v>
+      </c>
+      <c r="H73" s="13" t="s">
         <v>257</v>
-      </c>
-      <c r="H73" s="13" t="s">
-        <v>256</v>
       </c>
       <c r="I73" s="12" t="s">
         <v>51</v>
@@ -12137,7 +12194,7 @@
       <c r="AH73" s="12"/>
       <c r="AI73" s="8"/>
     </row>
-    <row r="74" spans="1:35" s="9" customFormat="1" ht="41.45" hidden="1" customHeight="1">
+    <row r="74" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A74" s="46">
         <v>2025</v>
       </c>
@@ -12149,10 +12206,10 @@
         <v>35</v>
       </c>
       <c r="D74" s="19" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E74" s="13" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F74" s="13" t="s">
         <v>87</v>
@@ -12161,7 +12218,7 @@
         <v>106</v>
       </c>
       <c r="H74" s="13" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="I74" s="12" t="s">
         <v>41</v>
@@ -12231,7 +12288,7 @@
       <c r="AH74" s="12"/>
       <c r="AI74" s="8"/>
     </row>
-    <row r="75" spans="1:35" s="9" customFormat="1" ht="41.45" hidden="1" customHeight="1">
+    <row r="75" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A75" s="46">
         <v>2025</v>
       </c>
@@ -12305,7 +12362,7 @@
       <c r="T75" s="12"/>
       <c r="U75" s="12"/>
       <c r="V75" s="12" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="W75" s="41">
         <v>45977</v>
@@ -12315,7 +12372,7 @@
       </c>
       <c r="Y75" s="12"/>
       <c r="Z75" s="35" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AA75" s="12"/>
       <c r="AB75" s="12"/>
@@ -12327,7 +12384,7 @@
       <c r="AH75" s="12"/>
       <c r="AI75" s="8"/>
     </row>
-    <row r="76" spans="1:35" s="9" customFormat="1" ht="41.45" hidden="1" customHeight="1">
+    <row r="76" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A76" s="46">
         <v>2025</v>
       </c>
@@ -12339,10 +12396,10 @@
         <v>35</v>
       </c>
       <c r="D76" s="19" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E76" s="16" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F76" s="17" t="s">
         <v>61</v>
@@ -12351,7 +12408,7 @@
         <v>94</v>
       </c>
       <c r="H76" s="17" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="I76" s="12" t="s">
         <v>51</v>
@@ -12399,8 +12456,8 @@
       <c r="R76" s="13"/>
       <c r="S76" s="17"/>
       <c r="T76" s="17"/>
-      <c r="U76" s="17"/>
-      <c r="V76" s="17"/>
+      <c r="U76" s="162"/>
+      <c r="V76" s="162"/>
       <c r="W76" s="26">
         <v>45931</v>
       </c>
@@ -12409,7 +12466,7 @@
       </c>
       <c r="Y76" s="22"/>
       <c r="Z76" s="31" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AA76" s="24"/>
       <c r="AB76" s="17"/>
@@ -12421,7 +12478,7 @@
       <c r="AH76" s="17"/>
       <c r="AI76" s="8"/>
     </row>
-    <row r="77" spans="1:35" s="9" customFormat="1" ht="41.45" hidden="1" customHeight="1">
+    <row r="77" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A77" s="46">
         <v>2025</v>
       </c>
@@ -12433,19 +12490,19 @@
         <v>35</v>
       </c>
       <c r="D77" s="19" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E77" s="16" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F77" s="17" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="G77" s="17" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H77" s="17" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="I77" s="17" t="s">
         <v>41</v>
@@ -12492,18 +12549,22 @@
       </c>
       <c r="R77" s="13"/>
       <c r="S77" s="17"/>
-      <c r="T77" s="17"/>
-      <c r="U77" s="17"/>
-      <c r="V77" s="17"/>
-      <c r="W77" s="26">
+      <c r="T77" s="22"/>
+      <c r="U77" s="167">
+        <v>16715</v>
+      </c>
+      <c r="V77" s="165" t="s">
+        <v>266</v>
+      </c>
+      <c r="W77" s="161">
         <v>45885</v>
       </c>
       <c r="X77" s="17" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Y77" s="22"/>
       <c r="Z77" s="31" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AA77" s="24"/>
       <c r="AB77" s="17"/>
@@ -12515,7 +12576,7 @@
       <c r="AH77" s="17"/>
       <c r="AI77" s="8"/>
     </row>
-    <row r="78" spans="1:35" s="11" customFormat="1" ht="41.45" hidden="1" customHeight="1">
+    <row r="78" spans="1:35" s="11" customFormat="1" ht="30" customHeight="1">
       <c r="A78" s="46">
         <v>2025</v>
       </c>
@@ -12527,19 +12588,19 @@
         <v>35</v>
       </c>
       <c r="D78" s="20" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="E78" s="12" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="F78" s="12" t="s">
         <v>48</v>
       </c>
       <c r="G78" s="12" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="H78" s="12" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="I78" s="12" t="s">
         <v>51</v>
@@ -12587,8 +12648,8 @@
       <c r="R78" s="13"/>
       <c r="S78" s="12"/>
       <c r="T78" s="12"/>
-      <c r="U78" s="12"/>
-      <c r="V78" s="12"/>
+      <c r="U78" s="163"/>
+      <c r="V78" s="163"/>
       <c r="W78" s="10">
         <v>45854</v>
       </c>
@@ -12597,7 +12658,7 @@
       </c>
       <c r="Y78" s="37"/>
       <c r="Z78" s="31" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AA78" s="23"/>
       <c r="AB78" s="12"/>
@@ -12615,7 +12676,7 @@
       <c r="AH78" s="12"/>
       <c r="AI78" s="8"/>
     </row>
-    <row r="79" spans="1:35" s="11" customFormat="1" ht="41.45" hidden="1" customHeight="1">
+    <row r="79" spans="1:35" s="11" customFormat="1" ht="30" customHeight="1">
       <c r="A79" s="46">
         <v>2025</v>
       </c>
@@ -12627,10 +12688,10 @@
         <v>35</v>
       </c>
       <c r="D79" s="20" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="E79" s="12" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="F79" s="12" t="s">
         <v>48</v>
@@ -12639,7 +12700,7 @@
         <v>97</v>
       </c>
       <c r="H79" s="12" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I79" s="12" t="s">
         <v>51</v>
@@ -12685,15 +12746,19 @@
       <c r="R79" s="13"/>
       <c r="S79" s="12"/>
       <c r="T79" s="12"/>
-      <c r="U79" s="12"/>
-      <c r="V79" s="12"/>
+      <c r="U79" s="164">
+        <v>16697</v>
+      </c>
+      <c r="V79" s="164" t="s">
+        <v>271</v>
+      </c>
       <c r="W79" s="10"/>
       <c r="X79" s="12" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Y79" s="37"/>
       <c r="Z79" s="31" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AA79" s="23"/>
       <c r="AB79" s="12"/>
@@ -12705,7 +12770,7 @@
       <c r="AH79" s="12"/>
       <c r="AI79" s="8"/>
     </row>
-    <row r="80" spans="1:35" s="11" customFormat="1" ht="41.45" hidden="1" customHeight="1">
+    <row r="80" spans="1:35" s="11" customFormat="1" ht="30" customHeight="1">
       <c r="A80" s="46">
         <v>2025</v>
       </c>
@@ -12720,16 +12785,16 @@
         <v>46</v>
       </c>
       <c r="E80" s="18" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F80" s="18" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="G80" s="18" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H80" s="18" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="I80" s="12" t="s">
         <v>41</v>
@@ -12785,7 +12850,7 @@
       <c r="X80" s="17"/>
       <c r="Y80" s="22"/>
       <c r="Z80" s="31" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AA80" s="24"/>
       <c r="AB80" s="17"/>
@@ -12797,7 +12862,7 @@
       <c r="AH80" s="17"/>
       <c r="AI80" s="8"/>
     </row>
-    <row r="81" spans="1:35" s="11" customFormat="1" ht="41.45" hidden="1" customHeight="1">
+    <row r="81" spans="1:35" s="11" customFormat="1" ht="30" customHeight="1">
       <c r="A81" s="46">
         <v>2025</v>
       </c>
@@ -12809,19 +12874,19 @@
         <v>35</v>
       </c>
       <c r="D81" s="19" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E81" s="13" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F81" s="13" t="s">
         <v>111</v>
       </c>
       <c r="G81" s="13" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H81" s="13" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="I81" s="12" t="s">
         <v>51</v>
@@ -12879,7 +12944,7 @@
       </c>
       <c r="Y81" s="12"/>
       <c r="Z81" s="35" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AA81" s="12"/>
       <c r="AB81" s="12"/>
@@ -12891,7 +12956,7 @@
       <c r="AH81" s="12"/>
       <c r="AI81" s="8"/>
     </row>
-    <row r="82" spans="1:35" s="11" customFormat="1" ht="41.45" hidden="1" customHeight="1">
+    <row r="82" spans="1:35" s="11" customFormat="1" ht="30" customHeight="1">
       <c r="A82" s="46">
         <v>2025</v>
       </c>
@@ -12903,19 +12968,19 @@
         <v>35</v>
       </c>
       <c r="D82" s="21" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="E82" s="18" t="s">
         <v>83</v>
       </c>
       <c r="F82" s="18" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="G82" s="18" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="H82" s="18" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="I82" s="17" t="s">
         <v>41</v>
@@ -12979,7 +13044,7 @@
       <c r="AH82" s="17"/>
       <c r="AI82" s="8"/>
     </row>
-    <row r="83" spans="1:35" s="11" customFormat="1" ht="41.45" hidden="1" customHeight="1">
+    <row r="83" spans="1:35" s="11" customFormat="1" ht="30" customHeight="1">
       <c r="A83" s="46">
         <v>2025</v>
       </c>
@@ -12991,10 +13056,10 @@
         <v>35</v>
       </c>
       <c r="D83" s="21" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="E83" s="18" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="F83" s="18" t="s">
         <v>90</v>
@@ -13003,7 +13068,7 @@
         <v>91</v>
       </c>
       <c r="H83" s="18" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="I83" s="17" t="s">
         <v>41</v>
@@ -13061,7 +13126,7 @@
       </c>
       <c r="Y83" s="22"/>
       <c r="Z83" s="31" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AA83" s="24"/>
       <c r="AB83" s="17"/>
@@ -13073,7 +13138,7 @@
       <c r="AH83" s="17"/>
       <c r="AI83" s="8"/>
     </row>
-    <row r="84" spans="1:35" s="11" customFormat="1" ht="41.45" hidden="1" customHeight="1">
+    <row r="84" spans="1:35" s="11" customFormat="1" ht="30" customHeight="1">
       <c r="A84" s="46">
         <v>2025</v>
       </c>
@@ -13085,10 +13150,10 @@
         <v>35</v>
       </c>
       <c r="D84" s="19" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="E84" s="16" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="F84" s="17" t="s">
         <v>61</v>
@@ -13097,7 +13162,7 @@
         <v>62</v>
       </c>
       <c r="H84" s="17" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="I84" s="12" t="s">
         <v>51</v>
@@ -13167,7 +13232,7 @@
       <c r="AH84" s="17"/>
       <c r="AI84" s="8"/>
     </row>
-    <row r="85" spans="1:35" s="11" customFormat="1" ht="41.45" hidden="1" customHeight="1">
+    <row r="85" spans="1:35" s="11" customFormat="1" ht="30" customHeight="1">
       <c r="A85" s="46">
         <v>2025</v>
       </c>
@@ -13179,10 +13244,10 @@
         <v>35</v>
       </c>
       <c r="D85" s="19" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E85" s="16" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F85" s="17" t="s">
         <v>87</v>
@@ -13191,7 +13256,7 @@
         <v>106</v>
       </c>
       <c r="H85" s="17" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="I85" s="17" t="s">
         <v>41</v>
@@ -13249,7 +13314,7 @@
       </c>
       <c r="Y85" s="17"/>
       <c r="Z85" s="33" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AA85" s="17"/>
       <c r="AB85" s="17"/>
@@ -13261,7 +13326,7 @@
       <c r="AH85" s="17"/>
       <c r="AI85" s="8"/>
     </row>
-    <row r="86" spans="1:35" s="11" customFormat="1" ht="41.45" hidden="1" customHeight="1">
+    <row r="86" spans="1:35" s="11" customFormat="1" ht="30" customHeight="1">
       <c r="A86" s="46">
         <v>2025</v>
       </c>
@@ -13273,19 +13338,19 @@
         <v>35</v>
       </c>
       <c r="D86" s="21" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="E86" s="18" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="F86" s="18" t="s">
         <v>38</v>
       </c>
       <c r="G86" s="18" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="H86" s="18" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="I86" s="12" t="s">
         <v>51</v>
@@ -13333,17 +13398,21 @@
       <c r="R86" s="13"/>
       <c r="S86" s="17"/>
       <c r="T86" s="17"/>
-      <c r="U86" s="17"/>
-      <c r="V86" s="17"/>
+      <c r="U86" s="166">
+        <v>16722</v>
+      </c>
+      <c r="V86" s="166" t="s">
+        <v>283</v>
+      </c>
       <c r="W86" s="26">
         <v>45931</v>
       </c>
       <c r="X86" s="17" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Y86" s="22"/>
       <c r="Z86" s="31" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AA86" s="24"/>
       <c r="AB86" s="17"/>
@@ -13355,7 +13424,7 @@
       <c r="AH86" s="17"/>
       <c r="AI86" s="8"/>
     </row>
-    <row r="87" spans="1:35" s="11" customFormat="1" ht="41.45" hidden="1" customHeight="1">
+    <row r="87" spans="1:35" s="11" customFormat="1" ht="30" customHeight="1">
       <c r="A87" s="46">
         <v>2025</v>
       </c>
@@ -13367,10 +13436,10 @@
         <v>35</v>
       </c>
       <c r="D87" s="21" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E87" s="18" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F87" s="18" t="s">
         <v>66</v>
@@ -13437,7 +13506,7 @@
       </c>
       <c r="Y87" s="22"/>
       <c r="Z87" s="31" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AA87" s="24"/>
       <c r="AB87" s="17"/>
@@ -13449,7 +13518,7 @@
       <c r="AH87" s="17"/>
       <c r="AI87" s="8"/>
     </row>
-    <row r="88" spans="1:35" s="11" customFormat="1" ht="41.45" hidden="1" customHeight="1">
+    <row r="88" spans="1:35" s="11" customFormat="1" ht="30" customHeight="1">
       <c r="A88" s="46">
         <v>2025</v>
       </c>
@@ -13461,7 +13530,7 @@
         <v>35</v>
       </c>
       <c r="D88" s="19" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="E88" s="16" t="s">
         <v>89</v>
@@ -13531,7 +13600,7 @@
       </c>
       <c r="Y88" s="17"/>
       <c r="Z88" s="35" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AA88" s="17"/>
       <c r="AB88" s="17"/>
@@ -13543,7 +13612,7 @@
       <c r="AH88" s="17"/>
       <c r="AI88" s="8"/>
     </row>
-    <row r="89" spans="1:35" s="11" customFormat="1" ht="41.45" hidden="1" customHeight="1">
+    <row r="89" spans="1:35" s="11" customFormat="1" ht="30" customHeight="1">
       <c r="A89" s="46">
         <v>2025</v>
       </c>
@@ -13555,19 +13624,19 @@
         <v>35</v>
       </c>
       <c r="D89" s="19" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="E89" s="16" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="F89" s="17" t="s">
         <v>66</v>
       </c>
       <c r="G89" s="17" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="H89" s="17" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="I89" s="12" t="s">
         <v>51</v>
@@ -13625,7 +13694,7 @@
       </c>
       <c r="Y89" s="22"/>
       <c r="Z89" s="17" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AA89" s="24"/>
       <c r="AB89" s="17"/>
@@ -13637,7 +13706,7 @@
       <c r="AH89" s="17"/>
       <c r="AI89" s="8"/>
     </row>
-    <row r="90" spans="1:35" s="11" customFormat="1" ht="41.45" hidden="1" customHeight="1">
+    <row r="90" spans="1:35" s="11" customFormat="1" ht="30" customHeight="1">
       <c r="A90" s="46">
         <v>2025</v>
       </c>
@@ -13649,19 +13718,19 @@
         <v>35</v>
       </c>
       <c r="D90" s="21" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="E90" s="18" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="F90" s="18" t="s">
         <v>66</v>
       </c>
       <c r="G90" s="18" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="H90" s="18" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="I90" s="17" t="s">
         <v>41</v>
@@ -13731,7 +13800,7 @@
       <c r="AH90" s="17"/>
       <c r="AI90" s="8"/>
     </row>
-    <row r="91" spans="1:35" s="11" customFormat="1" ht="41.45" hidden="1" customHeight="1">
+    <row r="91" spans="1:35" s="11" customFormat="1" ht="30" customHeight="1">
       <c r="A91" s="46">
         <v>2025</v>
       </c>
@@ -13743,17 +13812,17 @@
         <v>35</v>
       </c>
       <c r="D91" s="21" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="E91" s="18" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="F91" s="18" t="s">
         <v>48</v>
       </c>
       <c r="G91" s="18"/>
       <c r="H91" s="18" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="I91" s="12" t="s">
         <v>51</v>
@@ -13811,7 +13880,7 @@
       </c>
       <c r="Y91" s="17"/>
       <c r="Z91" s="25" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AA91" s="17"/>
       <c r="AB91" s="17"/>
@@ -13823,7 +13892,7 @@
       <c r="AH91" s="17"/>
       <c r="AI91" s="8"/>
     </row>
-    <row r="92" spans="1:35" s="11" customFormat="1" ht="41.45" hidden="1" customHeight="1">
+    <row r="92" spans="1:35" s="11" customFormat="1" ht="30" customHeight="1">
       <c r="A92" s="46">
         <v>2025</v>
       </c>
@@ -13835,10 +13904,10 @@
         <v>35</v>
       </c>
       <c r="D92" s="21" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="E92" s="18" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="F92" s="18" t="s">
         <v>48</v>
@@ -13847,7 +13916,7 @@
         <v>97</v>
       </c>
       <c r="H92" s="18" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I92" s="12" t="s">
         <v>51</v>
@@ -13884,7 +13953,7 @@
       Dropdown!$A$2:$A$100
    )
 )</f>
-        <v>219</v>
+        <v>235</v>
       </c>
       <c r="Q92" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -13903,7 +13972,7 @@
       </c>
       <c r="Y92" s="22"/>
       <c r="Z92" s="31" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AA92" s="24"/>
       <c r="AB92" s="17"/>
@@ -13915,7 +13984,7 @@
       <c r="AH92" s="17"/>
       <c r="AI92" s="8"/>
     </row>
-    <row r="93" spans="1:35" s="11" customFormat="1" ht="41.45" hidden="1" customHeight="1">
+    <row r="93" spans="1:35" s="11" customFormat="1" ht="30" customHeight="1">
       <c r="A93" s="46">
         <v>2025</v>
       </c>
@@ -13930,16 +13999,16 @@
         <v>46</v>
       </c>
       <c r="E93" s="18" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="F93" s="18" t="s">
         <v>147</v>
       </c>
       <c r="G93" s="18" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="H93" s="18" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="I93" s="12" t="s">
         <v>41</v>
@@ -14003,7 +14072,7 @@
       <c r="AH93" s="17"/>
       <c r="AI93" s="8"/>
     </row>
-    <row r="94" spans="1:35" s="11" customFormat="1" ht="41.45" hidden="1" customHeight="1">
+    <row r="94" spans="1:35" s="11" customFormat="1" ht="30" customHeight="1">
       <c r="A94" s="46">
         <v>2025</v>
       </c>
@@ -14015,10 +14084,10 @@
         <v>35</v>
       </c>
       <c r="D94" s="19" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E94" s="16" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="F94" s="17" t="s">
         <v>61</v>
@@ -14027,7 +14096,7 @@
         <v>104</v>
       </c>
       <c r="H94" s="17" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="I94" s="17" t="s">
         <v>41</v>
@@ -14097,7 +14166,7 @@
       <c r="AH94" s="17"/>
       <c r="AI94" s="8"/>
     </row>
-    <row r="95" spans="1:35" s="11" customFormat="1" ht="41.45" hidden="1" customHeight="1">
+    <row r="95" spans="1:35" s="11" customFormat="1" ht="30" customHeight="1">
       <c r="A95" s="46">
         <v>2025</v>
       </c>
@@ -14109,19 +14178,19 @@
         <v>35</v>
       </c>
       <c r="D95" s="19" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="E95" s="16" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="F95" s="17" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="G95" s="17" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="H95" s="17" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="I95" s="12" t="s">
         <v>41</v>
@@ -14191,7 +14260,7 @@
       <c r="AH95" s="17"/>
       <c r="AI95" s="8"/>
     </row>
-    <row r="96" spans="1:35" s="11" customFormat="1" ht="41.45" hidden="1" customHeight="1">
+    <row r="96" spans="1:35" s="11" customFormat="1" ht="30" customHeight="1">
       <c r="A96" s="46">
         <v>2025</v>
       </c>
@@ -14203,16 +14272,16 @@
         <v>35</v>
       </c>
       <c r="D96" s="21" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="E96" s="18" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="F96" s="18" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="G96" s="18" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="H96" s="18"/>
       <c r="I96" s="17" t="s">
@@ -14250,7 +14319,7 @@
       Dropdown!$A$2:$A$100
    )
 )</f>
-        <v>194</v>
+        <v>210</v>
       </c>
       <c r="Q96" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -14269,7 +14338,7 @@
       </c>
       <c r="Y96" s="17"/>
       <c r="Z96" s="31" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AA96" s="17"/>
       <c r="AB96" s="17"/>
@@ -14281,7 +14350,7 @@
       <c r="AH96" s="17"/>
       <c r="AI96" s="8"/>
     </row>
-    <row r="97" spans="1:35" s="11" customFormat="1" ht="41.45" hidden="1" customHeight="1">
+    <row r="97" spans="1:35" s="11" customFormat="1" ht="30" customHeight="1">
       <c r="A97" s="46">
         <v>2025</v>
       </c>
@@ -14293,19 +14362,19 @@
         <v>35</v>
       </c>
       <c r="D97" s="19" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="E97" s="16" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="F97" s="17" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="G97" s="17" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="H97" s="17" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="I97" s="12" t="s">
         <v>51</v>
@@ -14342,7 +14411,7 @@
       Dropdown!$A$2:$A$100
    )
 )</f>
-        <v>194</v>
+        <v>210</v>
       </c>
       <c r="Q97" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -14371,7 +14440,7 @@
       <c r="AH97" s="17"/>
       <c r="AI97" s="8"/>
     </row>
-    <row r="98" spans="1:35" s="11" customFormat="1" ht="41.45" hidden="1" customHeight="1">
+    <row r="98" spans="1:35" s="11" customFormat="1" ht="30" customHeight="1">
       <c r="A98" s="46">
         <v>2025</v>
       </c>
@@ -14383,19 +14452,19 @@
         <v>35</v>
       </c>
       <c r="D98" s="21" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="E98" s="18" t="s">
         <v>116</v>
       </c>
       <c r="F98" s="18" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="G98" s="18" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="H98" s="18" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="I98" s="12" t="s">
         <v>82</v>
@@ -14473,7 +14542,7 @@
       <c r="AH98" s="17"/>
       <c r="AI98" s="8"/>
     </row>
-    <row r="99" spans="1:35" s="54" customFormat="1" ht="36" customHeight="1">
+    <row r="99" spans="1:35" s="54" customFormat="1" ht="30" customHeight="1">
       <c r="A99" s="53">
         <v>2026</v>
       </c>
@@ -14485,19 +14554,19 @@
         <v>35</v>
       </c>
       <c r="D99" s="53" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E99" s="53" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F99" s="54" t="s">
         <v>111</v>
       </c>
       <c r="G99" s="53" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H99" s="53" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="I99" s="53" t="s">
         <v>51</v>
@@ -14543,29 +14612,29 @@
         <v>ON KPI</v>
       </c>
       <c r="R99" s="53" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="S99" s="53">
         <v>15432</v>
       </c>
       <c r="T99" s="53" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="U99" s="53"/>
       <c r="V99" s="111" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="W99" s="53" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="X99" s="53" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Y99" s="56">
         <v>46097</v>
       </c>
       <c r="Z99" s="53" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AA99" s="53"/>
       <c r="AB99" s="53"/>
@@ -14584,7 +14653,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:35" s="60" customFormat="1" ht="36" customHeight="1">
+    <row r="100" spans="1:35" s="60" customFormat="1" ht="30" customHeight="1">
       <c r="A100" s="59">
         <v>2026</v>
       </c>
@@ -14596,16 +14665,16 @@
         <v>35</v>
       </c>
       <c r="D100" s="59" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="E100" s="59" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="F100" s="60" t="s">
         <v>111</v>
       </c>
       <c r="G100" s="59" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="H100" s="59" t="s">
         <v>113</v>
@@ -14654,27 +14723,27 @@
         <v>OVER KPI</v>
       </c>
       <c r="R100" s="59" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="S100" s="59">
         <v>15166</v>
       </c>
       <c r="T100" s="59" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="U100" s="59"/>
       <c r="V100" s="112" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="W100" s="53" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="X100" s="59" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Y100" s="62"/>
       <c r="Z100" s="59" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AA100" s="59"/>
       <c r="AB100" s="59"/>
@@ -14693,7 +14762,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="1:35" s="65" customFormat="1" ht="36" customHeight="1">
+    <row r="101" spans="1:35" s="65" customFormat="1" ht="30" customHeight="1">
       <c r="A101" s="60">
         <v>2026</v>
       </c>
@@ -14705,19 +14774,19 @@
         <v>35</v>
       </c>
       <c r="D101" s="60" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="E101" s="60" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="F101" s="60" t="s">
         <v>48</v>
       </c>
       <c r="G101" s="60" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="H101" s="60" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="I101" s="59" t="s">
         <v>51</v>
@@ -14763,7 +14832,7 @@
         <v>ON KPI</v>
       </c>
       <c r="R101" s="59" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="S101" s="60">
         <v>16631</v>
@@ -14771,17 +14840,17 @@
       <c r="T101" s="60"/>
       <c r="U101" s="60"/>
       <c r="V101" s="113" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="W101" s="53" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="X101" s="60" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Y101" s="63"/>
       <c r="Z101" s="59" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AA101" s="60"/>
       <c r="AB101" s="60"/>
@@ -14800,7 +14869,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="1:35" s="60" customFormat="1" ht="36" customHeight="1">
+    <row r="102" spans="1:35" s="60" customFormat="1" ht="30" customHeight="1">
       <c r="A102" s="60">
         <v>2026</v>
       </c>
@@ -14812,19 +14881,19 @@
         <v>35</v>
       </c>
       <c r="D102" s="60" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="E102" s="60" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="F102" s="60" t="s">
         <v>75</v>
       </c>
       <c r="G102" s="60" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="H102" s="60" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="I102" s="59" t="s">
         <v>41</v>
@@ -14867,14 +14936,14 @@
         <v>OVER KPI</v>
       </c>
       <c r="R102" s="59" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="V102" s="113"/>
       <c r="W102" s="60" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="X102" s="60" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="Y102" s="63"/>
       <c r="Z102" s="59"/>
@@ -14884,7 +14953,7 @@
       <c r="AF102" s="64"/>
       <c r="AG102" s="64"/>
     </row>
-    <row r="103" spans="1:35" s="65" customFormat="1" ht="36" customHeight="1">
+    <row r="103" spans="1:35" s="65" customFormat="1" ht="30" customHeight="1">
       <c r="A103" s="60">
         <v>2026</v>
       </c>
@@ -14896,19 +14965,19 @@
         <v>35</v>
       </c>
       <c r="D103" s="60" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="E103" s="60" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="F103" s="60" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="G103" s="59" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="H103" s="60" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="I103" s="59" t="s">
         <v>51</v>
@@ -14917,7 +14986,7 @@
         <v>42</v>
       </c>
       <c r="K103" s="60" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="L103" s="59" t="s">
         <v>43</v>
@@ -14954,27 +15023,27 @@
         <v>ON KPI</v>
       </c>
       <c r="R103" s="59" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="S103" s="60">
         <v>16552</v>
       </c>
       <c r="T103" s="60" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="U103" s="60"/>
       <c r="V103" s="113" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="W103" s="60" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="X103" s="60" t="s">
-        <v>150</v>
+        <v>191</v>
       </c>
       <c r="Y103" s="63"/>
       <c r="Z103" s="59" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AA103" s="60"/>
       <c r="AB103" s="60"/>
@@ -14993,7 +15062,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="104" spans="1:35" s="60" customFormat="1" ht="36" customHeight="1">
+    <row r="104" spans="1:35" s="60" customFormat="1" ht="30" customHeight="1">
       <c r="A104" s="60">
         <v>2026</v>
       </c>
@@ -15005,10 +15074,10 @@
         <v>35</v>
       </c>
       <c r="D104" s="60" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E104" s="60" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F104" s="60" t="s">
         <v>48</v>
@@ -15017,7 +15086,7 @@
         <v>97</v>
       </c>
       <c r="H104" s="60" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="I104" s="59" t="s">
         <v>41</v>
@@ -15064,17 +15133,17 @@
       </c>
       <c r="R104" s="59"/>
       <c r="V104" s="113" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="W104" s="60" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="X104" s="60" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Y104" s="63"/>
       <c r="Z104" s="59" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AC104" s="64">
         <v>274</v>
@@ -15091,7 +15160,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="105" spans="1:35" s="65" customFormat="1" ht="36" customHeight="1">
+    <row r="105" spans="1:35" s="65" customFormat="1" ht="30" customHeight="1">
       <c r="A105" s="60">
         <v>2026</v>
       </c>
@@ -15103,19 +15172,19 @@
         <v>35</v>
       </c>
       <c r="D105" s="60" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="E105" s="60" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="F105" s="60" t="s">
         <v>48</v>
       </c>
       <c r="G105" s="60" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="H105" s="60" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="I105" s="59" t="s">
         <v>51</v>
@@ -15161,7 +15230,7 @@
         <v>ON KPI</v>
       </c>
       <c r="R105" s="59" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="S105" s="60">
         <v>15969</v>
@@ -15169,17 +15238,17 @@
       <c r="T105" s="60"/>
       <c r="U105" s="60"/>
       <c r="V105" s="113" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="W105" s="60" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="X105" s="60" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Y105" s="63"/>
       <c r="Z105" s="59" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AA105" s="60"/>
       <c r="AB105" s="60"/>
@@ -15190,7 +15259,7 @@
       <c r="AG105" s="64"/>
       <c r="AH105" s="60"/>
     </row>
-    <row r="106" spans="1:35" s="60" customFormat="1" ht="36" customHeight="1">
+    <row r="106" spans="1:35" s="60" customFormat="1" ht="30" customHeight="1">
       <c r="A106" s="60">
         <v>2026</v>
       </c>
@@ -15202,10 +15271,10 @@
         <v>35</v>
       </c>
       <c r="D106" s="60" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="E106" s="60" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="I106" s="59" t="s">
         <v>41</v>
@@ -15251,13 +15320,13 @@
         <v>OVER KPI</v>
       </c>
       <c r="R106" s="59" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="V106" s="113" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="W106" s="60" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="X106" s="60" t="s">
         <v>118</v>
@@ -15272,7 +15341,7 @@
       <c r="AF106" s="64"/>
       <c r="AG106" s="64"/>
     </row>
-    <row r="107" spans="1:35" s="65" customFormat="1" ht="36" customHeight="1">
+    <row r="107" spans="1:35" s="65" customFormat="1" ht="30" customHeight="1">
       <c r="A107" s="60">
         <v>2026</v>
       </c>
@@ -15284,19 +15353,19 @@
         <v>35</v>
       </c>
       <c r="D107" s="60" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E107" s="60" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F107" s="60" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="G107" s="60" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H107" s="60" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="I107" s="59" t="s">
         <v>41</v>
@@ -15342,29 +15411,29 @@
         <v>ON KPI</v>
       </c>
       <c r="R107" s="59" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="S107" s="60">
         <v>16733</v>
       </c>
       <c r="T107" s="60" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="U107" s="60">
         <v>16749</v>
       </c>
       <c r="V107" s="113" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="W107" s="60" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="X107" s="60" t="s">
         <v>118</v>
       </c>
       <c r="Y107" s="63"/>
       <c r="Z107" s="59" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AA107" s="60"/>
       <c r="AB107" s="60"/>
@@ -15375,7 +15444,7 @@
       <c r="AG107" s="64"/>
       <c r="AH107" s="60"/>
     </row>
-    <row r="108" spans="1:35" s="65" customFormat="1" ht="34.5" customHeight="1">
+    <row r="108" spans="1:35" s="65" customFormat="1" ht="30" customHeight="1">
       <c r="A108" s="66">
         <v>2026</v>
       </c>
@@ -15387,19 +15456,19 @@
         <v>35</v>
       </c>
       <c r="D108" s="60" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="E108" s="60" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="F108" s="60" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="G108" s="60" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="H108" s="60" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="I108" s="59" t="s">
         <v>51</v>
@@ -15445,27 +15514,27 @@
         <v>ON KPI</v>
       </c>
       <c r="R108" s="59" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="S108" s="60">
         <v>16269</v>
       </c>
       <c r="T108" s="60" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="U108" s="60"/>
       <c r="V108" s="113" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="W108" s="60" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="X108" s="60" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Y108" s="63"/>
       <c r="Z108" s="59" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AA108" s="60"/>
       <c r="AB108" s="60"/>
@@ -15475,7 +15544,7 @@
       <c r="AF108" s="67"/>
       <c r="AG108" s="67"/>
     </row>
-    <row r="109" spans="1:35" s="65" customFormat="1" ht="34.5" customHeight="1">
+    <row r="109" spans="1:35" s="65" customFormat="1" ht="30" customHeight="1">
       <c r="A109" s="66">
         <v>2026</v>
       </c>
@@ -15490,7 +15559,7 @@
         <v>46</v>
       </c>
       <c r="E109" s="60" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F109" s="60" t="s">
         <v>61</v>
@@ -15499,7 +15568,7 @@
         <v>104</v>
       </c>
       <c r="H109" s="60" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="I109" s="59" t="s">
         <v>41</v>
@@ -15545,27 +15614,27 @@
         <v>ON KPI</v>
       </c>
       <c r="R109" s="59" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="S109" s="60" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="T109" s="60" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="U109" s="60"/>
       <c r="V109" s="113" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="W109" s="60" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="X109" s="60" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Y109" s="63"/>
       <c r="Z109" s="59" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AA109" s="60"/>
       <c r="AB109" s="60"/>
@@ -15575,7 +15644,7 @@
       <c r="AF109" s="68"/>
       <c r="AG109" s="68"/>
     </row>
-    <row r="110" spans="1:35" s="65" customFormat="1" ht="34.5" customHeight="1">
+    <row r="110" spans="1:35" s="65" customFormat="1" ht="30" customHeight="1">
       <c r="A110" s="66">
         <v>2026</v>
       </c>
@@ -15587,10 +15656,10 @@
         <v>35</v>
       </c>
       <c r="D110" s="60" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="E110" s="60" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="F110" s="60" t="s">
         <v>87</v>
@@ -15599,7 +15668,7 @@
         <v>106</v>
       </c>
       <c r="H110" s="60" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="I110" s="59" t="s">
         <v>41</v>
@@ -15645,27 +15714,27 @@
         <v>ON KPI</v>
       </c>
       <c r="R110" s="59" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="S110" s="60">
         <v>15917</v>
       </c>
       <c r="T110" s="60" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="U110" s="60"/>
       <c r="V110" s="113" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="W110" s="60" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="X110" s="60" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Y110" s="63"/>
       <c r="Z110" s="59" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AA110" s="60"/>
       <c r="AB110" s="60"/>
@@ -15675,10 +15744,10 @@
       <c r="AF110" s="68"/>
       <c r="AG110" s="68"/>
       <c r="AI110" s="69" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="111" spans="1:35" s="65" customFormat="1" ht="34.5" customHeight="1">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="111" spans="1:35" s="65" customFormat="1" ht="30" customHeight="1">
       <c r="A111" s="66">
         <v>2026</v>
       </c>
@@ -15690,10 +15759,10 @@
         <v>35</v>
       </c>
       <c r="D111" s="70" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="E111" s="70" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="F111" s="70" t="s">
         <v>87</v>
@@ -15702,7 +15771,7 @@
         <v>106</v>
       </c>
       <c r="H111" s="70" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="I111" s="71" t="s">
         <v>41</v>
@@ -15714,7 +15783,7 @@
         <v>52</v>
       </c>
       <c r="L111" s="71" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="M111" s="72">
         <v>46151</v>
@@ -15754,11 +15823,11 @@
         <v>15880</v>
       </c>
       <c r="V111" s="114" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="W111" s="70"/>
       <c r="X111" s="70" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="Y111" s="74"/>
       <c r="Z111" s="71" t="s">
@@ -15773,7 +15842,7 @@
       <c r="AG111" s="67"/>
       <c r="AH111" s="76"/>
     </row>
-    <row r="112" spans="1:35" s="65" customFormat="1" ht="34.5" customHeight="1">
+    <row r="112" spans="1:35" s="65" customFormat="1" ht="30" customHeight="1">
       <c r="A112" s="66">
         <v>2026</v>
       </c>
@@ -15785,19 +15854,19 @@
         <v>35</v>
       </c>
       <c r="D112" s="109" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="E112" s="60" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="F112" s="60" t="s">
         <v>111</v>
       </c>
       <c r="G112" s="60" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="H112" s="60" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="I112" s="59" t="s">
         <v>51</v>
@@ -15809,7 +15878,7 @@
         <v>52</v>
       </c>
       <c r="L112" s="71" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="M112" s="72">
         <v>46182</v>
@@ -15825,9 +15894,7 @@
 )</f>
         <v>46251</v>
       </c>
-      <c r="O112" s="63">
-        <v>46212</v>
-      </c>
+      <c r="O112" s="63"/>
       <c r="P112" s="59">
         <f ca="1">IF(M112="",                                                                                                                                                                                                   "",
    NETWORKDAYS(
@@ -15836,11 +15903,11 @@
       Dropdown!$A$2:$A$100
    )
 )</f>
-        <v>23</v>
+        <v>56</v>
       </c>
       <c r="Q112" s="59" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>ON KPI</v>
+        <v>OVER KPI</v>
       </c>
       <c r="R112" s="59"/>
       <c r="S112" s="60">
@@ -15851,13 +15918,15 @@
       <c r="V112" s="113"/>
       <c r="W112" s="60"/>
       <c r="X112" s="60" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="Y112" s="63"/>
       <c r="Z112" s="59"/>
-      <c r="AA112" s="60"/>
+      <c r="AA112" s="60" t="s">
+        <v>370</v>
+      </c>
       <c r="AB112" s="60" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="AC112" s="64"/>
       <c r="AD112" s="64"/>
@@ -15865,10 +15934,10 @@
       <c r="AF112" s="67"/>
       <c r="AG112" s="67"/>
       <c r="AI112" s="69" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="113" spans="1:35" s="65" customFormat="1" ht="34.5" customHeight="1">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="113" spans="1:35" s="65" customFormat="1" ht="30" customHeight="1">
       <c r="A113" s="66">
         <v>2026</v>
       </c>
@@ -15904,7 +15973,7 @@
         <v>52</v>
       </c>
       <c r="L113" s="71" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="M113" s="72">
         <v>46182</v>
@@ -15944,21 +16013,21 @@
       <c r="T113" s="70"/>
       <c r="U113" s="70"/>
       <c r="V113" s="114" t="s">
-        <v>368</v>
-      </c>
-      <c r="W113" s="60" t="s">
-        <v>369</v>
+        <v>373</v>
+      </c>
+      <c r="W113" s="160" t="s">
+        <v>374</v>
       </c>
       <c r="X113" s="70" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="Y113" s="74"/>
       <c r="Z113" s="71" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AA113" s="70"/>
       <c r="AB113" s="71" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="AC113" s="75"/>
       <c r="AD113" s="75"/>
@@ -15967,10 +16036,10 @@
       <c r="AG113" s="67"/>
       <c r="AH113" s="76"/>
       <c r="AI113" s="69" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="114" spans="1:35" s="65" customFormat="1" ht="34.5" customHeight="1">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="114" spans="1:35" s="65" customFormat="1" ht="30" customHeight="1">
       <c r="A114" s="66">
         <v>2026</v>
       </c>
@@ -15982,19 +16051,19 @@
         <v>35</v>
       </c>
       <c r="D114" s="70" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="E114" s="70" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="F114" s="70" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="G114" s="70" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="H114" s="70" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="I114" s="71" t="s">
         <v>41</v>
@@ -16048,15 +16117,15 @@
       <c r="V114" s="114"/>
       <c r="W114" s="70"/>
       <c r="X114" s="70" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Y114" s="74"/>
       <c r="Z114" s="71" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AA114" s="70"/>
       <c r="AB114" s="70" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="AC114" s="75"/>
       <c r="AD114" s="75"/>
@@ -16065,10 +16134,10 @@
       <c r="AG114" s="67"/>
       <c r="AH114" s="76"/>
       <c r="AI114" s="45" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="115" spans="1:35" s="65" customFormat="1" ht="34.5" customHeight="1">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="115" spans="1:35" s="65" customFormat="1" ht="30" customHeight="1">
       <c r="A115" s="66">
         <v>2026</v>
       </c>
@@ -16080,16 +16149,16 @@
         <v>35</v>
       </c>
       <c r="D115" s="70" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="E115" s="70" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="F115" s="70" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="G115" s="70" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="H115" s="70"/>
       <c r="I115" s="71" t="s">
@@ -16142,19 +16211,19 @@
       <c r="T115" s="70"/>
       <c r="U115" s="76"/>
       <c r="V115" s="117" t="s">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="W115" s="119"/>
       <c r="X115" s="70" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Y115" s="74"/>
       <c r="Z115" s="71" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AA115" s="70"/>
       <c r="AB115" s="60" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="AC115" s="75"/>
       <c r="AD115" s="75"/>
@@ -16163,10 +16232,10 @@
       <c r="AG115" s="67"/>
       <c r="AH115" s="76"/>
       <c r="AI115" s="45" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="116" spans="1:35" s="76" customFormat="1" ht="34.5" customHeight="1">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="116" spans="1:35" s="76" customFormat="1" ht="30" customHeight="1">
       <c r="A116" s="66">
         <v>2026</v>
       </c>
@@ -16178,19 +16247,19 @@
         <v>35</v>
       </c>
       <c r="D116" s="70" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="E116" s="70" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="F116" s="70" t="s">
         <v>48</v>
       </c>
       <c r="G116" s="70" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="H116" s="70" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="I116" s="71" t="s">
         <v>51</v>
@@ -16236,28 +16305,28 @@
         <v>ON KPI</v>
       </c>
       <c r="R116" s="71" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="S116" s="70">
         <v>16404</v>
       </c>
       <c r="T116" s="70"/>
       <c r="V116" s="118" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="W116" s="66" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="X116" s="70" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Y116" s="74"/>
       <c r="Z116" s="71" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AA116" s="70"/>
       <c r="AB116" s="60" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="AC116" s="75"/>
       <c r="AD116" s="75"/>
@@ -16265,10 +16334,10 @@
       <c r="AF116" s="67"/>
       <c r="AG116" s="67"/>
       <c r="AI116" s="77" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="117" spans="1:35" s="105" customFormat="1" ht="34.5" customHeight="1">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="117" spans="1:35" s="105" customFormat="1" ht="30" customHeight="1">
       <c r="A117" s="95">
         <v>2026</v>
       </c>
@@ -16279,17 +16348,17 @@
       <c r="C117" s="96" t="s">
         <v>35</v>
       </c>
-      <c r="D117" s="97" t="s">
-        <v>382</v>
+      <c r="D117" s="158" t="s">
+        <v>387</v>
       </c>
       <c r="E117" s="97" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="F117" s="97" t="s">
         <v>90</v>
       </c>
       <c r="G117" s="70" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H117" s="97"/>
       <c r="I117" s="96" t="s">
@@ -16298,9 +16367,11 @@
       <c r="J117" s="96" t="s">
         <v>42</v>
       </c>
-      <c r="K117" s="97"/>
+      <c r="K117" s="97" t="s">
+        <v>52</v>
+      </c>
       <c r="L117" s="96" t="s">
-        <v>383</v>
+        <v>369</v>
       </c>
       <c r="M117" s="98">
         <v>46226</v>
@@ -16316,7 +16387,9 @@
 )</f>
         <v>46274</v>
       </c>
-      <c r="O117" s="100"/>
+      <c r="O117" s="100">
+        <v>46266</v>
+      </c>
       <c r="P117" s="96">
         <f ca="1">IF(M117="",                                                                                                                                                                                                   "",
    NETWORKDAYS(
@@ -16325,14 +16398,14 @@
       Dropdown!$A$2:$A$100
    )
 )</f>
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="Q117" s="96" t="str">
         <f t="shared" ca="1" si="6"/>
         <v>ON KPI</v>
       </c>
       <c r="R117" s="96" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="S117" s="97">
         <v>15880</v>
@@ -16342,13 +16415,15 @@
       <c r="V117" s="115"/>
       <c r="W117" s="100"/>
       <c r="X117" s="97" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="Y117" s="101"/>
       <c r="Z117" s="96"/>
-      <c r="AA117" s="97"/>
+      <c r="AA117" s="96" t="s">
+        <v>388</v>
+      </c>
       <c r="AB117" s="146" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="AC117" s="102"/>
       <c r="AD117" s="102"/>
@@ -16357,10 +16432,10 @@
       <c r="AG117" s="103"/>
       <c r="AH117" s="104"/>
       <c r="AI117" s="108" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="118" spans="1:35" s="105" customFormat="1" ht="34.5" customHeight="1">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="118" spans="1:35" s="105" customFormat="1" ht="30" customHeight="1">
       <c r="A118" s="95">
         <v>2026</v>
       </c>
@@ -16372,19 +16447,19 @@
         <v>35</v>
       </c>
       <c r="D118" s="120" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="E118" s="97" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="F118" s="97" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="G118" s="106" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="H118" s="107" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="I118" s="96" t="s">
         <v>51</v>
@@ -16392,9 +16467,11 @@
       <c r="J118" s="96" t="s">
         <v>42</v>
       </c>
-      <c r="K118" s="97"/>
+      <c r="K118" s="97" t="s">
+        <v>114</v>
+      </c>
       <c r="L118" s="96" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="M118" s="98">
         <v>46203</v>
@@ -16410,7 +16487,9 @@
 )</f>
         <v>46272</v>
       </c>
-      <c r="O118" s="100"/>
+      <c r="O118" s="100">
+        <v>46245</v>
+      </c>
       <c r="P118" s="96">
         <f ca="1">IF(M118="",                                                                                                                                                                                                   "",
    NETWORKDAYS(
@@ -16419,32 +16498,34 @@
       Dropdown!$A$2:$A$100
    )
 )</f>
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="Q118" s="96" t="str">
         <f t="shared" ca="1" si="6"/>
         <v>ON KPI</v>
       </c>
       <c r="R118" s="96" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="S118" s="97">
         <v>16748</v>
       </c>
       <c r="T118" s="97" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="U118" s="97"/>
-      <c r="V118" s="115"/>
+      <c r="V118" s="115" t="s">
+        <v>391</v>
+      </c>
       <c r="W118" s="100"/>
       <c r="X118" s="97" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="Y118" s="101"/>
       <c r="Z118" s="96"/>
       <c r="AA118" s="97"/>
       <c r="AB118" s="97" t="s">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="AC118" s="102"/>
       <c r="AD118" s="102"/>
@@ -16453,10 +16534,10 @@
       <c r="AG118" s="103"/>
       <c r="AH118" s="104"/>
       <c r="AI118" s="108" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="119" spans="1:35" s="105" customFormat="1" ht="34.5" customHeight="1">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="119" spans="1:35" s="105" customFormat="1" ht="30" customHeight="1">
       <c r="A119" s="95">
         <v>2026</v>
       </c>
@@ -16471,7 +16552,7 @@
         <v>46</v>
       </c>
       <c r="E119" s="97" t="s">
-        <v>388</v>
+        <v>394</v>
       </c>
       <c r="F119" s="97" t="s">
         <v>61</v>
@@ -16480,7 +16561,7 @@
         <v>104</v>
       </c>
       <c r="H119" s="97" t="s">
-        <v>389</v>
+        <v>395</v>
       </c>
       <c r="I119" s="96" t="s">
         <v>41</v>
@@ -16490,7 +16571,7 @@
       </c>
       <c r="K119" s="97"/>
       <c r="L119" s="96" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="M119" s="98">
         <v>46182</v>
@@ -16524,25 +16605,27 @@
         <v>OVER KPI</v>
       </c>
       <c r="R119" s="96" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="S119" s="97">
         <v>15647</v>
       </c>
       <c r="T119" s="97" t="s">
-        <v>390</v>
+        <v>396</v>
       </c>
       <c r="U119" s="97"/>
-      <c r="V119" s="115"/>
+      <c r="V119" s="115" t="s">
+        <v>397</v>
+      </c>
       <c r="W119" s="100"/>
       <c r="X119" s="97" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="Y119" s="101"/>
       <c r="Z119" s="96"/>
       <c r="AA119" s="97"/>
       <c r="AB119" s="96" t="s">
-        <v>391</v>
+        <v>398</v>
       </c>
       <c r="AC119" s="102"/>
       <c r="AD119" s="102"/>
@@ -16551,39 +16634,51 @@
       <c r="AG119" s="103"/>
       <c r="AH119" s="104"/>
       <c r="AI119" s="108" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="120" spans="1:35" ht="34.5" customHeight="1">
-      <c r="A120" s="149">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="120" spans="1:35" ht="30" customHeight="1">
+      <c r="A120" s="95">
         <v>2026</v>
       </c>
-      <c r="B120" s="147" t="str">
+      <c r="B120" s="96" t="str">
         <f>IF(M120="", "", TEXT(M120, "[$-en-US]mmmm"))</f>
-        <v>July</v>
-      </c>
-      <c r="C120" s="147"/>
-      <c r="D120" s="150" t="s">
-        <v>372</v>
-      </c>
-      <c r="E120" s="150"/>
-      <c r="F120" s="150"/>
-      <c r="G120" s="150"/>
-      <c r="H120" s="150"/>
-      <c r="I120" s="147" t="s">
+        <v>August</v>
+      </c>
+      <c r="C120" s="96" t="s">
+        <v>45</v>
+      </c>
+      <c r="D120" s="97" t="s">
+        <v>377</v>
+      </c>
+      <c r="E120" s="97" t="s">
+        <v>400</v>
+      </c>
+      <c r="F120" s="97" t="s">
+        <v>178</v>
+      </c>
+      <c r="G120" s="97" t="s">
+        <v>179</v>
+      </c>
+      <c r="H120" s="97" t="s">
+        <v>401</v>
+      </c>
+      <c r="I120" s="96" t="s">
         <v>41</v>
       </c>
-      <c r="J120" s="147" t="s">
+      <c r="J120" s="96" t="s">
         <v>42</v>
       </c>
-      <c r="K120" s="150"/>
-      <c r="L120" s="147" t="s">
-        <v>383</v>
-      </c>
-      <c r="M120" s="98">
-        <v>46217</v>
-      </c>
-      <c r="N120" s="151">
+      <c r="K120" s="97" t="s">
+        <v>114</v>
+      </c>
+      <c r="L120" s="96" t="s">
+        <v>369</v>
+      </c>
+      <c r="M120" s="168">
+        <v>46260</v>
+      </c>
+      <c r="N120" s="169">
         <f>IF(M120="",                                                                                                                                                                                                  "",
    WORKDAY(
       M120,
@@ -16592,10 +16687,10 @@
       Dropdown!$A$2:$A$100
    )
 )</f>
-        <v>46265</v>
-      </c>
-      <c r="O120" s="152"/>
-      <c r="P120" s="147">
+        <v>46302</v>
+      </c>
+      <c r="O120" s="100"/>
+      <c r="P120" s="96">
         <f ca="1">IF(M120="",                                                                                                                                                                                                   "",
    NETWORKDAYS(
       M120,
@@ -16603,9 +16698,9 @@
       Dropdown!$A$2:$A$100
    )
 )</f>
-        <v>15</v>
-      </c>
-      <c r="Q120" s="147" t="str">
+        <v>4</v>
+      </c>
+      <c r="Q120" s="96" t="str">
         <f ca="1">IF(P120="",                                                                                                                                                                                                   "",
    IF(OR(I120="O-General",                                                                                                                                                                                                   I120="S-General"),
       IF(P120&lt;=30,                                                                                                                                                                                                   "ON KPI",                                                                                                                                                                                                   "OVER KPI"),
@@ -16617,53 +16712,71 @@
 )</f>
         <v>ON KPI</v>
       </c>
-      <c r="R120" s="147"/>
-      <c r="S120" s="150"/>
-      <c r="T120" s="150"/>
-      <c r="U120" s="150"/>
-      <c r="V120" s="150"/>
-      <c r="W120" s="152"/>
-      <c r="X120" s="150" t="s">
-        <v>320</v>
-      </c>
-      <c r="Y120" s="153"/>
-      <c r="Z120" s="147"/>
-      <c r="AA120" s="150"/>
-      <c r="AB120" s="150"/>
-      <c r="AC120" s="154"/>
-      <c r="AD120" s="154"/>
-      <c r="AE120" s="154"/>
-      <c r="AF120" s="148"/>
-      <c r="AG120" s="148"/>
-      <c r="AH120" s="155"/>
-      <c r="AI120" s="156"/>
-    </row>
-    <row r="121" spans="1:35" ht="34.5" customHeight="1">
-      <c r="A121" s="149"/>
-      <c r="B121" s="147" t="str">
+      <c r="R120" s="96"/>
+      <c r="S120" s="97">
+        <v>16257</v>
+      </c>
+      <c r="T120" s="97"/>
+      <c r="U120" s="97"/>
+      <c r="V120" s="97"/>
+      <c r="W120" s="100"/>
+      <c r="X120" s="97" t="s">
+        <v>324</v>
+      </c>
+      <c r="Y120" s="101"/>
+      <c r="Z120" s="96"/>
+      <c r="AA120" s="97"/>
+      <c r="AB120" s="97"/>
+      <c r="AC120" s="102"/>
+      <c r="AD120" s="102"/>
+      <c r="AE120" s="102"/>
+      <c r="AF120" s="103"/>
+      <c r="AG120" s="103"/>
+      <c r="AH120" s="104"/>
+      <c r="AI120" s="159"/>
+    </row>
+    <row r="121" spans="1:35" ht="30" customHeight="1">
+      <c r="A121" s="95">
+        <v>2026</v>
+      </c>
+      <c r="B121" s="96" t="str">
         <f>IF(M121="", "", TEXT(M121, "[$-en-US]mmmm"))</f>
-        <v/>
-      </c>
-      <c r="C121" s="147"/>
-      <c r="D121" s="150" t="s">
-        <v>46</v>
-      </c>
-      <c r="E121" s="150" t="s">
-        <v>393</v>
-      </c>
-      <c r="F121" s="150"/>
-      <c r="G121" s="150"/>
-      <c r="H121" s="150"/>
-      <c r="I121" s="147" t="s">
+        <v>August</v>
+      </c>
+      <c r="C121" s="96" t="s">
+        <v>35</v>
+      </c>
+      <c r="D121" s="97" t="s">
+        <v>402</v>
+      </c>
+      <c r="E121" s="97" t="s">
+        <v>403</v>
+      </c>
+      <c r="F121" s="97" t="s">
+        <v>87</v>
+      </c>
+      <c r="G121" s="97" t="s">
+        <v>404</v>
+      </c>
+      <c r="H121" s="97" t="s">
+        <v>405</v>
+      </c>
+      <c r="I121" s="96" t="s">
         <v>41</v>
       </c>
-      <c r="J121" s="147" t="s">
-        <v>394</v>
-      </c>
-      <c r="K121" s="150"/>
-      <c r="L121" s="147"/>
-      <c r="M121" s="157"/>
-      <c r="N121" s="151" t="str">
+      <c r="J121" s="96" t="s">
+        <v>42</v>
+      </c>
+      <c r="K121" s="97" t="s">
+        <v>114</v>
+      </c>
+      <c r="L121" s="96" t="s">
+        <v>369</v>
+      </c>
+      <c r="M121" s="98">
+        <v>46252</v>
+      </c>
+      <c r="N121" s="99">
         <f>IF(M121="",                                                                                                                                                                                                  "",
    WORKDAY(
       M121,
@@ -16672,10 +16785,10 @@
       Dropdown!$A$2:$A$100
    )
 )</f>
-        <v/>
-      </c>
-      <c r="O121" s="152"/>
-      <c r="P121" s="147" t="str">
+        <v>46294</v>
+      </c>
+      <c r="O121" s="100"/>
+      <c r="P121" s="96">
         <f ca="1">IF(M121="",                                                                                                                                                                                                   "",
    NETWORKDAYS(
       M121,
@@ -16683,9 +16796,9 @@
       Dropdown!$A$2:$A$100
    )
 )</f>
-        <v/>
-      </c>
-      <c r="Q121" s="147" t="str">
+        <v>10</v>
+      </c>
+      <c r="Q121" s="96" t="str">
         <f ca="1">IF(P121="",                                                                                                                                                                                                   "",
    IF(OR(I121="O-General",                                                                                                                                                                                                   I121="S-General"),
       IF(P121&lt;=30,                                                                                                                                                                                                   "ON KPI",                                                                                                                                                                                                   "OVER KPI"),
@@ -16695,26 +16808,38 @@
       )
    )
 )</f>
-        <v/>
-      </c>
-      <c r="R121" s="147"/>
-      <c r="S121" s="150"/>
-      <c r="T121" s="150"/>
-      <c r="U121" s="150"/>
-      <c r="V121" s="150"/>
-      <c r="W121" s="152"/>
-      <c r="X121" s="150"/>
-      <c r="Y121" s="153"/>
-      <c r="Z121" s="147"/>
-      <c r="AA121" s="150"/>
-      <c r="AB121" s="150"/>
-      <c r="AC121" s="154"/>
-      <c r="AD121" s="154"/>
-      <c r="AE121" s="154"/>
-      <c r="AF121" s="148"/>
-      <c r="AG121" s="148"/>
-      <c r="AH121" s="155"/>
-      <c r="AI121" s="156"/>
+        <v>ON KPI</v>
+      </c>
+      <c r="R121" s="96" t="s">
+        <v>406</v>
+      </c>
+      <c r="S121" s="97">
+        <v>16122</v>
+      </c>
+      <c r="T121" s="97" t="s">
+        <v>407</v>
+      </c>
+      <c r="U121" s="97"/>
+      <c r="V121" s="97"/>
+      <c r="W121" s="100"/>
+      <c r="X121" s="97" t="s">
+        <v>324</v>
+      </c>
+      <c r="Y121" s="101"/>
+      <c r="Z121" s="96"/>
+      <c r="AA121" s="97"/>
+      <c r="AB121" s="97" t="s">
+        <v>408</v>
+      </c>
+      <c r="AC121" s="102"/>
+      <c r="AD121" s="102"/>
+      <c r="AE121" s="102"/>
+      <c r="AF121" s="103"/>
+      <c r="AG121" s="103"/>
+      <c r="AH121" s="104"/>
+      <c r="AI121" s="108" t="s">
+        <v>409</v>
+      </c>
     </row>
     <row r="122" spans="1:35" ht="20.25" customHeight="1">
       <c r="A122" s="149"/>
@@ -16745,7 +16870,7 @@
         <v/>
       </c>
       <c r="O122" s="152"/>
-      <c r="P122" s="170" t="str">
+      <c r="P122" s="147" t="str">
         <f ca="1">IF(M122="",                                                                                                                                                                                                   "",
    NETWORKDAYS(
       M122,
@@ -16755,7 +16880,7 @@
 )</f>
         <v/>
       </c>
-      <c r="Q122" s="170" t="str">
+      <c r="Q122" s="147" t="str">
         <f ca="1">IF(P122="",                                                                                                                                                                                                   "",
    IF(OR(I122="O-General",                                                                                                                                                                                                   I122="S-General"),
       IF(P122&lt;=30,                                                                                                                                                                                                   "ON KPI",                                                                                                                                                                                                   "OVER KPI"),
@@ -16787,7 +16912,7 @@
       <c r="AI122" s="156"/>
     </row>
   </sheetData>
-  <autoFilter ref="V127" xr:uid="{817CD080-0396-428F-B39B-215D57916061}"/>
+  <autoFilter ref="D129" xr:uid="{817CD080-0396-428F-B39B-215D57916061}"/>
   <phoneticPr fontId="5" type="noConversion"/>
   <conditionalFormatting sqref="I1:I1048576">
     <cfRule type="containsText" dxfId="62" priority="3" operator="containsText" text="Special">
@@ -16838,14 +16963,15 @@
     <hyperlink ref="AI119" r:id="rId7" xr:uid="{6412AD55-DFDE-4449-8C87-7306C306DF21}"/>
     <hyperlink ref="AI118" r:id="rId8" xr:uid="{3AE257EE-27A3-49C5-A451-67A7958DDEDF}"/>
     <hyperlink ref="AI117" r:id="rId9" display="https://kubotagroup-my.sharepoint.com/:p:/g/personal/sopicha_p_kubota_com/IQC5U4NeJoqtTp54_1oiR2KoAUQFW18kzy5euvdtwGkyYeY?email=lapat.j%40kubota.com&amp;wdExp=TEAMS-TREATMENT&amp;web=1&amp;TeamsCID=f5692ebc-edb5-4e7a-b85e-ccf204ef4d18&amp;isSPOFile=1&amp;ovuser=cdf09dce-c865-4f42-901d-32d3d8d3f60f%2Clapat.j%40kubota.com&amp;clickparams=eyJBcHBOYW1lIjoiVGVhbXMtRGVza3RvcCIsIkFwcFZlcnNpb24iOiI0OS8yNjA2MTExODIxNiIsIkhhc0ZlZGVyYXRlZFVzZXIiOmZhbHNlfQ%3D%3D" xr:uid="{932F9692-9604-47F9-9C67-1579DC12341D}"/>
+    <hyperlink ref="AI121" r:id="rId10" xr:uid="{F9F73A2D-6C3D-4A5F-9411-2D89FAC66157}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
     <ignoredError sqref="B32" calculatedColumn="1"/>
   </ignoredErrors>
-  <legacyDrawing r:id="rId10"/>
+  <legacyDrawing r:id="rId11"/>
   <tableParts count="1">
-    <tablePart r:id="rId11"/>
+    <tablePart r:id="rId12"/>
   </tableParts>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
@@ -16941,46 +17067,46 @@
   <sheetData>
     <row r="1" spans="1:14">
       <c r="A1" s="3" t="s">
-        <v>395</v>
+        <v>410</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>396</v>
+        <v>411</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>397</v>
+        <v>412</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>398</v>
+        <v>413</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>399</v>
+        <v>414</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>72</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>400</v>
+        <v>415</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>9</v>
       </c>
       <c r="J1" s="6" t="s">
-        <v>401</v>
+        <v>416</v>
       </c>
       <c r="K1" s="6" t="s">
-        <v>402</v>
+        <v>417</v>
       </c>
       <c r="L1" s="7" t="s">
-        <v>403</v>
+        <v>418</v>
       </c>
       <c r="M1" s="1" t="s">
         <v>23</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>404</v>
+        <v>419</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="84">
@@ -17000,7 +17126,7 @@
         <v>29</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>72</v>
@@ -17012,19 +17138,19 @@
         <v>83</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>405</v>
+        <v>420</v>
       </c>
       <c r="M2" s="1" t="s">
         <v>118</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="84.6" thickBot="1">
@@ -17035,13 +17161,13 @@
         <v>51</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>45</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>406</v>
+        <v>421</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>53</v>
@@ -17050,25 +17176,25 @@
         <v>114</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>394</v>
+        <v>422</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>407</v>
+        <v>423</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="84.6" thickBot="1">
@@ -17079,13 +17205,13 @@
         <v>82</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>365</v>
+        <v>424</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>54</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>409</v>
+        <v>425</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>72</v>
@@ -17100,16 +17226,16 @@
         <v>124</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>410</v>
+        <v>426</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="105.6" thickBot="1">
@@ -17117,25 +17243,25 @@
         <v>46026</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>411</v>
+        <v>427</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>412</v>
+        <v>428</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>413</v>
+        <v>429</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>414</v>
+        <v>430</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="84">
@@ -17143,25 +17269,25 @@
         <v>46032</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>383</v>
+        <v>369</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>415</v>
+        <v>431</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>120</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>416</v>
+        <v>432</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>417</v>
+        <v>433</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>418</v>
+        <v>434</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="63.6" thickBot="1">
@@ -17172,22 +17298,22 @@
         <v>84</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>419</v>
+        <v>435</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>420</v>
+        <v>436</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>421</v>
+        <v>437</v>
       </c>
       <c r="M7" s="1" t="s">
         <v>72</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="42.6" thickBot="1">
@@ -17198,16 +17324,16 @@
         <v>83</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>128</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>422</v>
+        <v>438</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>423</v>
+        <v>439</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="84.6" thickBot="1">
@@ -17215,10 +17341,10 @@
         <v>46040</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>424</v>
+        <v>440</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>147</v>
@@ -17227,7 +17353,7 @@
         <v>121</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>425</v>
+        <v>441</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="84.6" thickBot="1">
@@ -17238,13 +17364,13 @@
         <v>139</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>426</v>
+        <v>442</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>427</v>
+        <v>443</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="105.6" thickBot="1">
@@ -17258,7 +17384,7 @@
         <v>125</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>428</v>
+        <v>444</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="42.6" thickBot="1">
@@ -17269,10 +17395,10 @@
         <v>111</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>429</v>
+        <v>445</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="63.6" thickBot="1">
@@ -17286,7 +17412,7 @@
         <v>129</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>430</v>
+        <v>446</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="84.6" thickBot="1">
@@ -17300,7 +17426,7 @@
         <v>49</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>431</v>
+        <v>447</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="84.6" thickBot="1">
@@ -17311,10 +17437,10 @@
         <v>66</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>432</v>
+        <v>448</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="63.6" thickBot="1">
@@ -17328,7 +17454,7 @@
         <v>133</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>433</v>
+        <v>449</v>
       </c>
     </row>
     <row r="17" spans="1:12" ht="84.6" thickBot="1">
@@ -17339,10 +17465,10 @@
         <v>75</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="18" spans="1:12" ht="63.6" thickBot="1">
@@ -17353,10 +17479,10 @@
         <v>87</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>434</v>
+        <v>450</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>435</v>
+        <v>451</v>
       </c>
     </row>
     <row r="19" spans="1:12" ht="84.6" thickBot="1">
@@ -17367,10 +17493,10 @@
         <v>79</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>436</v>
+        <v>452</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>437</v>
+        <v>453</v>
       </c>
     </row>
     <row r="20" spans="1:12" ht="84.6" thickBot="1">
@@ -17381,10 +17507,10 @@
         <v>90</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>438</v>
+        <v>454</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>439</v>
+        <v>455</v>
       </c>
     </row>
     <row r="21" spans="1:12" ht="105.6" thickBot="1">
@@ -17395,10 +17521,10 @@
         <v>38</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>440</v>
+        <v>456</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>441</v>
+        <v>457</v>
       </c>
     </row>
     <row r="22" spans="1:12" ht="63.6" thickBot="1">
@@ -17406,13 +17532,13 @@
         <v>46096</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>442</v>
+        <v>458</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>443</v>
+        <v>459</v>
       </c>
     </row>
     <row r="23" spans="1:12" ht="84.6" thickBot="1">
@@ -17420,13 +17546,13 @@
         <v>46103</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>444</v>
+        <v>460</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>445</v>
+        <v>461</v>
       </c>
     </row>
     <row r="24" spans="1:12" ht="63.6" thickBot="1">
@@ -17434,13 +17560,13 @@
         <v>46109</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>446</v>
+        <v>462</v>
       </c>
     </row>
     <row r="25" spans="1:12" ht="63.6" thickBot="1">
@@ -17448,13 +17574,13 @@
         <v>46110</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>447</v>
+        <v>463</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>448</v>
+        <v>464</v>
       </c>
     </row>
     <row r="26" spans="1:12" ht="63.6" thickBot="1">
@@ -17462,13 +17588,13 @@
         <v>46116</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>449</v>
+        <v>465</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>450</v>
+        <v>466</v>
       </c>
     </row>
     <row r="27" spans="1:12" ht="84">
@@ -17476,10 +17602,10 @@
         <v>46117</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="L27" s="2" t="s">
         <v>126</v>
@@ -17494,7 +17620,7 @@
         <v>81</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>451</v>
+        <v>467</v>
       </c>
     </row>
     <row r="29" spans="1:12" ht="84.6" thickBot="1">
@@ -17518,7 +17644,7 @@
         <v>67</v>
       </c>
       <c r="L30" s="2" t="s">
-        <v>452</v>
+        <v>468</v>
       </c>
     </row>
     <row r="31" spans="1:12" ht="84.6" thickBot="1">
@@ -17530,7 +17656,7 @@
         <v>57</v>
       </c>
       <c r="L31" s="2" t="s">
-        <v>453</v>
+        <v>469</v>
       </c>
     </row>
     <row r="32" spans="1:12" ht="42.6" thickBot="1">
@@ -17542,7 +17668,7 @@
         <v>70</v>
       </c>
       <c r="L32" s="2" t="s">
-        <v>454</v>
+        <v>470</v>
       </c>
     </row>
     <row r="33" spans="1:12" ht="63.6" thickBot="1">
@@ -17554,7 +17680,7 @@
         <v>76</v>
       </c>
       <c r="L33" s="2" t="s">
-        <v>455</v>
+        <v>471</v>
       </c>
     </row>
     <row r="34" spans="1:12" ht="63.6" thickBot="1">
@@ -17566,7 +17692,7 @@
         <v>99</v>
       </c>
       <c r="L34" s="2" t="s">
-        <v>456</v>
+        <v>472</v>
       </c>
     </row>
     <row r="35" spans="1:12" ht="63.6" thickBot="1">
@@ -17578,7 +17704,7 @@
         <v>80</v>
       </c>
       <c r="L35" s="2" t="s">
-        <v>457</v>
+        <v>473</v>
       </c>
     </row>
     <row r="36" spans="1:12" ht="42.6" thickBot="1">
@@ -17590,7 +17716,7 @@
         <v>94</v>
       </c>
       <c r="L36" s="2" t="s">
-        <v>458</v>
+        <v>474</v>
       </c>
     </row>
     <row r="37" spans="1:12" ht="63.6" thickBot="1">
@@ -17602,7 +17728,7 @@
         <v>91</v>
       </c>
       <c r="L37" s="2" t="s">
-        <v>459</v>
+        <v>475</v>
       </c>
     </row>
     <row r="38" spans="1:12" ht="63.6" thickBot="1">
@@ -17614,7 +17740,7 @@
         <v>97</v>
       </c>
       <c r="L38" s="2" t="s">
-        <v>460</v>
+        <v>476</v>
       </c>
     </row>
     <row r="39" spans="1:12" ht="63.6" thickBot="1">
@@ -17626,7 +17752,7 @@
         <v>39</v>
       </c>
       <c r="L39" s="2" t="s">
-        <v>461</v>
+        <v>477</v>
       </c>
     </row>
     <row r="40" spans="1:12" ht="84.6" thickBot="1">
@@ -17635,10 +17761,10 @@
       </c>
       <c r="J40" s="2"/>
       <c r="K40" s="2" t="s">
-        <v>462</v>
+        <v>478</v>
       </c>
       <c r="L40" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="41" spans="1:12" ht="63.6" thickBot="1">
@@ -17650,7 +17776,7 @@
         <v>104</v>
       </c>
       <c r="L41" s="2" t="s">
-        <v>463</v>
+        <v>479</v>
       </c>
     </row>
     <row r="42" spans="1:12" ht="63.6" thickBot="1">
@@ -17662,7 +17788,7 @@
         <v>101</v>
       </c>
       <c r="L42" s="2" t="s">
-        <v>464</v>
+        <v>480</v>
       </c>
     </row>
     <row r="43" spans="1:12" ht="84.6" thickBot="1">
@@ -17674,7 +17800,7 @@
         <v>112</v>
       </c>
       <c r="L43" s="2" t="s">
-        <v>465</v>
+        <v>481</v>
       </c>
     </row>
     <row r="44" spans="1:12" ht="42.6" thickBot="1">
@@ -17683,10 +17809,10 @@
       </c>
       <c r="J44" s="2"/>
       <c r="K44" s="2" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="L44" s="2" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="45" spans="1:12" ht="84.6" thickBot="1">
@@ -17695,10 +17821,10 @@
       </c>
       <c r="J45" s="2"/>
       <c r="K45" s="2" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="L45" s="2" t="s">
-        <v>466</v>
+        <v>482</v>
       </c>
     </row>
     <row r="46" spans="1:12" ht="42.6" thickBot="1">
@@ -17710,7 +17836,7 @@
         <v>144</v>
       </c>
       <c r="L46" s="2" t="s">
-        <v>467</v>
+        <v>483</v>
       </c>
     </row>
     <row r="47" spans="1:12" ht="84.6" thickBot="1">
@@ -17722,7 +17848,7 @@
         <v>137</v>
       </c>
       <c r="L47" s="2" t="s">
-        <v>468</v>
+        <v>484</v>
       </c>
     </row>
     <row r="48" spans="1:12" ht="42.6" thickBot="1">
@@ -17731,10 +17857,10 @@
       </c>
       <c r="J48" s="2"/>
       <c r="K48" s="2" t="s">
-        <v>469</v>
+        <v>485</v>
       </c>
       <c r="L48" s="2" t="s">
-        <v>470</v>
+        <v>486</v>
       </c>
     </row>
     <row r="49" spans="1:12" ht="42.6" thickBot="1">
@@ -17743,10 +17869,10 @@
       </c>
       <c r="J49" s="2"/>
       <c r="K49" s="2" t="s">
-        <v>471</v>
+        <v>487</v>
       </c>
       <c r="L49" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="50" spans="1:12" ht="84.6" thickBot="1">
@@ -17755,10 +17881,10 @@
       </c>
       <c r="J50" s="2"/>
       <c r="K50" s="2" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="L50" s="2" t="s">
-        <v>472</v>
+        <v>488</v>
       </c>
     </row>
     <row r="51" spans="1:12" ht="105.6" thickBot="1">
@@ -17767,10 +17893,10 @@
       </c>
       <c r="J51" s="2"/>
       <c r="K51" s="2" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="L51" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="52" spans="1:12" ht="63.6" thickBot="1">
@@ -17779,7 +17905,7 @@
       </c>
       <c r="J52" s="2"/>
       <c r="K52" s="2" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="L52" s="2" t="s">
         <v>134</v>
@@ -17791,10 +17917,10 @@
       </c>
       <c r="J53" s="2"/>
       <c r="K53" s="2" t="s">
-        <v>473</v>
+        <v>489</v>
       </c>
       <c r="L53" s="2" t="s">
-        <v>474</v>
+        <v>490</v>
       </c>
     </row>
     <row r="54" spans="1:12" ht="63.6" thickBot="1">
@@ -17806,7 +17932,7 @@
         <v>148</v>
       </c>
       <c r="L54" s="2" t="s">
-        <v>475</v>
+        <v>491</v>
       </c>
     </row>
     <row r="55" spans="1:12" ht="63.6" thickBot="1">
@@ -17815,10 +17941,10 @@
       </c>
       <c r="J55" s="2"/>
       <c r="K55" s="2" t="s">
-        <v>476</v>
+        <v>492</v>
       </c>
       <c r="L55" s="2" t="s">
-        <v>477</v>
+        <v>493</v>
       </c>
     </row>
     <row r="56" spans="1:12" ht="63.6" thickBot="1">
@@ -17827,10 +17953,10 @@
       </c>
       <c r="J56" s="2"/>
       <c r="K56" s="2" t="s">
-        <v>478</v>
+        <v>494</v>
       </c>
       <c r="L56" s="2" t="s">
-        <v>479</v>
+        <v>495</v>
       </c>
     </row>
     <row r="57" spans="1:12" ht="105.6" thickBot="1">
@@ -17839,10 +17965,10 @@
       </c>
       <c r="J57" s="2"/>
       <c r="K57" s="2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="L57" s="2" t="s">
-        <v>480</v>
+        <v>496</v>
       </c>
     </row>
     <row r="58" spans="1:12" ht="84.6" thickBot="1">
@@ -17851,10 +17977,10 @@
       </c>
       <c r="J58" s="2"/>
       <c r="K58" s="2" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="L58" s="2" t="s">
-        <v>481</v>
+        <v>497</v>
       </c>
     </row>
     <row r="59" spans="1:12" ht="63.6" thickBot="1">
@@ -17866,7 +17992,7 @@
         <v>106</v>
       </c>
       <c r="L59" s="2" t="s">
-        <v>482</v>
+        <v>498</v>
       </c>
     </row>
     <row r="60" spans="1:12" ht="63.6" thickBot="1">
@@ -17875,10 +18001,10 @@
       </c>
       <c r="J60" s="2"/>
       <c r="K60" s="2" t="s">
-        <v>483</v>
+        <v>499</v>
       </c>
       <c r="L60" s="2" t="s">
-        <v>484</v>
+        <v>500</v>
       </c>
     </row>
     <row r="61" spans="1:12" ht="84.6" thickBot="1">
@@ -17887,10 +18013,10 @@
       </c>
       <c r="J61" s="2"/>
       <c r="K61" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="L61" s="2" t="s">
-        <v>485</v>
+        <v>501</v>
       </c>
     </row>
     <row r="62" spans="1:12" ht="84.6" thickBot="1">
@@ -17899,10 +18025,10 @@
       </c>
       <c r="J62" s="2"/>
       <c r="K62" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="L62" s="2" t="s">
-        <v>486</v>
+        <v>502</v>
       </c>
     </row>
     <row r="63" spans="1:12" ht="63.6" thickBot="1">
@@ -17911,10 +18037,10 @@
       </c>
       <c r="J63" s="2"/>
       <c r="K63" s="2" t="s">
-        <v>487</v>
+        <v>503</v>
       </c>
       <c r="L63" s="2" t="s">
-        <v>488</v>
+        <v>504</v>
       </c>
     </row>
     <row r="64" spans="1:12" ht="63.6" thickBot="1">
@@ -17923,10 +18049,10 @@
       </c>
       <c r="J64" s="2"/>
       <c r="K64" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="L64" s="2" t="s">
-        <v>489</v>
+        <v>505</v>
       </c>
     </row>
     <row r="65" spans="1:12" ht="42.6" thickBot="1">
@@ -17935,10 +18061,10 @@
       </c>
       <c r="J65" s="2"/>
       <c r="K65" s="2" t="s">
-        <v>490</v>
+        <v>506</v>
       </c>
       <c r="L65" s="2" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="66" spans="1:12" ht="63.6" thickBot="1">
@@ -17947,10 +18073,10 @@
       </c>
       <c r="J66" s="2"/>
       <c r="K66" s="2" t="s">
-        <v>491</v>
+        <v>507</v>
       </c>
       <c r="L66" s="2" t="s">
-        <v>492</v>
+        <v>508</v>
       </c>
     </row>
     <row r="67" spans="1:12" ht="63.6" thickBot="1">
@@ -17959,10 +18085,10 @@
       </c>
       <c r="J67" s="2"/>
       <c r="K67" s="2" t="s">
-        <v>493</v>
+        <v>509</v>
       </c>
       <c r="L67" s="2" t="s">
-        <v>494</v>
+        <v>510</v>
       </c>
     </row>
     <row r="68" spans="1:12" ht="42.6" thickBot="1">
@@ -17971,10 +18097,10 @@
       </c>
       <c r="J68" s="2"/>
       <c r="K68" s="2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="L68" s="2" t="s">
-        <v>495</v>
+        <v>511</v>
       </c>
     </row>
     <row r="69" spans="1:12" ht="42.6" thickBot="1">
@@ -17983,10 +18109,10 @@
       </c>
       <c r="J69" s="2"/>
       <c r="K69" s="2" t="s">
-        <v>496</v>
+        <v>512</v>
       </c>
       <c r="L69" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="70" spans="1:12" ht="42.6" thickBot="1">
@@ -17995,7 +18121,7 @@
       </c>
       <c r="J70" s="2"/>
       <c r="K70" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="L70" s="2" t="s">
         <v>50</v>
@@ -18007,10 +18133,10 @@
       </c>
       <c r="J71" s="2"/>
       <c r="K71" s="2" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="L71" s="2" t="s">
-        <v>497</v>
+        <v>513</v>
       </c>
     </row>
     <row r="72" spans="1:12" ht="84.6" thickBot="1">
@@ -18019,10 +18145,10 @@
       </c>
       <c r="J72" s="2"/>
       <c r="K72" s="2" t="s">
-        <v>498</v>
+        <v>514</v>
       </c>
       <c r="L72" s="2" t="s">
-        <v>499</v>
+        <v>515</v>
       </c>
     </row>
     <row r="73" spans="1:12" ht="63.6" thickBot="1">
@@ -18031,10 +18157,10 @@
       </c>
       <c r="J73" s="2"/>
       <c r="K73" s="2" t="s">
-        <v>500</v>
+        <v>516</v>
       </c>
       <c r="L73" s="2" t="s">
-        <v>501</v>
+        <v>517</v>
       </c>
     </row>
     <row r="74" spans="1:12" ht="84.6" thickBot="1">
@@ -18043,10 +18169,10 @@
       </c>
       <c r="J74" s="2"/>
       <c r="K74" s="2" t="s">
-        <v>502</v>
+        <v>518</v>
       </c>
       <c r="L74" s="2" t="s">
-        <v>503</v>
+        <v>519</v>
       </c>
     </row>
     <row r="75" spans="1:12" ht="84.6" thickBot="1">
@@ -18055,10 +18181,10 @@
       </c>
       <c r="J75" s="2"/>
       <c r="K75" s="2" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="L75" s="2" t="s">
-        <v>504</v>
+        <v>520</v>
       </c>
     </row>
     <row r="76" spans="1:12" ht="42.6" thickBot="1">
@@ -18067,10 +18193,10 @@
       </c>
       <c r="J76" s="2"/>
       <c r="K76" s="2" t="s">
-        <v>505</v>
+        <v>521</v>
       </c>
       <c r="L76" s="2" t="s">
-        <v>506</v>
+        <v>522</v>
       </c>
     </row>
     <row r="77" spans="1:12" ht="42.6" thickBot="1">
@@ -18079,10 +18205,10 @@
       </c>
       <c r="J77" s="2"/>
       <c r="K77" s="2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="L77" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="78" spans="1:12" ht="63.6" thickBot="1">
@@ -18091,10 +18217,10 @@
       </c>
       <c r="J78" s="2"/>
       <c r="K78" s="2" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="L78" s="2" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
     </row>
     <row r="79" spans="1:12" ht="105.6" thickBot="1">
@@ -18103,7 +18229,7 @@
       </c>
       <c r="J79" s="2"/>
       <c r="K79" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="L79" s="2" t="s">
         <v>131</v>
@@ -18115,10 +18241,10 @@
       </c>
       <c r="J80" s="2"/>
       <c r="K80" s="2" t="s">
-        <v>507</v>
+        <v>523</v>
       </c>
       <c r="L80" s="2" t="s">
-        <v>508</v>
+        <v>401</v>
       </c>
     </row>
     <row r="81" spans="1:12" ht="63.6" thickBot="1">
@@ -18127,10 +18253,10 @@
       </c>
       <c r="J81" s="2"/>
       <c r="K81" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L81" s="2" t="s">
-        <v>509</v>
+        <v>524</v>
       </c>
     </row>
     <row r="82" spans="1:12" ht="42.6" thickBot="1">
@@ -18139,10 +18265,10 @@
       </c>
       <c r="J82" s="2"/>
       <c r="K82" s="2" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="L82" s="2" t="s">
-        <v>510</v>
+        <v>525</v>
       </c>
     </row>
     <row r="83" spans="1:12" ht="63.6" thickBot="1">
@@ -18151,10 +18277,10 @@
       </c>
       <c r="J83" s="2"/>
       <c r="K83" s="2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="L83" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="84" spans="1:12" ht="84.6" thickBot="1">
@@ -18163,10 +18289,10 @@
       </c>
       <c r="J84" s="2"/>
       <c r="K84" s="2" t="s">
-        <v>498</v>
+        <v>514</v>
       </c>
       <c r="L84" s="2" t="s">
-        <v>511</v>
+        <v>526</v>
       </c>
     </row>
     <row r="85" spans="1:12" ht="63.6" thickBot="1">
@@ -18175,7 +18301,7 @@
       </c>
       <c r="J85" s="2"/>
       <c r="K85" s="2" t="s">
-        <v>512</v>
+        <v>527</v>
       </c>
       <c r="L85" s="2" t="s">
         <v>81</v>
@@ -18187,7 +18313,7 @@
       </c>
       <c r="J86" s="2"/>
       <c r="K86" s="2" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="L86" s="2" t="s">
         <v>63</v>
@@ -18199,7 +18325,7 @@
       </c>
       <c r="J87" s="2"/>
       <c r="K87" s="2" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="L87" s="2" t="s">
         <v>68</v>
@@ -18211,7 +18337,7 @@
       </c>
       <c r="J88" s="2"/>
       <c r="K88" s="2" t="s">
-        <v>513</v>
+        <v>528</v>
       </c>
       <c r="L88" s="2" t="s">
         <v>58</v>
@@ -18223,7 +18349,7 @@
       </c>
       <c r="J89" s="2"/>
       <c r="K89" s="2" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="L89" s="2" t="s">
         <v>71</v>
@@ -18235,7 +18361,7 @@
       </c>
       <c r="J90" s="2"/>
       <c r="K90" s="2" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="L90" s="2" t="s">
         <v>74</v>
@@ -18247,7 +18373,7 @@
       </c>
       <c r="J91" s="2"/>
       <c r="K91" s="2" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="L91" s="2" t="s">
         <v>88</v>
@@ -18259,7 +18385,7 @@
       </c>
       <c r="J92" s="2"/>
       <c r="K92" s="2" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="L92" s="2" t="s">
         <v>95</v>
@@ -18271,7 +18397,7 @@
       </c>
       <c r="J93" s="2"/>
       <c r="K93" s="2" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="L93" s="2" t="s">
         <v>92</v>
@@ -18283,7 +18409,7 @@
       </c>
       <c r="J94" s="2"/>
       <c r="K94" s="2" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="L94" s="2" t="s">
         <v>98</v>
@@ -18295,7 +18421,7 @@
       </c>
       <c r="J95" s="2"/>
       <c r="K95" s="2" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="L95" s="2" t="s">
         <v>40</v>
@@ -18307,10 +18433,10 @@
       </c>
       <c r="J96" s="2"/>
       <c r="K96" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="L96" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="97" spans="1:12" ht="84.6" thickBot="1">
@@ -18331,7 +18457,7 @@
       </c>
       <c r="J98" s="2"/>
       <c r="K98" s="2" t="s">
-        <v>514</v>
+        <v>404</v>
       </c>
       <c r="L98" s="2" t="s">
         <v>113</v>
@@ -18343,7 +18469,7 @@
       </c>
       <c r="J99" s="2"/>
       <c r="K99" s="2" t="s">
-        <v>515</v>
+        <v>529</v>
       </c>
       <c r="L99" s="2" t="s">
         <v>149</v>
@@ -18355,10 +18481,10 @@
       </c>
       <c r="J100" s="2"/>
       <c r="K100" s="2" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="L100" s="2" t="s">
-        <v>516</v>
+        <v>530</v>
       </c>
     </row>
     <row r="101" spans="1:12" ht="63">
@@ -18367,7 +18493,7 @@
       </c>
       <c r="J101" s="2"/>
       <c r="K101" s="2" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="L101" s="2" t="s">
         <v>69</v>
@@ -18379,7 +18505,7 @@
       </c>
       <c r="J102" s="2"/>
       <c r="K102" s="94" t="s">
-        <v>517</v>
+        <v>531</v>
       </c>
       <c r="L102" s="2" t="s">
         <v>140</v>
@@ -18391,20 +18517,22 @@
       </c>
       <c r="J103" s="2"/>
       <c r="K103" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="L103" s="2" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="104" spans="1:12" ht="42.6" thickBot="1">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="104" spans="1:12" ht="102.75">
       <c r="A104" s="4">
         <v>46354</v>
       </c>
       <c r="J104" s="2"/>
-      <c r="K104" s="2"/>
+      <c r="K104" s="2" t="s">
+        <v>454</v>
+      </c>
       <c r="L104" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="105" spans="1:12" ht="42.6" thickBot="1">
@@ -18414,7 +18542,7 @@
       <c r="J105" s="2"/>
       <c r="K105" s="2"/>
       <c r="L105" s="2" t="s">
-        <v>518</v>
+        <v>532</v>
       </c>
     </row>
     <row r="106" spans="1:12" ht="63.6" thickBot="1">
@@ -18424,7 +18552,7 @@
       <c r="J106" s="2"/>
       <c r="K106" s="2"/>
       <c r="L106" s="2" t="s">
-        <v>519</v>
+        <v>533</v>
       </c>
     </row>
     <row r="107" spans="1:12" ht="63.6" thickBot="1">
@@ -18434,7 +18562,7 @@
       <c r="J107" s="2"/>
       <c r="K107" s="2"/>
       <c r="L107" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="108" spans="1:12" ht="21.6" thickBot="1">
@@ -18464,7 +18592,7 @@
       <c r="J110" s="2"/>
       <c r="K110" s="2"/>
       <c r="L110" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="111" spans="1:12" ht="63.6" thickBot="1">
@@ -18474,7 +18602,7 @@
       <c r="J111" s="2"/>
       <c r="K111" s="2"/>
       <c r="L111" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="112" spans="1:12" ht="63.6" thickBot="1">
@@ -18484,7 +18612,7 @@
       <c r="J112" s="2"/>
       <c r="K112" s="2"/>
       <c r="L112" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="113" spans="1:12" ht="63.6" thickBot="1">
@@ -18494,7 +18622,7 @@
       <c r="J113" s="2"/>
       <c r="K113" s="2"/>
       <c r="L113" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="114" spans="1:12" ht="63.6" thickBot="1">
@@ -18504,7 +18632,7 @@
       <c r="J114" s="2"/>
       <c r="K114" s="2"/>
       <c r="L114" s="2" t="s">
-        <v>520</v>
+        <v>534</v>
       </c>
     </row>
     <row r="115" spans="1:12" ht="63.6" thickBot="1">
@@ -18514,7 +18642,7 @@
       <c r="J115" s="2"/>
       <c r="K115" s="2"/>
       <c r="L115" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="116" spans="1:12" ht="42.6" thickBot="1">
@@ -18524,77 +18652,77 @@
       <c r="J116" s="2"/>
       <c r="K116" s="2"/>
       <c r="L116" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="117" spans="1:12" ht="42.6" thickBot="1">
       <c r="J117" s="2"/>
       <c r="K117" s="2"/>
       <c r="L117" s="2" t="s">
-        <v>521</v>
+        <v>405</v>
       </c>
     </row>
     <row r="118" spans="1:12" ht="63.6" thickBot="1">
       <c r="J118" s="2"/>
       <c r="K118" s="2"/>
       <c r="L118" s="2" t="s">
-        <v>522</v>
+        <v>535</v>
       </c>
     </row>
     <row r="119" spans="1:12" ht="21.6" thickBot="1">
       <c r="J119" s="2"/>
       <c r="K119" s="2"/>
       <c r="L119" s="2" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="120" spans="1:12" ht="42.6" thickBot="1">
       <c r="J120" s="2"/>
       <c r="K120" s="2"/>
       <c r="L120" s="2" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="121" spans="1:12" ht="63.6" thickBot="1">
       <c r="J121" s="2"/>
       <c r="K121" s="2"/>
       <c r="L121" s="2" t="s">
-        <v>523</v>
+        <v>536</v>
       </c>
     </row>
     <row r="122" spans="1:12" ht="42.6" thickBot="1">
       <c r="J122" s="2"/>
       <c r="K122" s="2"/>
       <c r="L122" s="2" t="s">
-        <v>524</v>
+        <v>537</v>
       </c>
     </row>
     <row r="123" spans="1:12" ht="42.6" thickBot="1">
       <c r="J123" s="2"/>
       <c r="K123" s="2"/>
       <c r="L123" s="2" t="s">
-        <v>525</v>
+        <v>538</v>
       </c>
     </row>
     <row r="124" spans="1:12" ht="21.6" thickBot="1">
       <c r="J124" s="2"/>
       <c r="K124" s="2"/>
       <c r="L124" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="125" spans="1:12" ht="63.6" thickBot="1">
       <c r="J125" s="2"/>
       <c r="K125" s="2"/>
       <c r="L125" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="126" spans="1:12" ht="63.6" thickBot="1">
       <c r="J126" s="2"/>
       <c r="K126" s="2"/>
       <c r="L126" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="127" spans="1:12" ht="21.6" thickBot="1">
@@ -18608,258 +18736,260 @@
       <c r="J128" s="2"/>
       <c r="K128" s="2"/>
       <c r="L128" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="129" spans="10:12" ht="21.6" thickBot="1">
       <c r="J129" s="2"/>
       <c r="K129" s="2"/>
       <c r="L129" s="5" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="130" spans="10:12" ht="42.6" thickBot="1">
       <c r="J130" s="2"/>
       <c r="K130" s="2"/>
       <c r="L130" s="2" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="131" spans="10:12" ht="21.6" thickBot="1">
       <c r="J131" s="2"/>
       <c r="K131" s="2"/>
       <c r="L131" s="2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="132" spans="10:12" ht="63.6" thickBot="1">
       <c r="J132" s="2"/>
       <c r="K132" s="2"/>
       <c r="L132" s="2" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="133" spans="10:12" ht="42.6" thickBot="1">
       <c r="J133" s="2"/>
       <c r="K133" s="2"/>
       <c r="L133" s="2" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="134" spans="10:12" ht="21.6" thickBot="1">
       <c r="J134" s="2"/>
       <c r="K134" s="2"/>
       <c r="L134" s="2" t="s">
-        <v>526</v>
+        <v>539</v>
       </c>
     </row>
     <row r="135" spans="10:12" ht="42.6" thickBot="1">
       <c r="J135" s="2"/>
       <c r="K135" s="2"/>
       <c r="L135" s="2" t="s">
-        <v>527</v>
+        <v>540</v>
       </c>
     </row>
     <row r="136" spans="10:12" ht="63.6" thickBot="1">
       <c r="J136" s="2"/>
       <c r="K136" s="2"/>
       <c r="L136" s="2" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="137" spans="10:12" ht="63.6" thickBot="1">
       <c r="J137" s="2"/>
       <c r="K137" s="2"/>
       <c r="L137" s="2" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
     </row>
     <row r="138" spans="10:12" ht="42.6" thickBot="1">
       <c r="J138" s="2"/>
       <c r="K138" s="2"/>
       <c r="L138" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="139" spans="10:12" ht="42.6" thickBot="1">
       <c r="J139" s="2"/>
       <c r="K139" s="2"/>
       <c r="L139" s="2" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
     </row>
     <row r="140" spans="10:12" ht="42.6" thickBot="1">
       <c r="J140" s="2"/>
       <c r="K140" s="2"/>
       <c r="L140" s="2" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
     </row>
     <row r="141" spans="10:12" ht="21.6" thickBot="1">
       <c r="J141" s="2"/>
       <c r="K141" s="2"/>
       <c r="L141" s="2" t="s">
-        <v>528</v>
+        <v>541</v>
       </c>
     </row>
     <row r="142" spans="10:12" ht="21.6" thickBot="1">
       <c r="J142" s="2"/>
       <c r="K142" s="2"/>
       <c r="L142" s="2" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
     </row>
     <row r="143" spans="10:12" ht="42.6" thickBot="1">
       <c r="J143" s="2"/>
       <c r="K143" s="2"/>
       <c r="L143" s="2" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
     </row>
     <row r="144" spans="10:12" ht="21.6" thickBot="1">
       <c r="J144" s="2"/>
       <c r="K144" s="2"/>
       <c r="L144" s="2" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
     </row>
     <row r="145" spans="10:12" ht="21.6" thickBot="1">
       <c r="J145" s="2"/>
       <c r="K145" s="2"/>
       <c r="L145" s="2" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
     </row>
     <row r="146" spans="10:12" ht="63.6" thickBot="1">
       <c r="J146" s="2"/>
       <c r="K146" s="2"/>
       <c r="L146" s="2" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
     </row>
     <row r="147" spans="10:12" ht="63.6" thickBot="1">
       <c r="J147" s="2"/>
       <c r="K147" s="2"/>
       <c r="L147" s="5" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="148" spans="10:12" ht="42.6" thickBot="1">
       <c r="J148" s="2"/>
       <c r="K148" s="2"/>
       <c r="L148" s="2" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
     </row>
     <row r="149" spans="10:12" ht="42.6" thickBot="1">
       <c r="J149" s="2"/>
       <c r="K149" s="2"/>
       <c r="L149" s="2" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
     </row>
     <row r="150" spans="10:12" ht="63.6" thickBot="1">
       <c r="J150" s="2"/>
       <c r="K150" s="2"/>
       <c r="L150" s="2" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
     </row>
     <row r="151" spans="10:12" ht="63.6" thickBot="1">
       <c r="J151" s="2"/>
       <c r="K151" s="2"/>
       <c r="L151" s="2" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
     </row>
     <row r="152" spans="10:12" ht="42.6" thickBot="1">
       <c r="J152" s="2"/>
       <c r="K152" s="2"/>
       <c r="L152" s="2" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
     </row>
     <row r="153" spans="10:12" ht="42.6" thickBot="1">
       <c r="J153" s="2"/>
       <c r="K153" s="2"/>
       <c r="L153" s="2" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
     </row>
     <row r="154" spans="10:12" ht="21.6" thickBot="1">
       <c r="J154" s="2"/>
       <c r="K154" s="2"/>
       <c r="L154" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="155" spans="10:12" ht="42.6" thickBot="1">
       <c r="J155" s="2"/>
       <c r="K155" s="2"/>
       <c r="L155" s="2" t="s">
-        <v>529</v>
+        <v>542</v>
       </c>
     </row>
     <row r="156" spans="10:12" ht="63.6" thickBot="1">
       <c r="J156" s="2"/>
       <c r="K156" s="2"/>
       <c r="L156" s="2" t="s">
-        <v>530</v>
+        <v>543</v>
       </c>
     </row>
     <row r="157" spans="10:12" ht="63.6" thickBot="1">
       <c r="J157" s="2"/>
       <c r="K157" s="2"/>
       <c r="L157" s="2" t="s">
-        <v>530</v>
+        <v>543</v>
       </c>
     </row>
     <row r="158" spans="10:12" ht="63.6" thickBot="1">
       <c r="J158" s="2"/>
       <c r="K158" s="2"/>
       <c r="L158" s="2" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
     </row>
     <row r="159" spans="10:12" ht="63.6" thickBot="1">
       <c r="J159" s="2"/>
       <c r="K159" s="2"/>
       <c r="L159" s="2" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
     </row>
     <row r="160" spans="10:12" ht="42">
       <c r="J160" s="2"/>
       <c r="K160" s="2"/>
       <c r="L160" s="2" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
     </row>
     <row r="161" spans="10:12" ht="42">
       <c r="J161" s="2"/>
       <c r="K161" s="2"/>
       <c r="L161" s="2" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
     </row>
     <row r="162" spans="10:12" ht="42">
       <c r="J162" s="2"/>
       <c r="K162" s="2"/>
       <c r="L162" s="2" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
     </row>
     <row r="163" spans="10:12" ht="63">
       <c r="J163" s="2"/>
       <c r="K163" s="2"/>
       <c r="L163" s="2" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="164" spans="10:12" ht="21.6" thickBot="1">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="164" spans="10:12" ht="82.5">
       <c r="J164" s="2"/>
       <c r="K164" s="2"/>
-      <c r="L164" s="2"/>
+      <c r="L164" s="2" t="s">
+        <v>401</v>
+      </c>
     </row>
     <row r="165" spans="10:12" ht="21.6" thickBot="1">
       <c r="J165" s="2"/>
@@ -23062,10 +23192,10 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>531</v>
+        <v>544</v>
       </c>
       <c r="C1" t="s">
-        <v>532</v>
+        <v>545</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -23073,7 +23203,7 @@
         <v>2026</v>
       </c>
       <c r="B2" t="s">
-        <v>533</v>
+        <v>546</v>
       </c>
       <c r="C2">
         <f>SUM(Recruitment!AC:AC)</f>
@@ -23109,7 +23239,7 @@
         <v>2026</v>
       </c>
       <c r="B5" t="s">
-        <v>534</v>
+        <v>547</v>
       </c>
       <c r="C5">
         <f>SUM(Recruitment!AH:AH)</f>
@@ -23138,25 +23268,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:30">
-      <c r="A1" s="165" t="s">
-        <v>535</v>
-      </c>
-      <c r="B1" s="161" t="s">
-        <v>536</v>
-      </c>
-      <c r="C1" s="161" t="s">
-        <v>537</v>
-      </c>
-      <c r="D1" s="161" t="s">
-        <v>538</v>
-      </c>
-      <c r="E1" s="158" t="s">
-        <v>539</v>
-      </c>
-      <c r="F1" s="159"/>
-      <c r="G1" s="160"/>
-      <c r="H1" s="161" t="s">
-        <v>540</v>
+      <c r="A1" s="177" t="s">
+        <v>548</v>
+      </c>
+      <c r="B1" s="173" t="s">
+        <v>549</v>
+      </c>
+      <c r="C1" s="173" t="s">
+        <v>550</v>
+      </c>
+      <c r="D1" s="173" t="s">
+        <v>551</v>
+      </c>
+      <c r="E1" s="170" t="s">
+        <v>552</v>
+      </c>
+      <c r="F1" s="171"/>
+      <c r="G1" s="172"/>
+      <c r="H1" s="173" t="s">
+        <v>553</v>
       </c>
       <c r="I1" s="121"/>
       <c r="J1" s="121"/>
@@ -23182,10 +23312,10 @@
       <c r="AD1" s="122"/>
     </row>
     <row r="2" spans="1:30">
-      <c r="A2" s="166"/>
-      <c r="B2" s="162"/>
-      <c r="C2" s="162"/>
-      <c r="D2" s="162"/>
+      <c r="A2" s="178"/>
+      <c r="B2" s="174"/>
+      <c r="C2" s="174"/>
+      <c r="D2" s="174"/>
       <c r="E2" s="124" t="s">
         <v>41</v>
       </c>
@@ -23193,13 +23323,13 @@
         <v>82</v>
       </c>
       <c r="G2" s="125" t="s">
-        <v>541</v>
-      </c>
-      <c r="H2" s="162"/>
+        <v>554</v>
+      </c>
+      <c r="H2" s="174"/>
       <c r="I2" s="126"/>
       <c r="J2" s="126"/>
       <c r="K2" s="126" t="s">
-        <v>542</v>
+        <v>555</v>
       </c>
       <c r="L2" s="127">
         <v>23000</v>
@@ -23225,7 +23355,7 @@
     </row>
     <row r="3" spans="1:30">
       <c r="A3" s="129" t="s">
-        <v>543</v>
+        <v>556</v>
       </c>
       <c r="B3" s="130"/>
       <c r="C3" s="130"/>
@@ -23243,7 +23373,7 @@
       <c r="I3" s="126"/>
       <c r="J3" s="126"/>
       <c r="K3" s="126" t="s">
-        <v>544</v>
+        <v>557</v>
       </c>
       <c r="L3" s="131">
         <v>178675</v>
@@ -23269,7 +23399,7 @@
     </row>
     <row r="4" spans="1:30">
       <c r="A4" s="129" t="s">
-        <v>545</v>
+        <v>558</v>
       </c>
       <c r="B4" s="130"/>
       <c r="C4" s="130"/>
@@ -23281,7 +23411,7 @@
       <c r="I4" s="126"/>
       <c r="J4" s="126"/>
       <c r="K4" s="126" t="s">
-        <v>546</v>
+        <v>559</v>
       </c>
       <c r="L4" s="131">
         <v>229650</v>
@@ -23306,17 +23436,17 @@
       <c r="AD4" s="128"/>
     </row>
     <row r="5" spans="1:30">
-      <c r="A5" s="167" t="s">
-        <v>547</v>
+      <c r="A5" s="179" t="s">
+        <v>560</v>
       </c>
       <c r="B5" s="130" t="s">
-        <v>548</v>
+        <v>561</v>
       </c>
       <c r="C5" s="132">
         <v>491400</v>
       </c>
       <c r="D5" s="130" t="s">
-        <v>549</v>
+        <v>562</v>
       </c>
       <c r="E5" s="130">
         <v>589</v>
@@ -23329,7 +23459,7 @@
       <c r="I5" s="126"/>
       <c r="J5" s="126"/>
       <c r="K5" s="126" t="s">
-        <v>550</v>
+        <v>563</v>
       </c>
       <c r="L5" s="126">
         <v>12910</v>
@@ -23354,15 +23484,15 @@
       <c r="AD5" s="128"/>
     </row>
     <row r="6" spans="1:30">
-      <c r="A6" s="168"/>
+      <c r="A6" s="180"/>
       <c r="B6" s="130" t="s">
-        <v>551</v>
+        <v>564</v>
       </c>
       <c r="C6" s="132">
         <v>80000</v>
       </c>
       <c r="D6" s="130" t="s">
-        <v>549</v>
+        <v>562</v>
       </c>
       <c r="E6" s="130"/>
       <c r="F6" s="130"/>
@@ -23371,7 +23501,7 @@
       <c r="I6" s="126"/>
       <c r="J6" s="126"/>
       <c r="K6" s="126" t="s">
-        <v>552</v>
+        <v>565</v>
       </c>
       <c r="L6" s="131">
         <v>57930</v>
@@ -23396,9 +23526,9 @@
       <c r="AD6" s="128"/>
     </row>
     <row r="7" spans="1:30">
-      <c r="A7" s="169"/>
+      <c r="A7" s="181"/>
       <c r="B7" s="133" t="s">
-        <v>553</v>
+        <v>566</v>
       </c>
       <c r="C7" s="132">
         <v>12157</v>
@@ -23433,10 +23563,10 @@
     </row>
     <row r="8" spans="1:30">
       <c r="A8" s="129" t="s">
-        <v>554</v>
+        <v>567</v>
       </c>
       <c r="B8" s="130" t="s">
-        <v>554</v>
+        <v>567</v>
       </c>
       <c r="C8" s="130">
         <v>0</v>
@@ -23470,17 +23600,17 @@
       <c r="AD8" s="128"/>
     </row>
     <row r="9" spans="1:30">
-      <c r="A9" s="167" t="s">
-        <v>555</v>
+      <c r="A9" s="179" t="s">
+        <v>568</v>
       </c>
       <c r="B9" s="130" t="s">
-        <v>556</v>
+        <v>569</v>
       </c>
       <c r="C9" s="130">
         <v>241.375</v>
       </c>
       <c r="D9" s="130" t="s">
-        <v>557</v>
+        <v>570</v>
       </c>
       <c r="E9" s="130"/>
       <c r="F9" s="130">
@@ -23514,9 +23644,9 @@
       <c r="AD9" s="128"/>
     </row>
     <row r="10" spans="1:30">
-      <c r="A10" s="169"/>
+      <c r="A10" s="181"/>
       <c r="B10" s="133" t="s">
-        <v>558</v>
+        <v>571</v>
       </c>
       <c r="C10" s="130">
         <v>139.8583333</v>
@@ -23550,17 +23680,17 @@
       <c r="AD10" s="128"/>
     </row>
     <row r="11" spans="1:30">
-      <c r="A11" s="167" t="s">
-        <v>411</v>
+      <c r="A11" s="179" t="s">
+        <v>427</v>
       </c>
       <c r="B11" s="130" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
       <c r="C11" s="130">
         <v>95.833333330000002</v>
       </c>
       <c r="D11" s="130" t="s">
-        <v>557</v>
+        <v>570</v>
       </c>
       <c r="E11" s="130">
         <v>15</v>
@@ -23598,15 +23728,15 @@
       <c r="AD11" s="128"/>
     </row>
     <row r="12" spans="1:30">
-      <c r="A12" s="168"/>
+      <c r="A12" s="180"/>
       <c r="B12" s="130" t="s">
-        <v>560</v>
+        <v>573</v>
       </c>
       <c r="C12" s="130">
         <v>241.375</v>
       </c>
       <c r="D12" s="130" t="s">
-        <v>557</v>
+        <v>570</v>
       </c>
       <c r="E12" s="130"/>
       <c r="F12" s="130"/>
@@ -23615,7 +23745,7 @@
       <c r="I12" s="126"/>
       <c r="J12" s="126"/>
       <c r="K12" s="126" t="s">
-        <v>561</v>
+        <v>574</v>
       </c>
       <c r="L12" s="126">
         <v>65</v>
@@ -23640,9 +23770,9 @@
       <c r="AD12" s="128"/>
     </row>
     <row r="13" spans="1:30">
-      <c r="A13" s="168"/>
+      <c r="A13" s="180"/>
       <c r="B13" s="133" t="s">
-        <v>562</v>
+        <v>575</v>
       </c>
       <c r="C13" s="130">
         <v>2529.0625</v>
@@ -23655,7 +23785,7 @@
       <c r="I13" s="126"/>
       <c r="J13" s="126"/>
       <c r="K13" s="126" t="s">
-        <v>563</v>
+        <v>576</v>
       </c>
       <c r="L13" s="126">
         <v>32</v>
@@ -23680,9 +23810,9 @@
       <c r="AD13" s="128"/>
     </row>
     <row r="14" spans="1:30">
-      <c r="A14" s="168"/>
+      <c r="A14" s="180"/>
       <c r="B14" s="133" t="s">
-        <v>564</v>
+        <v>577</v>
       </c>
       <c r="C14" s="130">
         <v>2529.0625</v>
@@ -23695,7 +23825,7 @@
       <c r="I14" s="126"/>
       <c r="J14" s="126"/>
       <c r="K14" s="126" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="L14" s="126">
         <v>7</v>
@@ -23720,9 +23850,9 @@
       <c r="AD14" s="128"/>
     </row>
     <row r="15" spans="1:30">
-      <c r="A15" s="169"/>
+      <c r="A15" s="181"/>
       <c r="B15" s="133" t="s">
-        <v>541</v>
+        <v>554</v>
       </c>
       <c r="C15" s="130">
         <v>2191.854167</v>
@@ -23735,7 +23865,7 @@
       <c r="I15" s="126"/>
       <c r="J15" s="126"/>
       <c r="K15" s="126" t="s">
-        <v>565</v>
+        <v>578</v>
       </c>
       <c r="L15" s="126">
         <v>33</v>
@@ -23760,17 +23890,17 @@
       <c r="AD15" s="128"/>
     </row>
     <row r="16" spans="1:30">
-      <c r="A16" s="167" t="s">
-        <v>365</v>
+      <c r="A16" s="179" t="s">
+        <v>424</v>
       </c>
       <c r="B16" s="130" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
       <c r="C16" s="130">
         <v>95.833333330000002</v>
       </c>
       <c r="D16" s="130" t="s">
-        <v>557</v>
+        <v>570</v>
       </c>
       <c r="E16" s="130">
         <v>4</v>
@@ -23787,7 +23917,7 @@
       <c r="I16" s="126"/>
       <c r="J16" s="126"/>
       <c r="K16" s="126" t="s">
-        <v>566</v>
+        <v>579</v>
       </c>
       <c r="L16" s="126">
         <v>4</v>
@@ -23812,15 +23942,15 @@
       <c r="AD16" s="128"/>
     </row>
     <row r="17" spans="1:30">
-      <c r="A17" s="168"/>
+      <c r="A17" s="180"/>
       <c r="B17" s="130" t="s">
-        <v>567</v>
+        <v>580</v>
       </c>
       <c r="C17" s="130">
         <v>956.875</v>
       </c>
       <c r="D17" s="130" t="s">
-        <v>557</v>
+        <v>570</v>
       </c>
       <c r="E17" s="130"/>
       <c r="F17" s="130"/>
@@ -23850,15 +23980,15 @@
       <c r="AD17" s="128"/>
     </row>
     <row r="18" spans="1:30">
-      <c r="A18" s="168"/>
+      <c r="A18" s="180"/>
       <c r="B18" s="130" t="s">
-        <v>568</v>
+        <v>581</v>
       </c>
       <c r="C18" s="130">
         <v>53.791666669999998</v>
       </c>
       <c r="D18" s="130" t="s">
-        <v>557</v>
+        <v>570</v>
       </c>
       <c r="E18" s="130"/>
       <c r="F18" s="130"/>
@@ -23888,15 +24018,15 @@
       <c r="AD18" s="128"/>
     </row>
     <row r="19" spans="1:30">
-      <c r="A19" s="168"/>
+      <c r="A19" s="180"/>
       <c r="B19" s="130" t="s">
-        <v>569</v>
+        <v>582</v>
       </c>
       <c r="C19" s="130">
         <v>956.875</v>
       </c>
       <c r="D19" s="130" t="s">
-        <v>557</v>
+        <v>570</v>
       </c>
       <c r="E19" s="130"/>
       <c r="F19" s="130"/>
@@ -23926,9 +24056,9 @@
       <c r="AD19" s="128"/>
     </row>
     <row r="20" spans="1:30">
-      <c r="A20" s="168"/>
+      <c r="A20" s="180"/>
       <c r="B20" s="133" t="s">
-        <v>570</v>
+        <v>583</v>
       </c>
       <c r="C20" s="130">
         <v>3095.0625</v>
@@ -23964,9 +24094,9 @@
       <c r="AD20" s="128"/>
     </row>
     <row r="21" spans="1:30">
-      <c r="A21" s="168"/>
+      <c r="A21" s="180"/>
       <c r="B21" s="133" t="s">
-        <v>571</v>
+        <v>584</v>
       </c>
       <c r="C21" s="130">
         <v>4126.75</v>
@@ -24000,9 +24130,9 @@
       <c r="AD21" s="128"/>
     </row>
     <row r="22" spans="1:30">
-      <c r="A22" s="169"/>
+      <c r="A22" s="181"/>
       <c r="B22" s="133" t="s">
-        <v>572</v>
+        <v>585</v>
       </c>
       <c r="C22" s="130">
         <v>3095.0625</v>
@@ -24037,10 +24167,10 @@
     </row>
     <row r="23" spans="1:30">
       <c r="A23" s="129" t="s">
-        <v>573</v>
+        <v>586</v>
       </c>
       <c r="B23" s="133" t="s">
-        <v>574</v>
+        <v>587</v>
       </c>
       <c r="C23" s="130">
         <v>1000</v>
@@ -24053,7 +24183,7 @@
       <c r="I23" s="126"/>
       <c r="J23" s="126"/>
       <c r="K23" s="126" t="s">
-        <v>575</v>
+        <v>588</v>
       </c>
       <c r="L23" s="126">
         <v>2</v>
@@ -24078,17 +24208,17 @@
       <c r="AD23" s="128"/>
     </row>
     <row r="24" spans="1:30">
-      <c r="A24" s="167" t="s">
-        <v>576</v>
-      </c>
-      <c r="B24" s="163" t="s">
-        <v>577</v>
+      <c r="A24" s="179" t="s">
+        <v>589</v>
+      </c>
+      <c r="B24" s="175" t="s">
+        <v>590</v>
       </c>
       <c r="C24" s="132">
         <v>1800</v>
       </c>
       <c r="D24" s="130" t="s">
-        <v>578</v>
+        <v>591</v>
       </c>
       <c r="E24" s="130">
         <v>1</v>
@@ -24103,7 +24233,7 @@
       <c r="I24" s="126"/>
       <c r="J24" s="126"/>
       <c r="K24" s="126" t="s">
-        <v>579</v>
+        <v>592</v>
       </c>
       <c r="L24" s="126">
         <v>14</v>
@@ -24128,13 +24258,13 @@
       <c r="AD24" s="128"/>
     </row>
     <row r="25" spans="1:30">
-      <c r="A25" s="169"/>
-      <c r="B25" s="164"/>
+      <c r="A25" s="181"/>
+      <c r="B25" s="176"/>
       <c r="C25" s="132">
         <v>2000</v>
       </c>
       <c r="D25" s="130" t="s">
-        <v>580</v>
+        <v>593</v>
       </c>
       <c r="E25" s="130"/>
       <c r="F25" s="130"/>
@@ -24143,7 +24273,7 @@
       <c r="I25" s="126"/>
       <c r="J25" s="126"/>
       <c r="K25" s="126" t="s">
-        <v>581</v>
+        <v>594</v>
       </c>
       <c r="L25" s="126">
         <v>12</v>
@@ -24179,7 +24309,7 @@
       <c r="I26" s="126"/>
       <c r="J26" s="126"/>
       <c r="K26" s="126" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="L26" s="126">
         <v>2</v>
@@ -24205,16 +24335,16 @@
     </row>
     <row r="27" spans="1:30">
       <c r="A27" s="134" t="s">
-        <v>558</v>
+        <v>571</v>
       </c>
       <c r="B27" s="126" t="s">
-        <v>582</v>
+        <v>595</v>
       </c>
       <c r="C27" s="126" t="s">
-        <v>578</v>
+        <v>591</v>
       </c>
       <c r="D27" s="126" t="s">
-        <v>580</v>
+        <v>593</v>
       </c>
       <c r="E27" s="126"/>
       <c r="F27" s="126"/>
@@ -24289,7 +24419,7 @@
     </row>
     <row r="29" spans="1:30">
       <c r="A29" s="134" t="s">
-        <v>583</v>
+        <v>596</v>
       </c>
       <c r="B29" s="127">
         <v>19813</v>
@@ -24307,7 +24437,7 @@
       <c r="I29" s="126"/>
       <c r="J29" s="126"/>
       <c r="K29" s="126" t="s">
-        <v>584</v>
+        <v>597</v>
       </c>
       <c r="L29" s="126"/>
       <c r="M29" s="126"/>
@@ -24331,7 +24461,7 @@
     </row>
     <row r="30" spans="1:30">
       <c r="A30" s="134" t="s">
-        <v>585</v>
+        <v>598</v>
       </c>
       <c r="B30" s="127">
         <v>19813</v>
@@ -24503,7 +24633,7 @@
     </row>
     <row r="35" spans="1:30">
       <c r="A35" s="134" t="s">
-        <v>586</v>
+        <v>599</v>
       </c>
       <c r="B35" s="126"/>
       <c r="C35" s="126"/>
@@ -24537,7 +24667,7 @@
     </row>
     <row r="36" spans="1:30">
       <c r="A36" s="134" t="s">
-        <v>587</v>
+        <v>600</v>
       </c>
       <c r="B36" s="126"/>
       <c r="C36" s="126"/>
@@ -24572,16 +24702,16 @@
     <row r="37" spans="1:30">
       <c r="A37" s="137"/>
       <c r="B37" s="138" t="s">
-        <v>588</v>
+        <v>601</v>
       </c>
       <c r="C37" s="138" t="s">
-        <v>411</v>
+        <v>427</v>
       </c>
       <c r="D37" s="138" t="s">
-        <v>365</v>
+        <v>424</v>
       </c>
       <c r="E37" s="139" t="s">
-        <v>589</v>
+        <v>602</v>
       </c>
       <c r="F37" s="126"/>
       <c r="G37" s="126"/>
@@ -24611,7 +24741,7 @@
     </row>
     <row r="38" spans="1:30">
       <c r="A38" s="140" t="s">
-        <v>590</v>
+        <v>603</v>
       </c>
       <c r="B38" s="141">
         <v>600</v>
@@ -24653,7 +24783,7 @@
     </row>
     <row r="39" spans="1:30">
       <c r="A39" s="143" t="s">
-        <v>591</v>
+        <v>604</v>
       </c>
       <c r="B39" s="144">
         <v>350</v>

--- a/data/Recruitment_Requisition.xlsx
+++ b/data/Recruitment_Requisition.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30425"/>
   <workbookPr hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://kubotagroup-my.sharepoint.com/personal/lapat_j_kubota_com/Documents/Documents/Recruitment Tools/Dashboard Data Report/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3544" documentId="8_{4185217D-4006-4629-AD3A-0737CE05813A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5DF28699-D34E-44BB-8FC4-5471B5FF98C6}"/>
+  <xr:revisionPtr revIDLastSave="3559" documentId="8_{4185217D-4006-4629-AD3A-0737CE05813A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0FD4E614-41C7-48D6-BD2C-D88188D12B54}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{5982D4A9-2AD8-4F8A-AE0B-0D729A27807E}"/>
   </bookViews>
@@ -19,7 +19,7 @@
     <sheet name="Cost Per Hire" sheetId="13" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Recruitment!$D$129:$D$129</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Recruitment!$C$128:$C$128</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -153,7 +153,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1911" uniqueCount="605">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1915" uniqueCount="607">
   <si>
     <t>Year</t>
   </si>
@@ -1317,6 +1317,12 @@
   </si>
   <si>
     <t>Communication Strategy</t>
+  </si>
+  <si>
+    <t>Domestic Communication - Tractor</t>
+  </si>
+  <si>
+    <t>ณอัญดา เกสรวิบูลย์</t>
   </si>
   <si>
     <t>ไฟนอล 1 Sep มี can แล้ว 2 คน ให้ส่งเพิ่ม 
@@ -5038,9 +5044,9 @@
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2A626EEB-FDFE-42FC-817A-963B6C771FE3}" name="Master" displayName="Master" ref="A1:AI122" totalsRowShown="0" headerRowDxfId="53" dataDxfId="52" tableBorderDxfId="51">
   <autoFilter ref="A1:AI122" xr:uid="{2A626EEB-FDFE-42FC-817A-963B6C771FE3}">
-    <filterColumn colId="23">
+    <filterColumn colId="0">
       <filters>
-        <filter val="Resign"/>
+        <filter val="2026"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -5602,7 +5608,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="2" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
+    <row r="2" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A2" s="46">
         <v>2024</v>
       </c>
@@ -5700,7 +5706,7 @@
       <c r="AH2" s="12"/>
       <c r="AI2" s="8"/>
     </row>
-    <row r="3" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
+    <row r="3" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A3" s="46">
         <v>2024</v>
       </c>
@@ -5792,7 +5798,7 @@
       <c r="AH3" s="12"/>
       <c r="AI3" s="8"/>
     </row>
-    <row r="4" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
+    <row r="4" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A4" s="46">
         <v>2024</v>
       </c>
@@ -5880,7 +5886,7 @@
       <c r="AH4" s="12"/>
       <c r="AI4" s="8"/>
     </row>
-    <row r="5" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
+    <row r="5" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A5" s="46">
         <v>2024</v>
       </c>
@@ -5970,7 +5976,7 @@
       <c r="AH5" s="12"/>
       <c r="AI5" s="8"/>
     </row>
-    <row r="6" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
+    <row r="6" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A6" s="46">
         <v>2024</v>
       </c>
@@ -6058,7 +6064,7 @@
       <c r="AH6" s="12"/>
       <c r="AI6" s="8"/>
     </row>
-    <row r="7" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
+    <row r="7" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A7" s="46">
         <v>2024</v>
       </c>
@@ -6146,7 +6152,7 @@
       <c r="AH7" s="12"/>
       <c r="AI7" s="8"/>
     </row>
-    <row r="8" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
+    <row r="8" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A8" s="46">
         <v>2024</v>
       </c>
@@ -6238,7 +6244,7 @@
       <c r="AH8" s="12"/>
       <c r="AI8" s="8"/>
     </row>
-    <row r="9" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
+    <row r="9" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A9" s="46">
         <v>2024</v>
       </c>
@@ -6324,7 +6330,7 @@
       <c r="AH9" s="12"/>
       <c r="AI9" s="8"/>
     </row>
-    <row r="10" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
+    <row r="10" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A10" s="46">
         <v>2024</v>
       </c>
@@ -6412,7 +6418,7 @@
       <c r="AH10" s="12"/>
       <c r="AI10" s="8"/>
     </row>
-    <row r="11" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
+    <row r="11" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A11" s="46">
         <v>2024</v>
       </c>
@@ -6502,7 +6508,7 @@
       <c r="AH11" s="12"/>
       <c r="AI11" s="8"/>
     </row>
-    <row r="12" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
+    <row r="12" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A12" s="46">
         <v>2024</v>
       </c>
@@ -6590,7 +6596,7 @@
       <c r="AH12" s="12"/>
       <c r="AI12" s="8"/>
     </row>
-    <row r="13" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
+    <row r="13" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A13" s="46">
         <v>2024</v>
       </c>
@@ -6680,7 +6686,7 @@
       <c r="AH13" s="12"/>
       <c r="AI13" s="8"/>
     </row>
-    <row r="14" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
+    <row r="14" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A14" s="46">
         <v>2024</v>
       </c>
@@ -6770,7 +6776,7 @@
       <c r="AH14" s="12"/>
       <c r="AI14" s="8"/>
     </row>
-    <row r="15" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
+    <row r="15" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A15" s="46">
         <v>2024</v>
       </c>
@@ -6858,7 +6864,7 @@
       <c r="AH15" s="12"/>
       <c r="AI15" s="8"/>
     </row>
-    <row r="16" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
+    <row r="16" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A16" s="46">
         <v>2024</v>
       </c>
@@ -6948,7 +6954,7 @@
       <c r="AH16" s="12"/>
       <c r="AI16" s="8"/>
     </row>
-    <row r="17" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
+    <row r="17" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A17" s="46">
         <v>2024</v>
       </c>
@@ -7036,7 +7042,7 @@
       <c r="AH17" s="12"/>
       <c r="AI17" s="8"/>
     </row>
-    <row r="18" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
+    <row r="18" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A18" s="46">
         <v>2024</v>
       </c>
@@ -7126,7 +7132,7 @@
       <c r="AH18" s="12"/>
       <c r="AI18" s="8"/>
     </row>
-    <row r="19" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
+    <row r="19" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A19" s="46">
         <v>2024</v>
       </c>
@@ -7216,7 +7222,7 @@
       <c r="AH19" s="12"/>
       <c r="AI19" s="8"/>
     </row>
-    <row r="20" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
+    <row r="20" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A20" s="46">
         <v>2024</v>
       </c>
@@ -7306,7 +7312,7 @@
       <c r="AH20" s="12"/>
       <c r="AI20" s="8"/>
     </row>
-    <row r="21" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
+    <row r="21" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A21" s="46">
         <v>2025</v>
       </c>
@@ -7398,7 +7404,7 @@
       <c r="AH21" s="12"/>
       <c r="AI21" s="8"/>
     </row>
-    <row r="22" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
+    <row r="22" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A22" s="46">
         <v>2025</v>
       </c>
@@ -7490,7 +7496,7 @@
       <c r="AH22" s="12"/>
       <c r="AI22" s="8"/>
     </row>
-    <row r="23" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
+    <row r="23" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A23" s="46">
         <v>2025</v>
       </c>
@@ -7582,7 +7588,7 @@
       <c r="AH23" s="12"/>
       <c r="AI23" s="8"/>
     </row>
-    <row r="24" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
+    <row r="24" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A24" s="46">
         <v>2025</v>
       </c>
@@ -7674,7 +7680,7 @@
       <c r="AH24" s="12"/>
       <c r="AI24" s="8"/>
     </row>
-    <row r="25" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
+    <row r="25" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A25" s="46">
         <v>2025</v>
       </c>
@@ -7766,7 +7772,7 @@
       <c r="AH25" s="12"/>
       <c r="AI25" s="8"/>
     </row>
-    <row r="26" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
+    <row r="26" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A26" s="46">
         <v>2025</v>
       </c>
@@ -7858,7 +7864,7 @@
       <c r="AH26" s="12"/>
       <c r="AI26" s="8"/>
     </row>
-    <row r="27" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
+    <row r="27" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A27" s="46">
         <v>2025</v>
       </c>
@@ -7950,7 +7956,7 @@
       <c r="AH27" s="12"/>
       <c r="AI27" s="8"/>
     </row>
-    <row r="28" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
+    <row r="28" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A28" s="46">
         <v>2025</v>
       </c>
@@ -8044,7 +8050,7 @@
       <c r="AH28" s="12"/>
       <c r="AI28" s="8"/>
     </row>
-    <row r="29" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
+    <row r="29" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A29" s="46">
         <v>2025</v>
       </c>
@@ -8136,7 +8142,7 @@
       <c r="AH29" s="12"/>
       <c r="AI29" s="8"/>
     </row>
-    <row r="30" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
+    <row r="30" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A30" s="46">
         <v>2025</v>
       </c>
@@ -8230,7 +8236,7 @@
       <c r="AH30" s="12"/>
       <c r="AI30" s="8"/>
     </row>
-    <row r="31" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
+    <row r="31" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A31" s="46">
         <v>2025</v>
       </c>
@@ -8328,7 +8334,7 @@
       <c r="AH31" s="12"/>
       <c r="AI31" s="8"/>
     </row>
-    <row r="32" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
+    <row r="32" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A32" s="46">
         <v>2025</v>
       </c>
@@ -8422,7 +8428,7 @@
       <c r="AH32" s="12"/>
       <c r="AI32" s="8"/>
     </row>
-    <row r="33" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
+    <row r="33" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A33" s="46">
         <v>2025</v>
       </c>
@@ -8514,7 +8520,7 @@
       <c r="AH33" s="12"/>
       <c r="AI33" s="8"/>
     </row>
-    <row r="34" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
+    <row r="34" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A34" s="46">
         <v>2025</v>
       </c>
@@ -8614,7 +8620,7 @@
       <c r="AH34" s="12"/>
       <c r="AI34" s="8"/>
     </row>
-    <row r="35" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
+    <row r="35" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A35" s="46">
         <v>2025</v>
       </c>
@@ -8708,7 +8714,7 @@
       <c r="AH35" s="12"/>
       <c r="AI35" s="8"/>
     </row>
-    <row r="36" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
+    <row r="36" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A36" s="46">
         <v>2025</v>
       </c>
@@ -8802,7 +8808,7 @@
       <c r="AH36" s="12"/>
       <c r="AI36" s="8"/>
     </row>
-    <row r="37" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
+    <row r="37" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A37" s="46">
         <v>2025</v>
       </c>
@@ -8861,7 +8867,7 @@
       Dropdown!$A$2:$A$100
    )
 )</f>
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="Q37" s="13" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -8886,7 +8892,7 @@
       <c r="AH37" s="12"/>
       <c r="AI37" s="8"/>
     </row>
-    <row r="38" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
+    <row r="38" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A38" s="46">
         <v>2025</v>
       </c>
@@ -8978,7 +8984,7 @@
       <c r="AH38" s="12"/>
       <c r="AI38" s="8"/>
     </row>
-    <row r="39" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
+    <row r="39" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A39" s="46">
         <v>2025</v>
       </c>
@@ -9068,7 +9074,7 @@
       <c r="AH39" s="12"/>
       <c r="AI39" s="8"/>
     </row>
-    <row r="40" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
+    <row r="40" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A40" s="46">
         <v>2025</v>
       </c>
@@ -9158,7 +9164,7 @@
       <c r="AH40" s="12"/>
       <c r="AI40" s="8"/>
     </row>
-    <row r="41" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
+    <row r="41" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A41" s="46">
         <v>2025</v>
       </c>
@@ -9250,7 +9256,7 @@
       <c r="AH41" s="12"/>
       <c r="AI41" s="8"/>
     </row>
-    <row r="42" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
+    <row r="42" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A42" s="46">
         <v>2025</v>
       </c>
@@ -9342,7 +9348,7 @@
       <c r="AH42" s="12"/>
       <c r="AI42" s="8"/>
     </row>
-    <row r="43" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
+    <row r="43" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A43" s="46">
         <v>2025</v>
       </c>
@@ -9434,7 +9440,7 @@
       <c r="AH43" s="12"/>
       <c r="AI43" s="8"/>
     </row>
-    <row r="44" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
+    <row r="44" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A44" s="46">
         <v>2025</v>
       </c>
@@ -9526,7 +9532,7 @@
       <c r="AH44" s="12"/>
       <c r="AI44" s="8"/>
     </row>
-    <row r="45" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
+    <row r="45" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A45" s="46">
         <v>2025</v>
       </c>
@@ -9618,7 +9624,7 @@
       <c r="AH45" s="12"/>
       <c r="AI45" s="8"/>
     </row>
-    <row r="46" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
+    <row r="46" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A46" s="46">
         <v>2025</v>
       </c>
@@ -9710,7 +9716,7 @@
       <c r="AH46" s="12"/>
       <c r="AI46" s="8"/>
     </row>
-    <row r="47" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
+    <row r="47" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A47" s="46">
         <v>2025</v>
       </c>
@@ -9798,7 +9804,7 @@
       <c r="AH47" s="12"/>
       <c r="AI47" s="8"/>
     </row>
-    <row r="48" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
+    <row r="48" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A48" s="46">
         <v>2025</v>
       </c>
@@ -9892,7 +9898,7 @@
       <c r="AH48" s="12"/>
       <c r="AI48" s="8"/>
     </row>
-    <row r="49" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
+    <row r="49" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A49" s="46">
         <v>2025</v>
       </c>
@@ -9986,7 +9992,7 @@
       <c r="AH49" s="12"/>
       <c r="AI49" s="8"/>
     </row>
-    <row r="50" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
+    <row r="50" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A50" s="46">
         <v>2025</v>
       </c>
@@ -10078,7 +10084,7 @@
       <c r="AH50" s="12"/>
       <c r="AI50" s="8"/>
     </row>
-    <row r="51" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
+    <row r="51" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A51" s="46">
         <v>2025</v>
       </c>
@@ -10170,7 +10176,7 @@
       <c r="AH51" s="12"/>
       <c r="AI51" s="8"/>
     </row>
-    <row r="52" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
+    <row r="52" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A52" s="46">
         <v>2025</v>
       </c>
@@ -10262,7 +10268,7 @@
       <c r="AH52" s="12"/>
       <c r="AI52" s="8"/>
     </row>
-    <row r="53" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
+    <row r="53" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A53" s="46">
         <v>2025</v>
       </c>
@@ -10350,7 +10356,7 @@
       <c r="AH53" s="12"/>
       <c r="AI53" s="8"/>
     </row>
-    <row r="54" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
+    <row r="54" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A54" s="46">
         <v>2025</v>
       </c>
@@ -10440,7 +10446,7 @@
       <c r="AH54" s="12"/>
       <c r="AI54" s="8"/>
     </row>
-    <row r="55" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
+    <row r="55" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A55" s="46">
         <v>2025</v>
       </c>
@@ -10530,7 +10536,7 @@
       <c r="AH55" s="12"/>
       <c r="AI55" s="8"/>
     </row>
-    <row r="56" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
+    <row r="56" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A56" s="46">
         <v>2025</v>
       </c>
@@ -10618,7 +10624,7 @@
       <c r="AH56" s="12"/>
       <c r="AI56" s="8"/>
     </row>
-    <row r="57" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
+    <row r="57" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A57" s="46">
         <v>2025</v>
       </c>
@@ -10706,7 +10712,7 @@
       <c r="AH57" s="12"/>
       <c r="AI57" s="8"/>
     </row>
-    <row r="58" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
+    <row r="58" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A58" s="46">
         <v>2025</v>
       </c>
@@ -10798,7 +10804,7 @@
       <c r="AH58" s="12"/>
       <c r="AI58" s="8"/>
     </row>
-    <row r="59" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
+    <row r="59" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A59" s="46">
         <v>2025</v>
       </c>
@@ -10892,7 +10898,7 @@
       <c r="AH59" s="12"/>
       <c r="AI59" s="8"/>
     </row>
-    <row r="60" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
+    <row r="60" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A60" s="46">
         <v>2025</v>
       </c>
@@ -10986,7 +10992,7 @@
       <c r="AH60" s="12"/>
       <c r="AI60" s="8"/>
     </row>
-    <row r="61" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
+    <row r="61" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A61" s="46">
         <v>2025</v>
       </c>
@@ -11076,7 +11082,7 @@
       <c r="AH61" s="12"/>
       <c r="AI61" s="8"/>
     </row>
-    <row r="62" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
+    <row r="62" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A62" s="46">
         <v>2025</v>
       </c>
@@ -11166,7 +11172,7 @@
       <c r="AH62" s="12"/>
       <c r="AI62" s="8"/>
     </row>
-    <row r="63" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
+    <row r="63" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A63" s="46">
         <v>2025</v>
       </c>
@@ -11256,7 +11262,7 @@
       <c r="AH63" s="12"/>
       <c r="AI63" s="8"/>
     </row>
-    <row r="64" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
+    <row r="64" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A64" s="46">
         <v>2025</v>
       </c>
@@ -11350,7 +11356,7 @@
       <c r="AH64" s="12"/>
       <c r="AI64" s="8"/>
     </row>
-    <row r="65" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
+    <row r="65" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A65" s="46">
         <v>2025</v>
       </c>
@@ -11444,7 +11450,7 @@
       <c r="AH65" s="12"/>
       <c r="AI65" s="8"/>
     </row>
-    <row r="66" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
+    <row r="66" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A66" s="46">
         <v>2025</v>
       </c>
@@ -11546,7 +11552,7 @@
       <c r="AH66" s="12"/>
       <c r="AI66" s="8"/>
     </row>
-    <row r="67" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
+    <row r="67" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A67" s="46">
         <v>2025</v>
       </c>
@@ -11638,7 +11644,7 @@
       <c r="AH67" s="12"/>
       <c r="AI67" s="8"/>
     </row>
-    <row r="68" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
+    <row r="68" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A68" s="46">
         <v>2025</v>
       </c>
@@ -11730,7 +11736,7 @@
       <c r="AH68" s="12"/>
       <c r="AI68" s="8"/>
     </row>
-    <row r="69" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
+    <row r="69" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A69" s="46">
         <v>2025</v>
       </c>
@@ -11822,7 +11828,7 @@
       <c r="AH69" s="12"/>
       <c r="AI69" s="8"/>
     </row>
-    <row r="70" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
+    <row r="70" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A70" s="46">
         <v>2025</v>
       </c>
@@ -11883,7 +11889,7 @@
       Dropdown!$A$2:$A$100
    )
 )</f>
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="Q70" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -11912,7 +11918,7 @@
       <c r="AH70" s="12"/>
       <c r="AI70" s="8"/>
     </row>
-    <row r="71" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
+    <row r="71" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A71" s="46">
         <v>2025</v>
       </c>
@@ -12006,7 +12012,7 @@
       <c r="AH71" s="12"/>
       <c r="AI71" s="8"/>
     </row>
-    <row r="72" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
+    <row r="72" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A72" s="46">
         <v>2025</v>
       </c>
@@ -12100,7 +12106,7 @@
       <c r="AH72" s="12"/>
       <c r="AI72" s="8"/>
     </row>
-    <row r="73" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
+    <row r="73" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A73" s="46">
         <v>2025</v>
       </c>
@@ -12194,7 +12200,7 @@
       <c r="AH73" s="12"/>
       <c r="AI73" s="8"/>
     </row>
-    <row r="74" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
+    <row r="74" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A74" s="46">
         <v>2025</v>
       </c>
@@ -12288,7 +12294,7 @@
       <c r="AH74" s="12"/>
       <c r="AI74" s="8"/>
     </row>
-    <row r="75" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
+    <row r="75" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A75" s="46">
         <v>2025</v>
       </c>
@@ -12384,7 +12390,7 @@
       <c r="AH75" s="12"/>
       <c r="AI75" s="8"/>
     </row>
-    <row r="76" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
+    <row r="76" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A76" s="46">
         <v>2025</v>
       </c>
@@ -12478,7 +12484,7 @@
       <c r="AH76" s="17"/>
       <c r="AI76" s="8"/>
     </row>
-    <row r="77" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
+    <row r="77" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A77" s="46">
         <v>2025</v>
       </c>
@@ -12576,7 +12582,7 @@
       <c r="AH77" s="17"/>
       <c r="AI77" s="8"/>
     </row>
-    <row r="78" spans="1:35" s="11" customFormat="1" ht="30" customHeight="1">
+    <row r="78" spans="1:35" s="11" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A78" s="46">
         <v>2025</v>
       </c>
@@ -12676,7 +12682,7 @@
       <c r="AH78" s="12"/>
       <c r="AI78" s="8"/>
     </row>
-    <row r="79" spans="1:35" s="11" customFormat="1" ht="30" customHeight="1">
+    <row r="79" spans="1:35" s="11" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A79" s="46">
         <v>2025</v>
       </c>
@@ -12770,7 +12776,7 @@
       <c r="AH79" s="12"/>
       <c r="AI79" s="8"/>
     </row>
-    <row r="80" spans="1:35" s="11" customFormat="1" ht="30" customHeight="1">
+    <row r="80" spans="1:35" s="11" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A80" s="46">
         <v>2025</v>
       </c>
@@ -12862,7 +12868,7 @@
       <c r="AH80" s="17"/>
       <c r="AI80" s="8"/>
     </row>
-    <row r="81" spans="1:35" s="11" customFormat="1" ht="30" customHeight="1">
+    <row r="81" spans="1:35" s="11" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A81" s="46">
         <v>2025</v>
       </c>
@@ -12956,7 +12962,7 @@
       <c r="AH81" s="12"/>
       <c r="AI81" s="8"/>
     </row>
-    <row r="82" spans="1:35" s="11" customFormat="1" ht="30" customHeight="1">
+    <row r="82" spans="1:35" s="11" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A82" s="46">
         <v>2025</v>
       </c>
@@ -13044,7 +13050,7 @@
       <c r="AH82" s="17"/>
       <c r="AI82" s="8"/>
     </row>
-    <row r="83" spans="1:35" s="11" customFormat="1" ht="30" customHeight="1">
+    <row r="83" spans="1:35" s="11" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A83" s="46">
         <v>2025</v>
       </c>
@@ -13138,7 +13144,7 @@
       <c r="AH83" s="17"/>
       <c r="AI83" s="8"/>
     </row>
-    <row r="84" spans="1:35" s="11" customFormat="1" ht="30" customHeight="1">
+    <row r="84" spans="1:35" s="11" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A84" s="46">
         <v>2025</v>
       </c>
@@ -13232,7 +13238,7 @@
       <c r="AH84" s="17"/>
       <c r="AI84" s="8"/>
     </row>
-    <row r="85" spans="1:35" s="11" customFormat="1" ht="30" customHeight="1">
+    <row r="85" spans="1:35" s="11" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A85" s="46">
         <v>2025</v>
       </c>
@@ -13326,7 +13332,7 @@
       <c r="AH85" s="17"/>
       <c r="AI85" s="8"/>
     </row>
-    <row r="86" spans="1:35" s="11" customFormat="1" ht="30" customHeight="1">
+    <row r="86" spans="1:35" s="11" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A86" s="46">
         <v>2025</v>
       </c>
@@ -13424,7 +13430,7 @@
       <c r="AH86" s="17"/>
       <c r="AI86" s="8"/>
     </row>
-    <row r="87" spans="1:35" s="11" customFormat="1" ht="30" customHeight="1">
+    <row r="87" spans="1:35" s="11" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A87" s="46">
         <v>2025</v>
       </c>
@@ -13518,7 +13524,7 @@
       <c r="AH87" s="17"/>
       <c r="AI87" s="8"/>
     </row>
-    <row r="88" spans="1:35" s="11" customFormat="1" ht="30" customHeight="1">
+    <row r="88" spans="1:35" s="11" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A88" s="46">
         <v>2025</v>
       </c>
@@ -13612,7 +13618,7 @@
       <c r="AH88" s="17"/>
       <c r="AI88" s="8"/>
     </row>
-    <row r="89" spans="1:35" s="11" customFormat="1" ht="30" customHeight="1">
+    <row r="89" spans="1:35" s="11" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A89" s="46">
         <v>2025</v>
       </c>
@@ -13706,7 +13712,7 @@
       <c r="AH89" s="17"/>
       <c r="AI89" s="8"/>
     </row>
-    <row r="90" spans="1:35" s="11" customFormat="1" ht="30" customHeight="1">
+    <row r="90" spans="1:35" s="11" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A90" s="46">
         <v>2025</v>
       </c>
@@ -13800,7 +13806,7 @@
       <c r="AH90" s="17"/>
       <c r="AI90" s="8"/>
     </row>
-    <row r="91" spans="1:35" s="11" customFormat="1" ht="30" customHeight="1">
+    <row r="91" spans="1:35" s="11" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A91" s="46">
         <v>2025</v>
       </c>
@@ -13892,7 +13898,7 @@
       <c r="AH91" s="17"/>
       <c r="AI91" s="8"/>
     </row>
-    <row r="92" spans="1:35" s="11" customFormat="1" ht="30" customHeight="1">
+    <row r="92" spans="1:35" s="11" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A92" s="46">
         <v>2025</v>
       </c>
@@ -13953,7 +13959,7 @@
       Dropdown!$A$2:$A$100
    )
 )</f>
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="Q92" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -13984,7 +13990,7 @@
       <c r="AH92" s="17"/>
       <c r="AI92" s="8"/>
     </row>
-    <row r="93" spans="1:35" s="11" customFormat="1" ht="30" customHeight="1">
+    <row r="93" spans="1:35" s="11" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A93" s="46">
         <v>2025</v>
       </c>
@@ -14072,7 +14078,7 @@
       <c r="AH93" s="17"/>
       <c r="AI93" s="8"/>
     </row>
-    <row r="94" spans="1:35" s="11" customFormat="1" ht="30" customHeight="1">
+    <row r="94" spans="1:35" s="11" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A94" s="46">
         <v>2025</v>
       </c>
@@ -14166,7 +14172,7 @@
       <c r="AH94" s="17"/>
       <c r="AI94" s="8"/>
     </row>
-    <row r="95" spans="1:35" s="11" customFormat="1" ht="30" customHeight="1">
+    <row r="95" spans="1:35" s="11" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A95" s="46">
         <v>2025</v>
       </c>
@@ -14260,7 +14266,7 @@
       <c r="AH95" s="17"/>
       <c r="AI95" s="8"/>
     </row>
-    <row r="96" spans="1:35" s="11" customFormat="1" ht="30" customHeight="1">
+    <row r="96" spans="1:35" s="11" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A96" s="46">
         <v>2025</v>
       </c>
@@ -14319,7 +14325,7 @@
       Dropdown!$A$2:$A$100
    )
 )</f>
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="Q96" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -14350,7 +14356,7 @@
       <c r="AH96" s="17"/>
       <c r="AI96" s="8"/>
     </row>
-    <row r="97" spans="1:35" s="11" customFormat="1" ht="30" customHeight="1">
+    <row r="97" spans="1:35" s="11" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A97" s="46">
         <v>2025</v>
       </c>
@@ -14411,7 +14417,7 @@
       Dropdown!$A$2:$A$100
    )
 )</f>
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="Q97" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -14440,7 +14446,7 @@
       <c r="AH97" s="17"/>
       <c r="AI97" s="8"/>
     </row>
-    <row r="98" spans="1:35" s="11" customFormat="1" ht="30" customHeight="1">
+    <row r="98" spans="1:35" s="11" customFormat="1" ht="30" hidden="1" customHeight="1">
       <c r="A98" s="46">
         <v>2025</v>
       </c>
@@ -15903,7 +15909,7 @@
       Dropdown!$A$2:$A$100
    )
 )</f>
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="Q112" s="59" t="str">
         <f t="shared" ca="1" si="6"/>
@@ -16360,7 +16366,9 @@
       <c r="G117" s="70" t="s">
         <v>160</v>
       </c>
-      <c r="H117" s="97"/>
+      <c r="H117" s="97" t="s">
+        <v>388</v>
+      </c>
       <c r="I117" s="96" t="s">
         <v>41</v>
       </c>
@@ -16371,7 +16379,7 @@
         <v>52</v>
       </c>
       <c r="L117" s="96" t="s">
-        <v>369</v>
+        <v>363</v>
       </c>
       <c r="M117" s="98">
         <v>46226</v>
@@ -16412,18 +16420,22 @@
       </c>
       <c r="T117" s="97"/>
       <c r="U117" s="97"/>
-      <c r="V117" s="115"/>
-      <c r="W117" s="100"/>
+      <c r="V117" s="115" t="s">
+        <v>389</v>
+      </c>
+      <c r="W117" s="100">
+        <v>46296</v>
+      </c>
       <c r="X117" s="97" t="s">
         <v>324</v>
       </c>
       <c r="Y117" s="101"/>
       <c r="Z117" s="96"/>
       <c r="AA117" s="96" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="AB117" s="146" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="AC117" s="102"/>
       <c r="AD117" s="102"/>
@@ -16432,7 +16444,7 @@
       <c r="AG117" s="103"/>
       <c r="AH117" s="104"/>
       <c r="AI117" s="108" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="118" spans="1:35" s="105" customFormat="1" ht="30" customHeight="1">
@@ -16515,7 +16527,7 @@
       </c>
       <c r="U118" s="97"/>
       <c r="V118" s="115" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="W118" s="100"/>
       <c r="X118" s="97" t="s">
@@ -16525,7 +16537,7 @@
       <c r="Z118" s="96"/>
       <c r="AA118" s="97"/>
       <c r="AB118" s="97" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AC118" s="102"/>
       <c r="AD118" s="102"/>
@@ -16534,7 +16546,7 @@
       <c r="AG118" s="103"/>
       <c r="AH118" s="104"/>
       <c r="AI118" s="108" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="119" spans="1:35" s="105" customFormat="1" ht="30" customHeight="1">
@@ -16552,7 +16564,7 @@
         <v>46</v>
       </c>
       <c r="E119" s="97" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="F119" s="97" t="s">
         <v>61</v>
@@ -16561,7 +16573,7 @@
         <v>104</v>
       </c>
       <c r="H119" s="97" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="I119" s="96" t="s">
         <v>41</v>
@@ -16611,11 +16623,11 @@
         <v>15647</v>
       </c>
       <c r="T119" s="97" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="U119" s="97"/>
       <c r="V119" s="115" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="W119" s="100"/>
       <c r="X119" s="97" t="s">
@@ -16625,7 +16637,7 @@
       <c r="Z119" s="96"/>
       <c r="AA119" s="97"/>
       <c r="AB119" s="96" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="AC119" s="102"/>
       <c r="AD119" s="102"/>
@@ -16634,7 +16646,7 @@
       <c r="AG119" s="103"/>
       <c r="AH119" s="104"/>
       <c r="AI119" s="108" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="120" spans="1:35" ht="30" customHeight="1">
@@ -16652,7 +16664,7 @@
         <v>377</v>
       </c>
       <c r="E120" s="97" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="F120" s="97" t="s">
         <v>178</v>
@@ -16661,7 +16673,7 @@
         <v>179</v>
       </c>
       <c r="H120" s="97" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="I120" s="96" t="s">
         <v>41</v>
@@ -16698,7 +16710,7 @@
       Dropdown!$A$2:$A$100
    )
 )</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Q120" s="96" t="str">
         <f ca="1">IF(P120="",                                                                                                                                                                                                   "",
@@ -16712,7 +16724,9 @@
 )</f>
         <v>ON KPI</v>
       </c>
-      <c r="R120" s="96"/>
+      <c r="R120" s="96" t="s">
+        <v>347</v>
+      </c>
       <c r="S120" s="97">
         <v>16257</v>
       </c>
@@ -16747,19 +16761,19 @@
         <v>35</v>
       </c>
       <c r="D121" s="97" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="E121" s="97" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="F121" s="97" t="s">
         <v>87</v>
       </c>
       <c r="G121" s="97" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="H121" s="97" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="I121" s="96" t="s">
         <v>41</v>
@@ -16796,7 +16810,7 @@
       Dropdown!$A$2:$A$100
    )
 )</f>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="Q121" s="96" t="str">
         <f ca="1">IF(P121="",                                                                                                                                                                                                   "",
@@ -16811,13 +16825,13 @@
         <v>ON KPI</v>
       </c>
       <c r="R121" s="96" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="S121" s="97">
         <v>16122</v>
       </c>
       <c r="T121" s="97" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="U121" s="97"/>
       <c r="V121" s="97"/>
@@ -16829,7 +16843,7 @@
       <c r="Z121" s="96"/>
       <c r="AA121" s="97"/>
       <c r="AB121" s="97" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="AC121" s="102"/>
       <c r="AD121" s="102"/>
@@ -16838,10 +16852,10 @@
       <c r="AG121" s="103"/>
       <c r="AH121" s="104"/>
       <c r="AI121" s="108" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="122" spans="1:35" ht="20.25" customHeight="1">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="122" spans="1:35" ht="20.25" hidden="1" customHeight="1">
       <c r="A122" s="149"/>
       <c r="B122" s="147" t="str">
         <f>IF(M122="", "", TEXT(M122, "[$-en-US]mmmm"))</f>
@@ -16912,7 +16926,7 @@
       <c r="AI122" s="156"/>
     </row>
   </sheetData>
-  <autoFilter ref="D129" xr:uid="{817CD080-0396-428F-B39B-215D57916061}"/>
+  <autoFilter ref="C128" xr:uid="{817CD080-0396-428F-B39B-215D57916061}"/>
   <phoneticPr fontId="5" type="noConversion"/>
   <conditionalFormatting sqref="I1:I1048576">
     <cfRule type="containsText" dxfId="62" priority="3" operator="containsText" text="Special">
@@ -17067,46 +17081,46 @@
   <sheetData>
     <row r="1" spans="1:14">
       <c r="A1" s="3" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>72</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>9</v>
       </c>
       <c r="J1" s="6" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="K1" s="6" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="L1" s="7" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="M1" s="1" t="s">
         <v>23</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="84">
@@ -17144,7 +17158,7 @@
         <v>179</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="M2" s="1" t="s">
         <v>118</v>
@@ -17167,7 +17181,7 @@
         <v>45</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>53</v>
@@ -17179,7 +17193,7 @@
         <v>191</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>186</v>
@@ -17188,13 +17202,13 @@
         <v>234</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="M3" s="1" t="s">
         <v>203</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="84.6" thickBot="1">
@@ -17205,13 +17219,13 @@
         <v>82</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>54</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>72</v>
@@ -17229,7 +17243,7 @@
         <v>230</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="M4" s="1" t="s">
         <v>191</v>
@@ -17243,13 +17257,13 @@
         <v>46026</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="K5" s="2" t="s">
         <v>290</v>
@@ -17261,7 +17275,7 @@
         <v>151</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="84">
@@ -17272,22 +17286,22 @@
         <v>369</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>120</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="M6" s="1" t="s">
         <v>324</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="63.6" thickBot="1">
@@ -17298,16 +17312,16 @@
         <v>84</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>181</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="M7" s="1" t="s">
         <v>72</v>
@@ -17330,10 +17344,10 @@
         <v>128</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="84.6" thickBot="1">
@@ -17341,7 +17355,7 @@
         <v>46040</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>164</v>
@@ -17353,7 +17367,7 @@
         <v>121</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="84.6" thickBot="1">
@@ -17364,13 +17378,13 @@
         <v>139</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="K10" s="2" t="s">
         <v>182</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="105.6" thickBot="1">
@@ -17384,7 +17398,7 @@
         <v>125</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="42.6" thickBot="1">
@@ -17398,7 +17412,7 @@
         <v>175</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="63.6" thickBot="1">
@@ -17412,7 +17426,7 @@
         <v>129</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="84.6" thickBot="1">
@@ -17426,7 +17440,7 @@
         <v>49</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="84.6" thickBot="1">
@@ -17440,7 +17454,7 @@
         <v>187</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="63.6" thickBot="1">
@@ -17454,7 +17468,7 @@
         <v>133</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
     </row>
     <row r="17" spans="1:12" ht="84.6" thickBot="1">
@@ -17479,10 +17493,10 @@
         <v>87</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="19" spans="1:12" ht="84.6" thickBot="1">
@@ -17493,10 +17507,10 @@
         <v>79</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
     </row>
     <row r="20" spans="1:12" ht="84.6" thickBot="1">
@@ -17507,10 +17521,10 @@
         <v>90</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
     </row>
     <row r="21" spans="1:12" ht="105.6" thickBot="1">
@@ -17521,10 +17535,10 @@
         <v>38</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
     </row>
     <row r="22" spans="1:12" ht="63.6" thickBot="1">
@@ -17535,10 +17549,10 @@
         <v>300</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="23" spans="1:12" ht="84.6" thickBot="1">
@@ -17549,10 +17563,10 @@
         <v>214</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="24" spans="1:12" ht="63.6" thickBot="1">
@@ -17566,7 +17580,7 @@
         <v>171</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
     </row>
     <row r="25" spans="1:12" ht="63.6" thickBot="1">
@@ -17577,10 +17591,10 @@
         <v>295</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="26" spans="1:12" ht="63.6" thickBot="1">
@@ -17591,10 +17605,10 @@
         <v>341</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
     </row>
     <row r="27" spans="1:12" ht="84">
@@ -17620,7 +17634,7 @@
         <v>81</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="29" spans="1:12" ht="84.6" thickBot="1">
@@ -17644,7 +17658,7 @@
         <v>67</v>
       </c>
       <c r="L30" s="2" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
     </row>
     <row r="31" spans="1:12" ht="84.6" thickBot="1">
@@ -17656,7 +17670,7 @@
         <v>57</v>
       </c>
       <c r="L31" s="2" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
     </row>
     <row r="32" spans="1:12" ht="42.6" thickBot="1">
@@ -17668,7 +17682,7 @@
         <v>70</v>
       </c>
       <c r="L32" s="2" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="33" spans="1:12" ht="63.6" thickBot="1">
@@ -17680,7 +17694,7 @@
         <v>76</v>
       </c>
       <c r="L33" s="2" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="34" spans="1:12" ht="63.6" thickBot="1">
@@ -17692,7 +17706,7 @@
         <v>99</v>
       </c>
       <c r="L34" s="2" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="35" spans="1:12" ht="63.6" thickBot="1">
@@ -17704,7 +17718,7 @@
         <v>80</v>
       </c>
       <c r="L35" s="2" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="36" spans="1:12" ht="42.6" thickBot="1">
@@ -17716,7 +17730,7 @@
         <v>94</v>
       </c>
       <c r="L36" s="2" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="37" spans="1:12" ht="63.6" thickBot="1">
@@ -17728,7 +17742,7 @@
         <v>91</v>
       </c>
       <c r="L37" s="2" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
     </row>
     <row r="38" spans="1:12" ht="63.6" thickBot="1">
@@ -17740,7 +17754,7 @@
         <v>97</v>
       </c>
       <c r="L38" s="2" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
     </row>
     <row r="39" spans="1:12" ht="63.6" thickBot="1">
@@ -17752,7 +17766,7 @@
         <v>39</v>
       </c>
       <c r="L39" s="2" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
     </row>
     <row r="40" spans="1:12" ht="84.6" thickBot="1">
@@ -17761,7 +17775,7 @@
       </c>
       <c r="J40" s="2"/>
       <c r="K40" s="2" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="L40" s="2" t="s">
         <v>235</v>
@@ -17776,7 +17790,7 @@
         <v>104</v>
       </c>
       <c r="L41" s="2" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="42" spans="1:12" ht="63.6" thickBot="1">
@@ -17788,7 +17802,7 @@
         <v>101</v>
       </c>
       <c r="L42" s="2" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
     </row>
     <row r="43" spans="1:12" ht="84.6" thickBot="1">
@@ -17800,7 +17814,7 @@
         <v>112</v>
       </c>
       <c r="L43" s="2" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="44" spans="1:12" ht="42.6" thickBot="1">
@@ -17824,7 +17838,7 @@
         <v>258</v>
       </c>
       <c r="L45" s="2" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="46" spans="1:12" ht="42.6" thickBot="1">
@@ -17836,7 +17850,7 @@
         <v>144</v>
       </c>
       <c r="L46" s="2" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
     </row>
     <row r="47" spans="1:12" ht="84.6" thickBot="1">
@@ -17848,7 +17862,7 @@
         <v>137</v>
       </c>
       <c r="L47" s="2" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
     <row r="48" spans="1:12" ht="42.6" thickBot="1">
@@ -17857,10 +17871,10 @@
       </c>
       <c r="J48" s="2"/>
       <c r="K48" s="2" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="L48" s="2" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
     </row>
     <row r="49" spans="1:12" ht="42.6" thickBot="1">
@@ -17869,7 +17883,7 @@
       </c>
       <c r="J49" s="2"/>
       <c r="K49" s="2" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="L49" s="2" t="s">
         <v>180</v>
@@ -17884,7 +17898,7 @@
         <v>274</v>
       </c>
       <c r="L50" s="2" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="51" spans="1:12" ht="105.6" thickBot="1">
@@ -17917,10 +17931,10 @@
       </c>
       <c r="J53" s="2"/>
       <c r="K53" s="2" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="L53" s="2" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
     </row>
     <row r="54" spans="1:12" ht="63.6" thickBot="1">
@@ -17932,7 +17946,7 @@
         <v>148</v>
       </c>
       <c r="L54" s="2" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="55" spans="1:12" ht="63.6" thickBot="1">
@@ -17941,10 +17955,10 @@
       </c>
       <c r="J55" s="2"/>
       <c r="K55" s="2" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="L55" s="2" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
     </row>
     <row r="56" spans="1:12" ht="63.6" thickBot="1">
@@ -17953,10 +17967,10 @@
       </c>
       <c r="J56" s="2"/>
       <c r="K56" s="2" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="L56" s="2" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="57" spans="1:12" ht="105.6" thickBot="1">
@@ -17968,7 +17982,7 @@
         <v>223</v>
       </c>
       <c r="L57" s="2" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
     </row>
     <row r="58" spans="1:12" ht="84.6" thickBot="1">
@@ -17980,7 +17994,7 @@
         <v>264</v>
       </c>
       <c r="L58" s="2" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
     </row>
     <row r="59" spans="1:12" ht="63.6" thickBot="1">
@@ -17992,7 +18006,7 @@
         <v>106</v>
       </c>
       <c r="L59" s="2" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
     </row>
     <row r="60" spans="1:12" ht="63.6" thickBot="1">
@@ -18001,10 +18015,10 @@
       </c>
       <c r="J60" s="2"/>
       <c r="K60" s="2" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="L60" s="2" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
     </row>
     <row r="61" spans="1:12" ht="84.6" thickBot="1">
@@ -18016,7 +18030,7 @@
         <v>198</v>
       </c>
       <c r="L61" s="2" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
     </row>
     <row r="62" spans="1:12" ht="84.6" thickBot="1">
@@ -18028,7 +18042,7 @@
         <v>242</v>
       </c>
       <c r="L62" s="2" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
     </row>
     <row r="63" spans="1:12" ht="63.6" thickBot="1">
@@ -18037,10 +18051,10 @@
       </c>
       <c r="J63" s="2"/>
       <c r="K63" s="2" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="L63" s="2" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="64" spans="1:12" ht="63.6" thickBot="1">
@@ -18052,7 +18066,7 @@
         <v>160</v>
       </c>
       <c r="L64" s="2" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
     </row>
     <row r="65" spans="1:12" ht="42.6" thickBot="1">
@@ -18061,7 +18075,7 @@
       </c>
       <c r="J65" s="2"/>
       <c r="K65" s="2" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="L65" s="2" t="s">
         <v>217</v>
@@ -18073,10 +18087,10 @@
       </c>
       <c r="J66" s="2"/>
       <c r="K66" s="2" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="L66" s="2" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
     </row>
     <row r="67" spans="1:12" ht="63.6" thickBot="1">
@@ -18085,10 +18099,10 @@
       </c>
       <c r="J67" s="2"/>
       <c r="K67" s="2" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="L67" s="2" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
     </row>
     <row r="68" spans="1:12" ht="42.6" thickBot="1">
@@ -18100,7 +18114,7 @@
         <v>215</v>
       </c>
       <c r="L68" s="2" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="69" spans="1:12" ht="42.6" thickBot="1">
@@ -18109,7 +18123,7 @@
       </c>
       <c r="J69" s="2"/>
       <c r="K69" s="2" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="L69" s="2" t="s">
         <v>219</v>
@@ -18136,7 +18150,7 @@
         <v>285</v>
       </c>
       <c r="L71" s="2" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
     </row>
     <row r="72" spans="1:12" ht="84.6" thickBot="1">
@@ -18145,10 +18159,10 @@
       </c>
       <c r="J72" s="2"/>
       <c r="K72" s="2" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="L72" s="2" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
     </row>
     <row r="73" spans="1:12" ht="63.6" thickBot="1">
@@ -18157,10 +18171,10 @@
       </c>
       <c r="J73" s="2"/>
       <c r="K73" s="2" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="L73" s="2" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
     </row>
     <row r="74" spans="1:12" ht="84.6" thickBot="1">
@@ -18169,10 +18183,10 @@
       </c>
       <c r="J74" s="2"/>
       <c r="K74" s="2" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="L74" s="2" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
     </row>
     <row r="75" spans="1:12" ht="84.6" thickBot="1">
@@ -18184,7 +18198,7 @@
         <v>296</v>
       </c>
       <c r="L75" s="2" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
     </row>
     <row r="76" spans="1:12" ht="42.6" thickBot="1">
@@ -18193,10 +18207,10 @@
       </c>
       <c r="J76" s="2"/>
       <c r="K76" s="2" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="L76" s="2" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
     </row>
     <row r="77" spans="1:12" ht="42.6" thickBot="1">
@@ -18241,10 +18255,10 @@
       </c>
       <c r="J80" s="2"/>
       <c r="K80" s="2" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="L80" s="2" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="81" spans="1:12" ht="63.6" thickBot="1">
@@ -18256,7 +18270,7 @@
         <v>208</v>
       </c>
       <c r="L81" s="2" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
     </row>
     <row r="82" spans="1:12" ht="42.6" thickBot="1">
@@ -18268,7 +18282,7 @@
         <v>238</v>
       </c>
       <c r="L82" s="2" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
     </row>
     <row r="83" spans="1:12" ht="63.6" thickBot="1">
@@ -18289,10 +18303,10 @@
       </c>
       <c r="J84" s="2"/>
       <c r="K84" s="2" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="L84" s="2" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
     </row>
     <row r="85" spans="1:12" ht="63.6" thickBot="1">
@@ -18301,7 +18315,7 @@
       </c>
       <c r="J85" s="2"/>
       <c r="K85" s="2" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="L85" s="2" t="s">
         <v>81</v>
@@ -18337,7 +18351,7 @@
       </c>
       <c r="J88" s="2"/>
       <c r="K88" s="2" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="L88" s="2" t="s">
         <v>58</v>
@@ -18457,7 +18471,7 @@
       </c>
       <c r="J98" s="2"/>
       <c r="K98" s="2" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="L98" s="2" t="s">
         <v>113</v>
@@ -18469,7 +18483,7 @@
       </c>
       <c r="J99" s="2"/>
       <c r="K99" s="2" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="L99" s="2" t="s">
         <v>149</v>
@@ -18484,7 +18498,7 @@
         <v>303</v>
       </c>
       <c r="L100" s="2" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
     </row>
     <row r="101" spans="1:12" ht="63">
@@ -18505,7 +18519,7 @@
       </c>
       <c r="J102" s="2"/>
       <c r="K102" s="94" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="L102" s="2" t="s">
         <v>140</v>
@@ -18529,7 +18543,7 @@
       </c>
       <c r="J104" s="2"/>
       <c r="K104" s="2" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="L104" s="2" t="s">
         <v>167</v>
@@ -18542,7 +18556,7 @@
       <c r="J105" s="2"/>
       <c r="K105" s="2"/>
       <c r="L105" s="2" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
     </row>
     <row r="106" spans="1:12" ht="63.6" thickBot="1">
@@ -18552,7 +18566,7 @@
       <c r="J106" s="2"/>
       <c r="K106" s="2"/>
       <c r="L106" s="2" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
     </row>
     <row r="107" spans="1:12" ht="63.6" thickBot="1">
@@ -18632,7 +18646,7 @@
       <c r="J114" s="2"/>
       <c r="K114" s="2"/>
       <c r="L114" s="2" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
     </row>
     <row r="115" spans="1:12" ht="63.6" thickBot="1">
@@ -18659,14 +18673,14 @@
       <c r="J117" s="2"/>
       <c r="K117" s="2"/>
       <c r="L117" s="2" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="118" spans="1:12" ht="63.6" thickBot="1">
       <c r="J118" s="2"/>
       <c r="K118" s="2"/>
       <c r="L118" s="2" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
     </row>
     <row r="119" spans="1:12" ht="21.6" thickBot="1">
@@ -18687,21 +18701,21 @@
       <c r="J121" s="2"/>
       <c r="K121" s="2"/>
       <c r="L121" s="2" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
     </row>
     <row r="122" spans="1:12" ht="42.6" thickBot="1">
       <c r="J122" s="2"/>
       <c r="K122" s="2"/>
       <c r="L122" s="2" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
     </row>
     <row r="123" spans="1:12" ht="42.6" thickBot="1">
       <c r="J123" s="2"/>
       <c r="K123" s="2"/>
       <c r="L123" s="2" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
     </row>
     <row r="124" spans="1:12" ht="21.6" thickBot="1">
@@ -18778,14 +18792,14 @@
       <c r="J134" s="2"/>
       <c r="K134" s="2"/>
       <c r="L134" s="2" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
     </row>
     <row r="135" spans="10:12" ht="42.6" thickBot="1">
       <c r="J135" s="2"/>
       <c r="K135" s="2"/>
       <c r="L135" s="2" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
     </row>
     <row r="136" spans="10:12" ht="63.6" thickBot="1">
@@ -18827,7 +18841,7 @@
       <c r="J141" s="2"/>
       <c r="K141" s="2"/>
       <c r="L141" s="2" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
     </row>
     <row r="142" spans="10:12" ht="21.6" thickBot="1">
@@ -18925,21 +18939,21 @@
       <c r="J155" s="2"/>
       <c r="K155" s="2"/>
       <c r="L155" s="2" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
     </row>
     <row r="156" spans="10:12" ht="63.6" thickBot="1">
       <c r="J156" s="2"/>
       <c r="K156" s="2"/>
       <c r="L156" s="2" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="157" spans="10:12" ht="63.6" thickBot="1">
       <c r="J157" s="2"/>
       <c r="K157" s="2"/>
       <c r="L157" s="2" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="158" spans="10:12" ht="63.6" thickBot="1">
@@ -18981,20 +18995,22 @@
       <c r="J163" s="2"/>
       <c r="K163" s="2"/>
       <c r="L163" s="2" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="164" spans="10:12" ht="82.5">
       <c r="J164" s="2"/>
       <c r="K164" s="2"/>
       <c r="L164" s="2" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="165" spans="10:12" ht="21.6" thickBot="1">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="165" spans="10:12" ht="82.5">
       <c r="J165" s="2"/>
       <c r="K165" s="2"/>
-      <c r="L165" s="2"/>
+      <c r="L165" s="2" t="s">
+        <v>388</v>
+      </c>
     </row>
     <row r="166" spans="10:12" ht="21.6" thickBot="1">
       <c r="J166" s="2"/>
@@ -23192,10 +23208,10 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="C1" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -23203,7 +23219,7 @@
         <v>2026</v>
       </c>
       <c r="B2" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="C2">
         <f>SUM(Recruitment!AC:AC)</f>
@@ -23239,7 +23255,7 @@
         <v>2026</v>
       </c>
       <c r="B5" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="C5">
         <f>SUM(Recruitment!AH:AH)</f>
@@ -23269,24 +23285,24 @@
   <sheetData>
     <row r="1" spans="1:30">
       <c r="A1" s="177" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="B1" s="173" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="C1" s="173" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="D1" s="173" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="E1" s="170" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="F1" s="171"/>
       <c r="G1" s="172"/>
       <c r="H1" s="173" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="I1" s="121"/>
       <c r="J1" s="121"/>
@@ -23323,13 +23339,13 @@
         <v>82</v>
       </c>
       <c r="G2" s="125" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="H2" s="174"/>
       <c r="I2" s="126"/>
       <c r="J2" s="126"/>
       <c r="K2" s="126" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="L2" s="127">
         <v>23000</v>
@@ -23355,7 +23371,7 @@
     </row>
     <row r="3" spans="1:30">
       <c r="A3" s="129" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="B3" s="130"/>
       <c r="C3" s="130"/>
@@ -23373,7 +23389,7 @@
       <c r="I3" s="126"/>
       <c r="J3" s="126"/>
       <c r="K3" s="126" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="L3" s="131">
         <v>178675</v>
@@ -23399,7 +23415,7 @@
     </row>
     <row r="4" spans="1:30">
       <c r="A4" s="129" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="B4" s="130"/>
       <c r="C4" s="130"/>
@@ -23411,7 +23427,7 @@
       <c r="I4" s="126"/>
       <c r="J4" s="126"/>
       <c r="K4" s="126" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="L4" s="131">
         <v>229650</v>
@@ -23437,16 +23453,16 @@
     </row>
     <row r="5" spans="1:30">
       <c r="A5" s="179" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="B5" s="130" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="C5" s="132">
         <v>491400</v>
       </c>
       <c r="D5" s="130" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="E5" s="130">
         <v>589</v>
@@ -23459,7 +23475,7 @@
       <c r="I5" s="126"/>
       <c r="J5" s="126"/>
       <c r="K5" s="126" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="L5" s="126">
         <v>12910</v>
@@ -23486,13 +23502,13 @@
     <row r="6" spans="1:30">
       <c r="A6" s="180"/>
       <c r="B6" s="130" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="C6" s="132">
         <v>80000</v>
       </c>
       <c r="D6" s="130" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="E6" s="130"/>
       <c r="F6" s="130"/>
@@ -23501,7 +23517,7 @@
       <c r="I6" s="126"/>
       <c r="J6" s="126"/>
       <c r="K6" s="126" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="L6" s="131">
         <v>57930</v>
@@ -23528,7 +23544,7 @@
     <row r="7" spans="1:30">
       <c r="A7" s="181"/>
       <c r="B7" s="133" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="C7" s="132">
         <v>12157</v>
@@ -23563,10 +23579,10 @@
     </row>
     <row r="8" spans="1:30">
       <c r="A8" s="129" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="B8" s="130" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="C8" s="130">
         <v>0</v>
@@ -23601,16 +23617,16 @@
     </row>
     <row r="9" spans="1:30">
       <c r="A9" s="179" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="B9" s="130" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="C9" s="130">
         <v>241.375</v>
       </c>
       <c r="D9" s="130" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="E9" s="130"/>
       <c r="F9" s="130">
@@ -23646,7 +23662,7 @@
     <row r="10" spans="1:30">
       <c r="A10" s="181"/>
       <c r="B10" s="133" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="C10" s="130">
         <v>139.8583333</v>
@@ -23681,16 +23697,16 @@
     </row>
     <row r="11" spans="1:30">
       <c r="A11" s="179" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="B11" s="130" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="C11" s="130">
         <v>95.833333330000002</v>
       </c>
       <c r="D11" s="130" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="E11" s="130">
         <v>15</v>
@@ -23730,13 +23746,13 @@
     <row r="12" spans="1:30">
       <c r="A12" s="180"/>
       <c r="B12" s="130" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="C12" s="130">
         <v>241.375</v>
       </c>
       <c r="D12" s="130" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="E12" s="130"/>
       <c r="F12" s="130"/>
@@ -23745,7 +23761,7 @@
       <c r="I12" s="126"/>
       <c r="J12" s="126"/>
       <c r="K12" s="126" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="L12" s="126">
         <v>65</v>
@@ -23772,7 +23788,7 @@
     <row r="13" spans="1:30">
       <c r="A13" s="180"/>
       <c r="B13" s="133" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="C13" s="130">
         <v>2529.0625</v>
@@ -23785,7 +23801,7 @@
       <c r="I13" s="126"/>
       <c r="J13" s="126"/>
       <c r="K13" s="126" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="L13" s="126">
         <v>32</v>
@@ -23812,7 +23828,7 @@
     <row r="14" spans="1:30">
       <c r="A14" s="180"/>
       <c r="B14" s="133" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="C14" s="130">
         <v>2529.0625</v>
@@ -23852,7 +23868,7 @@
     <row r="15" spans="1:30">
       <c r="A15" s="181"/>
       <c r="B15" s="133" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="C15" s="130">
         <v>2191.854167</v>
@@ -23865,7 +23881,7 @@
       <c r="I15" s="126"/>
       <c r="J15" s="126"/>
       <c r="K15" s="126" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="L15" s="126">
         <v>33</v>
@@ -23891,16 +23907,16 @@
     </row>
     <row r="16" spans="1:30">
       <c r="A16" s="179" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="B16" s="130" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="C16" s="130">
         <v>95.833333330000002</v>
       </c>
       <c r="D16" s="130" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="E16" s="130">
         <v>4</v>
@@ -23917,7 +23933,7 @@
       <c r="I16" s="126"/>
       <c r="J16" s="126"/>
       <c r="K16" s="126" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="L16" s="126">
         <v>4</v>
@@ -23944,13 +23960,13 @@
     <row r="17" spans="1:30">
       <c r="A17" s="180"/>
       <c r="B17" s="130" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="C17" s="130">
         <v>956.875</v>
       </c>
       <c r="D17" s="130" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="E17" s="130"/>
       <c r="F17" s="130"/>
@@ -23982,13 +23998,13 @@
     <row r="18" spans="1:30">
       <c r="A18" s="180"/>
       <c r="B18" s="130" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="C18" s="130">
         <v>53.791666669999998</v>
       </c>
       <c r="D18" s="130" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="E18" s="130"/>
       <c r="F18" s="130"/>
@@ -24020,13 +24036,13 @@
     <row r="19" spans="1:30">
       <c r="A19" s="180"/>
       <c r="B19" s="130" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="C19" s="130">
         <v>956.875</v>
       </c>
       <c r="D19" s="130" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="E19" s="130"/>
       <c r="F19" s="130"/>
@@ -24058,7 +24074,7 @@
     <row r="20" spans="1:30">
       <c r="A20" s="180"/>
       <c r="B20" s="133" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="C20" s="130">
         <v>3095.0625</v>
@@ -24096,7 +24112,7 @@
     <row r="21" spans="1:30">
       <c r="A21" s="180"/>
       <c r="B21" s="133" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="C21" s="130">
         <v>4126.75</v>
@@ -24132,7 +24148,7 @@
     <row r="22" spans="1:30">
       <c r="A22" s="181"/>
       <c r="B22" s="133" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="C22" s="130">
         <v>3095.0625</v>
@@ -24167,10 +24183,10 @@
     </row>
     <row r="23" spans="1:30">
       <c r="A23" s="129" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="B23" s="133" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="C23" s="130">
         <v>1000</v>
@@ -24183,7 +24199,7 @@
       <c r="I23" s="126"/>
       <c r="J23" s="126"/>
       <c r="K23" s="126" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="L23" s="126">
         <v>2</v>
@@ -24209,16 +24225,16 @@
     </row>
     <row r="24" spans="1:30">
       <c r="A24" s="179" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="B24" s="175" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="C24" s="132">
         <v>1800</v>
       </c>
       <c r="D24" s="130" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="E24" s="130">
         <v>1</v>
@@ -24233,7 +24249,7 @@
       <c r="I24" s="126"/>
       <c r="J24" s="126"/>
       <c r="K24" s="126" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="L24" s="126">
         <v>14</v>
@@ -24264,7 +24280,7 @@
         <v>2000</v>
       </c>
       <c r="D25" s="130" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="E25" s="130"/>
       <c r="F25" s="130"/>
@@ -24273,7 +24289,7 @@
       <c r="I25" s="126"/>
       <c r="J25" s="126"/>
       <c r="K25" s="126" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="L25" s="126">
         <v>12</v>
@@ -24335,16 +24351,16 @@
     </row>
     <row r="27" spans="1:30">
       <c r="A27" s="134" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="B27" s="126" t="s">
+        <v>597</v>
+      </c>
+      <c r="C27" s="126" t="s">
+        <v>593</v>
+      </c>
+      <c r="D27" s="126" t="s">
         <v>595</v>
-      </c>
-      <c r="C27" s="126" t="s">
-        <v>591</v>
-      </c>
-      <c r="D27" s="126" t="s">
-        <v>593</v>
       </c>
       <c r="E27" s="126"/>
       <c r="F27" s="126"/>
@@ -24419,7 +24435,7 @@
     </row>
     <row r="29" spans="1:30">
       <c r="A29" s="134" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="B29" s="127">
         <v>19813</v>
@@ -24437,7 +24453,7 @@
       <c r="I29" s="126"/>
       <c r="J29" s="126"/>
       <c r="K29" s="126" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="L29" s="126"/>
       <c r="M29" s="126"/>
@@ -24461,7 +24477,7 @@
     </row>
     <row r="30" spans="1:30">
       <c r="A30" s="134" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="B30" s="127">
         <v>19813</v>
@@ -24633,7 +24649,7 @@
     </row>
     <row r="35" spans="1:30">
       <c r="A35" s="134" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="B35" s="126"/>
       <c r="C35" s="126"/>
@@ -24667,7 +24683,7 @@
     </row>
     <row r="36" spans="1:30">
       <c r="A36" s="134" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="B36" s="126"/>
       <c r="C36" s="126"/>
@@ -24702,16 +24718,16 @@
     <row r="37" spans="1:30">
       <c r="A37" s="137"/>
       <c r="B37" s="138" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="C37" s="138" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="D37" s="138" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="E37" s="139" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="F37" s="126"/>
       <c r="G37" s="126"/>
@@ -24741,7 +24757,7 @@
     </row>
     <row r="38" spans="1:30">
       <c r="A38" s="140" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="B38" s="141">
         <v>600</v>
@@ -24783,7 +24799,7 @@
     </row>
     <row r="39" spans="1:30">
       <c r="A39" s="143" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="B39" s="144">
         <v>350</v>

--- a/data/Recruitment_Requisition.xlsx
+++ b/data/Recruitment_Requisition.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://kubotagroup-my.sharepoint.com/personal/lapat_j_kubota_com/Documents/Documents/Recruitment Tools/Dashboard Data Report/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3559" documentId="8_{4185217D-4006-4629-AD3A-0737CE05813A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0FD4E614-41C7-48D6-BD2C-D88188D12B54}"/>
+  <xr:revisionPtr revIDLastSave="3560" documentId="8_{4185217D-4006-4629-AD3A-0737CE05813A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0CA8569E-9496-4E58-BDB2-2BA34AFF5D43}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{5982D4A9-2AD8-4F8A-AE0B-0D729A27807E}"/>
   </bookViews>
@@ -16452,7 +16452,7 @@
         <v>2026</v>
       </c>
       <c r="B118" s="96" t="str">
-        <f t="shared" ref="B118:B119" si="9">IF(M118="", "", TEXT(M118, "[$-en-US]mmm"))</f>
+        <f t="shared" ref="B118:B121" si="9">IF(M118="", "", TEXT(M118, "[$-en-US]mmm"))</f>
         <v>Jun</v>
       </c>
       <c r="C118" s="96" t="s">
@@ -16654,8 +16654,8 @@
         <v>2026</v>
       </c>
       <c r="B120" s="96" t="str">
-        <f>IF(M120="", "", TEXT(M120, "[$-en-US]mmmm"))</f>
-        <v>August</v>
+        <f t="shared" si="9"/>
+        <v>Aug</v>
       </c>
       <c r="C120" s="96" t="s">
         <v>45</v>
@@ -16754,8 +16754,8 @@
         <v>2026</v>
       </c>
       <c r="B121" s="96" t="str">
-        <f>IF(M121="", "", TEXT(M121, "[$-en-US]mmmm"))</f>
-        <v>August</v>
+        <f t="shared" si="9"/>
+        <v>Aug</v>
       </c>
       <c r="C121" s="96" t="s">
         <v>35</v>

--- a/data/Recruitment_Requisition.xlsx
+++ b/data/Recruitment_Requisition.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://kubotagroup-my.sharepoint.com/personal/lapat_j_kubota_com/Documents/Documents/Recruitment Tools/Dashboard Data Report/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3560" documentId="8_{4185217D-4006-4629-AD3A-0737CE05813A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0CA8569E-9496-4E58-BDB2-2BA34AFF5D43}"/>
+  <xr:revisionPtr revIDLastSave="3562" documentId="8_{4185217D-4006-4629-AD3A-0737CE05813A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C176AD31-31B9-4E1D-A49C-B1D9C3DDD4F3}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{5982D4A9-2AD8-4F8A-AE0B-0D729A27807E}"/>
   </bookViews>
@@ -5043,13 +5043,7 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2A626EEB-FDFE-42FC-817A-963B6C771FE3}" name="Master" displayName="Master" ref="A1:AI122" totalsRowShown="0" headerRowDxfId="53" dataDxfId="52" tableBorderDxfId="51">
-  <autoFilter ref="A1:AI122" xr:uid="{2A626EEB-FDFE-42FC-817A-963B6C771FE3}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="2026"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:AI122" xr:uid="{2A626EEB-FDFE-42FC-817A-963B6C771FE3}"/>
   <tableColumns count="35">
     <tableColumn id="1" xr3:uid="{FF1CE6B1-DB01-49DC-BA43-064CD949FF4D}" name="Year" dataDxfId="50"/>
     <tableColumn id="2" xr3:uid="{7F3A3465-03B1-4D22-80CE-2DF0F09BDF7E}" name="Month" dataDxfId="49">
@@ -5608,7 +5602,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="2" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
+    <row r="2" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A2" s="46">
         <v>2024</v>
       </c>
@@ -5706,7 +5700,7 @@
       <c r="AH2" s="12"/>
       <c r="AI2" s="8"/>
     </row>
-    <row r="3" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
+    <row r="3" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A3" s="46">
         <v>2024</v>
       </c>
@@ -5798,7 +5792,7 @@
       <c r="AH3" s="12"/>
       <c r="AI3" s="8"/>
     </row>
-    <row r="4" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
+    <row r="4" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A4" s="46">
         <v>2024</v>
       </c>
@@ -5886,7 +5880,7 @@
       <c r="AH4" s="12"/>
       <c r="AI4" s="8"/>
     </row>
-    <row r="5" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
+    <row r="5" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A5" s="46">
         <v>2024</v>
       </c>
@@ -5976,7 +5970,7 @@
       <c r="AH5" s="12"/>
       <c r="AI5" s="8"/>
     </row>
-    <row r="6" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
+    <row r="6" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A6" s="46">
         <v>2024</v>
       </c>
@@ -6064,7 +6058,7 @@
       <c r="AH6" s="12"/>
       <c r="AI6" s="8"/>
     </row>
-    <row r="7" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
+    <row r="7" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A7" s="46">
         <v>2024</v>
       </c>
@@ -6152,7 +6146,7 @@
       <c r="AH7" s="12"/>
       <c r="AI7" s="8"/>
     </row>
-    <row r="8" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
+    <row r="8" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A8" s="46">
         <v>2024</v>
       </c>
@@ -6244,7 +6238,7 @@
       <c r="AH8" s="12"/>
       <c r="AI8" s="8"/>
     </row>
-    <row r="9" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
+    <row r="9" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A9" s="46">
         <v>2024</v>
       </c>
@@ -6330,7 +6324,7 @@
       <c r="AH9" s="12"/>
       <c r="AI9" s="8"/>
     </row>
-    <row r="10" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
+    <row r="10" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A10" s="46">
         <v>2024</v>
       </c>
@@ -6418,7 +6412,7 @@
       <c r="AH10" s="12"/>
       <c r="AI10" s="8"/>
     </row>
-    <row r="11" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
+    <row r="11" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A11" s="46">
         <v>2024</v>
       </c>
@@ -6508,7 +6502,7 @@
       <c r="AH11" s="12"/>
       <c r="AI11" s="8"/>
     </row>
-    <row r="12" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
+    <row r="12" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A12" s="46">
         <v>2024</v>
       </c>
@@ -6596,7 +6590,7 @@
       <c r="AH12" s="12"/>
       <c r="AI12" s="8"/>
     </row>
-    <row r="13" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
+    <row r="13" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A13" s="46">
         <v>2024</v>
       </c>
@@ -6686,7 +6680,7 @@
       <c r="AH13" s="12"/>
       <c r="AI13" s="8"/>
     </row>
-    <row r="14" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
+    <row r="14" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A14" s="46">
         <v>2024</v>
       </c>
@@ -6776,7 +6770,7 @@
       <c r="AH14" s="12"/>
       <c r="AI14" s="8"/>
     </row>
-    <row r="15" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
+    <row r="15" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A15" s="46">
         <v>2024</v>
       </c>
@@ -6864,7 +6858,7 @@
       <c r="AH15" s="12"/>
       <c r="AI15" s="8"/>
     </row>
-    <row r="16" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
+    <row r="16" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A16" s="46">
         <v>2024</v>
       </c>
@@ -6954,7 +6948,7 @@
       <c r="AH16" s="12"/>
       <c r="AI16" s="8"/>
     </row>
-    <row r="17" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
+    <row r="17" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A17" s="46">
         <v>2024</v>
       </c>
@@ -7042,7 +7036,7 @@
       <c r="AH17" s="12"/>
       <c r="AI17" s="8"/>
     </row>
-    <row r="18" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
+    <row r="18" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A18" s="46">
         <v>2024</v>
       </c>
@@ -7132,7 +7126,7 @@
       <c r="AH18" s="12"/>
       <c r="AI18" s="8"/>
     </row>
-    <row r="19" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
+    <row r="19" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A19" s="46">
         <v>2024</v>
       </c>
@@ -7222,7 +7216,7 @@
       <c r="AH19" s="12"/>
       <c r="AI19" s="8"/>
     </row>
-    <row r="20" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
+    <row r="20" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A20" s="46">
         <v>2024</v>
       </c>
@@ -7312,7 +7306,7 @@
       <c r="AH20" s="12"/>
       <c r="AI20" s="8"/>
     </row>
-    <row r="21" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
+    <row r="21" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A21" s="46">
         <v>2025</v>
       </c>
@@ -7404,7 +7398,7 @@
       <c r="AH21" s="12"/>
       <c r="AI21" s="8"/>
     </row>
-    <row r="22" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
+    <row r="22" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A22" s="46">
         <v>2025</v>
       </c>
@@ -7496,7 +7490,7 @@
       <c r="AH22" s="12"/>
       <c r="AI22" s="8"/>
     </row>
-    <row r="23" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
+    <row r="23" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A23" s="46">
         <v>2025</v>
       </c>
@@ -7588,7 +7582,7 @@
       <c r="AH23" s="12"/>
       <c r="AI23" s="8"/>
     </row>
-    <row r="24" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
+    <row r="24" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A24" s="46">
         <v>2025</v>
       </c>
@@ -7680,7 +7674,7 @@
       <c r="AH24" s="12"/>
       <c r="AI24" s="8"/>
     </row>
-    <row r="25" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
+    <row r="25" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A25" s="46">
         <v>2025</v>
       </c>
@@ -7772,7 +7766,7 @@
       <c r="AH25" s="12"/>
       <c r="AI25" s="8"/>
     </row>
-    <row r="26" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
+    <row r="26" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A26" s="46">
         <v>2025</v>
       </c>
@@ -7864,7 +7858,7 @@
       <c r="AH26" s="12"/>
       <c r="AI26" s="8"/>
     </row>
-    <row r="27" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
+    <row r="27" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A27" s="46">
         <v>2025</v>
       </c>
@@ -7956,7 +7950,7 @@
       <c r="AH27" s="12"/>
       <c r="AI27" s="8"/>
     </row>
-    <row r="28" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
+    <row r="28" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A28" s="46">
         <v>2025</v>
       </c>
@@ -8050,7 +8044,7 @@
       <c r="AH28" s="12"/>
       <c r="AI28" s="8"/>
     </row>
-    <row r="29" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
+    <row r="29" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A29" s="46">
         <v>2025</v>
       </c>
@@ -8142,7 +8136,7 @@
       <c r="AH29" s="12"/>
       <c r="AI29" s="8"/>
     </row>
-    <row r="30" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
+    <row r="30" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A30" s="46">
         <v>2025</v>
       </c>
@@ -8236,7 +8230,7 @@
       <c r="AH30" s="12"/>
       <c r="AI30" s="8"/>
     </row>
-    <row r="31" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
+    <row r="31" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A31" s="46">
         <v>2025</v>
       </c>
@@ -8334,7 +8328,7 @@
       <c r="AH31" s="12"/>
       <c r="AI31" s="8"/>
     </row>
-    <row r="32" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
+    <row r="32" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A32" s="46">
         <v>2025</v>
       </c>
@@ -8428,7 +8422,7 @@
       <c r="AH32" s="12"/>
       <c r="AI32" s="8"/>
     </row>
-    <row r="33" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
+    <row r="33" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A33" s="46">
         <v>2025</v>
       </c>
@@ -8520,7 +8514,7 @@
       <c r="AH33" s="12"/>
       <c r="AI33" s="8"/>
     </row>
-    <row r="34" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
+    <row r="34" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A34" s="46">
         <v>2025</v>
       </c>
@@ -8620,7 +8614,7 @@
       <c r="AH34" s="12"/>
       <c r="AI34" s="8"/>
     </row>
-    <row r="35" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
+    <row r="35" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A35" s="46">
         <v>2025</v>
       </c>
@@ -8714,7 +8708,7 @@
       <c r="AH35" s="12"/>
       <c r="AI35" s="8"/>
     </row>
-    <row r="36" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
+    <row r="36" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A36" s="46">
         <v>2025</v>
       </c>
@@ -8808,7 +8802,7 @@
       <c r="AH36" s="12"/>
       <c r="AI36" s="8"/>
     </row>
-    <row r="37" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
+    <row r="37" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A37" s="46">
         <v>2025</v>
       </c>
@@ -8867,7 +8861,7 @@
       Dropdown!$A$2:$A$100
    )
 )</f>
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="Q37" s="13" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -8892,7 +8886,7 @@
       <c r="AH37" s="12"/>
       <c r="AI37" s="8"/>
     </row>
-    <row r="38" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
+    <row r="38" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A38" s="46">
         <v>2025</v>
       </c>
@@ -8984,7 +8978,7 @@
       <c r="AH38" s="12"/>
       <c r="AI38" s="8"/>
     </row>
-    <row r="39" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
+    <row r="39" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A39" s="46">
         <v>2025</v>
       </c>
@@ -9074,7 +9068,7 @@
       <c r="AH39" s="12"/>
       <c r="AI39" s="8"/>
     </row>
-    <row r="40" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
+    <row r="40" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A40" s="46">
         <v>2025</v>
       </c>
@@ -9164,7 +9158,7 @@
       <c r="AH40" s="12"/>
       <c r="AI40" s="8"/>
     </row>
-    <row r="41" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
+    <row r="41" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A41" s="46">
         <v>2025</v>
       </c>
@@ -9256,7 +9250,7 @@
       <c r="AH41" s="12"/>
       <c r="AI41" s="8"/>
     </row>
-    <row r="42" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
+    <row r="42" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A42" s="46">
         <v>2025</v>
       </c>
@@ -9348,7 +9342,7 @@
       <c r="AH42" s="12"/>
       <c r="AI42" s="8"/>
     </row>
-    <row r="43" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
+    <row r="43" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A43" s="46">
         <v>2025</v>
       </c>
@@ -9440,7 +9434,7 @@
       <c r="AH43" s="12"/>
       <c r="AI43" s="8"/>
     </row>
-    <row r="44" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
+    <row r="44" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A44" s="46">
         <v>2025</v>
       </c>
@@ -9532,7 +9526,7 @@
       <c r="AH44" s="12"/>
       <c r="AI44" s="8"/>
     </row>
-    <row r="45" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
+    <row r="45" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A45" s="46">
         <v>2025</v>
       </c>
@@ -9624,7 +9618,7 @@
       <c r="AH45" s="12"/>
       <c r="AI45" s="8"/>
     </row>
-    <row r="46" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
+    <row r="46" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A46" s="46">
         <v>2025</v>
       </c>
@@ -9716,7 +9710,7 @@
       <c r="AH46" s="12"/>
       <c r="AI46" s="8"/>
     </row>
-    <row r="47" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
+    <row r="47" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A47" s="46">
         <v>2025</v>
       </c>
@@ -9804,7 +9798,7 @@
       <c r="AH47" s="12"/>
       <c r="AI47" s="8"/>
     </row>
-    <row r="48" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
+    <row r="48" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A48" s="46">
         <v>2025</v>
       </c>
@@ -9898,7 +9892,7 @@
       <c r="AH48" s="12"/>
       <c r="AI48" s="8"/>
     </row>
-    <row r="49" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
+    <row r="49" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A49" s="46">
         <v>2025</v>
       </c>
@@ -9992,7 +9986,7 @@
       <c r="AH49" s="12"/>
       <c r="AI49" s="8"/>
     </row>
-    <row r="50" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
+    <row r="50" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A50" s="46">
         <v>2025</v>
       </c>
@@ -10084,7 +10078,7 @@
       <c r="AH50" s="12"/>
       <c r="AI50" s="8"/>
     </row>
-    <row r="51" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
+    <row r="51" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A51" s="46">
         <v>2025</v>
       </c>
@@ -10176,7 +10170,7 @@
       <c r="AH51" s="12"/>
       <c r="AI51" s="8"/>
     </row>
-    <row r="52" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
+    <row r="52" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A52" s="46">
         <v>2025</v>
       </c>
@@ -10268,7 +10262,7 @@
       <c r="AH52" s="12"/>
       <c r="AI52" s="8"/>
     </row>
-    <row r="53" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
+    <row r="53" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A53" s="46">
         <v>2025</v>
       </c>
@@ -10356,7 +10350,7 @@
       <c r="AH53" s="12"/>
       <c r="AI53" s="8"/>
     </row>
-    <row r="54" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
+    <row r="54" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A54" s="46">
         <v>2025</v>
       </c>
@@ -10446,7 +10440,7 @@
       <c r="AH54" s="12"/>
       <c r="AI54" s="8"/>
     </row>
-    <row r="55" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
+    <row r="55" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A55" s="46">
         <v>2025</v>
       </c>
@@ -10536,7 +10530,7 @@
       <c r="AH55" s="12"/>
       <c r="AI55" s="8"/>
     </row>
-    <row r="56" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
+    <row r="56" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A56" s="46">
         <v>2025</v>
       </c>
@@ -10624,7 +10618,7 @@
       <c r="AH56" s="12"/>
       <c r="AI56" s="8"/>
     </row>
-    <row r="57" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
+    <row r="57" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A57" s="46">
         <v>2025</v>
       </c>
@@ -10712,7 +10706,7 @@
       <c r="AH57" s="12"/>
       <c r="AI57" s="8"/>
     </row>
-    <row r="58" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
+    <row r="58" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A58" s="46">
         <v>2025</v>
       </c>
@@ -10804,7 +10798,7 @@
       <c r="AH58" s="12"/>
       <c r="AI58" s="8"/>
     </row>
-    <row r="59" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
+    <row r="59" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A59" s="46">
         <v>2025</v>
       </c>
@@ -10898,7 +10892,7 @@
       <c r="AH59" s="12"/>
       <c r="AI59" s="8"/>
     </row>
-    <row r="60" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
+    <row r="60" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A60" s="46">
         <v>2025</v>
       </c>
@@ -10992,7 +10986,7 @@
       <c r="AH60" s="12"/>
       <c r="AI60" s="8"/>
     </row>
-    <row r="61" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
+    <row r="61" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A61" s="46">
         <v>2025</v>
       </c>
@@ -11082,7 +11076,7 @@
       <c r="AH61" s="12"/>
       <c r="AI61" s="8"/>
     </row>
-    <row r="62" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
+    <row r="62" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A62" s="46">
         <v>2025</v>
       </c>
@@ -11172,7 +11166,7 @@
       <c r="AH62" s="12"/>
       <c r="AI62" s="8"/>
     </row>
-    <row r="63" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
+    <row r="63" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A63" s="46">
         <v>2025</v>
       </c>
@@ -11262,7 +11256,7 @@
       <c r="AH63" s="12"/>
       <c r="AI63" s="8"/>
     </row>
-    <row r="64" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
+    <row r="64" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A64" s="46">
         <v>2025</v>
       </c>
@@ -11356,7 +11350,7 @@
       <c r="AH64" s="12"/>
       <c r="AI64" s="8"/>
     </row>
-    <row r="65" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
+    <row r="65" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A65" s="46">
         <v>2025</v>
       </c>
@@ -11450,7 +11444,7 @@
       <c r="AH65" s="12"/>
       <c r="AI65" s="8"/>
     </row>
-    <row r="66" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
+    <row r="66" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A66" s="46">
         <v>2025</v>
       </c>
@@ -11552,7 +11546,7 @@
       <c r="AH66" s="12"/>
       <c r="AI66" s="8"/>
     </row>
-    <row r="67" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
+    <row r="67" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A67" s="46">
         <v>2025</v>
       </c>
@@ -11644,7 +11638,7 @@
       <c r="AH67" s="12"/>
       <c r="AI67" s="8"/>
     </row>
-    <row r="68" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
+    <row r="68" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A68" s="46">
         <v>2025</v>
       </c>
@@ -11736,7 +11730,7 @@
       <c r="AH68" s="12"/>
       <c r="AI68" s="8"/>
     </row>
-    <row r="69" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
+    <row r="69" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A69" s="46">
         <v>2025</v>
       </c>
@@ -11828,7 +11822,7 @@
       <c r="AH69" s="12"/>
       <c r="AI69" s="8"/>
     </row>
-    <row r="70" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
+    <row r="70" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A70" s="46">
         <v>2025</v>
       </c>
@@ -11889,7 +11883,7 @@
       Dropdown!$A$2:$A$100
    )
 )</f>
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q70" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -11918,7 +11912,7 @@
       <c r="AH70" s="12"/>
       <c r="AI70" s="8"/>
     </row>
-    <row r="71" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
+    <row r="71" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A71" s="46">
         <v>2025</v>
       </c>
@@ -12012,7 +12006,7 @@
       <c r="AH71" s="12"/>
       <c r="AI71" s="8"/>
     </row>
-    <row r="72" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
+    <row r="72" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A72" s="46">
         <v>2025</v>
       </c>
@@ -12106,7 +12100,7 @@
       <c r="AH72" s="12"/>
       <c r="AI72" s="8"/>
     </row>
-    <row r="73" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
+    <row r="73" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A73" s="46">
         <v>2025</v>
       </c>
@@ -12200,7 +12194,7 @@
       <c r="AH73" s="12"/>
       <c r="AI73" s="8"/>
     </row>
-    <row r="74" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
+    <row r="74" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A74" s="46">
         <v>2025</v>
       </c>
@@ -12294,7 +12288,7 @@
       <c r="AH74" s="12"/>
       <c r="AI74" s="8"/>
     </row>
-    <row r="75" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
+    <row r="75" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A75" s="46">
         <v>2025</v>
       </c>
@@ -12390,7 +12384,7 @@
       <c r="AH75" s="12"/>
       <c r="AI75" s="8"/>
     </row>
-    <row r="76" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
+    <row r="76" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A76" s="46">
         <v>2025</v>
       </c>
@@ -12484,7 +12478,7 @@
       <c r="AH76" s="17"/>
       <c r="AI76" s="8"/>
     </row>
-    <row r="77" spans="1:35" s="9" customFormat="1" ht="30" hidden="1" customHeight="1">
+    <row r="77" spans="1:35" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A77" s="46">
         <v>2025</v>
       </c>
@@ -12582,7 +12576,7 @@
       <c r="AH77" s="17"/>
       <c r="AI77" s="8"/>
     </row>
-    <row r="78" spans="1:35" s="11" customFormat="1" ht="30" hidden="1" customHeight="1">
+    <row r="78" spans="1:35" s="11" customFormat="1" ht="30" customHeight="1">
       <c r="A78" s="46">
         <v>2025</v>
       </c>
@@ -12682,7 +12676,7 @@
       <c r="AH78" s="12"/>
       <c r="AI78" s="8"/>
     </row>
-    <row r="79" spans="1:35" s="11" customFormat="1" ht="30" hidden="1" customHeight="1">
+    <row r="79" spans="1:35" s="11" customFormat="1" ht="30" customHeight="1">
       <c r="A79" s="46">
         <v>2025</v>
       </c>
@@ -12776,7 +12770,7 @@
       <c r="AH79" s="12"/>
       <c r="AI79" s="8"/>
     </row>
-    <row r="80" spans="1:35" s="11" customFormat="1" ht="30" hidden="1" customHeight="1">
+    <row r="80" spans="1:35" s="11" customFormat="1" ht="30" customHeight="1">
       <c r="A80" s="46">
         <v>2025</v>
       </c>
@@ -12868,7 +12862,7 @@
       <c r="AH80" s="17"/>
       <c r="AI80" s="8"/>
     </row>
-    <row r="81" spans="1:35" s="11" customFormat="1" ht="30" hidden="1" customHeight="1">
+    <row r="81" spans="1:35" s="11" customFormat="1" ht="30" customHeight="1">
       <c r="A81" s="46">
         <v>2025</v>
       </c>
@@ -12962,7 +12956,7 @@
       <c r="AH81" s="12"/>
       <c r="AI81" s="8"/>
     </row>
-    <row r="82" spans="1:35" s="11" customFormat="1" ht="30" hidden="1" customHeight="1">
+    <row r="82" spans="1:35" s="11" customFormat="1" ht="30" customHeight="1">
       <c r="A82" s="46">
         <v>2025</v>
       </c>
@@ -13050,7 +13044,7 @@
       <c r="AH82" s="17"/>
       <c r="AI82" s="8"/>
     </row>
-    <row r="83" spans="1:35" s="11" customFormat="1" ht="30" hidden="1" customHeight="1">
+    <row r="83" spans="1:35" s="11" customFormat="1" ht="30" customHeight="1">
       <c r="A83" s="46">
         <v>2025</v>
       </c>
@@ -13144,7 +13138,7 @@
       <c r="AH83" s="17"/>
       <c r="AI83" s="8"/>
     </row>
-    <row r="84" spans="1:35" s="11" customFormat="1" ht="30" hidden="1" customHeight="1">
+    <row r="84" spans="1:35" s="11" customFormat="1" ht="30" customHeight="1">
       <c r="A84" s="46">
         <v>2025</v>
       </c>
@@ -13238,7 +13232,7 @@
       <c r="AH84" s="17"/>
       <c r="AI84" s="8"/>
     </row>
-    <row r="85" spans="1:35" s="11" customFormat="1" ht="30" hidden="1" customHeight="1">
+    <row r="85" spans="1:35" s="11" customFormat="1" ht="30" customHeight="1">
       <c r="A85" s="46">
         <v>2025</v>
       </c>
@@ -13332,7 +13326,7 @@
       <c r="AH85" s="17"/>
       <c r="AI85" s="8"/>
     </row>
-    <row r="86" spans="1:35" s="11" customFormat="1" ht="30" hidden="1" customHeight="1">
+    <row r="86" spans="1:35" s="11" customFormat="1" ht="30" customHeight="1">
       <c r="A86" s="46">
         <v>2025</v>
       </c>
@@ -13430,7 +13424,7 @@
       <c r="AH86" s="17"/>
       <c r="AI86" s="8"/>
     </row>
-    <row r="87" spans="1:35" s="11" customFormat="1" ht="30" hidden="1" customHeight="1">
+    <row r="87" spans="1:35" s="11" customFormat="1" ht="30" customHeight="1">
       <c r="A87" s="46">
         <v>2025</v>
       </c>
@@ -13524,7 +13518,7 @@
       <c r="AH87" s="17"/>
       <c r="AI87" s="8"/>
     </row>
-    <row r="88" spans="1:35" s="11" customFormat="1" ht="30" hidden="1" customHeight="1">
+    <row r="88" spans="1:35" s="11" customFormat="1" ht="30" customHeight="1">
       <c r="A88" s="46">
         <v>2025</v>
       </c>
@@ -13618,7 +13612,7 @@
       <c r="AH88" s="17"/>
       <c r="AI88" s="8"/>
     </row>
-    <row r="89" spans="1:35" s="11" customFormat="1" ht="30" hidden="1" customHeight="1">
+    <row r="89" spans="1:35" s="11" customFormat="1" ht="30" customHeight="1">
       <c r="A89" s="46">
         <v>2025</v>
       </c>
@@ -13712,7 +13706,7 @@
       <c r="AH89" s="17"/>
       <c r="AI89" s="8"/>
     </row>
-    <row r="90" spans="1:35" s="11" customFormat="1" ht="30" hidden="1" customHeight="1">
+    <row r="90" spans="1:35" s="11" customFormat="1" ht="30" customHeight="1">
       <c r="A90" s="46">
         <v>2025</v>
       </c>
@@ -13806,7 +13800,7 @@
       <c r="AH90" s="17"/>
       <c r="AI90" s="8"/>
     </row>
-    <row r="91" spans="1:35" s="11" customFormat="1" ht="30" hidden="1" customHeight="1">
+    <row r="91" spans="1:35" s="11" customFormat="1" ht="30" customHeight="1">
       <c r="A91" s="46">
         <v>2025</v>
       </c>
@@ -13898,7 +13892,7 @@
       <c r="AH91" s="17"/>
       <c r="AI91" s="8"/>
     </row>
-    <row r="92" spans="1:35" s="11" customFormat="1" ht="30" hidden="1" customHeight="1">
+    <row r="92" spans="1:35" s="11" customFormat="1" ht="30" customHeight="1">
       <c r="A92" s="46">
         <v>2025</v>
       </c>
@@ -13959,7 +13953,7 @@
       Dropdown!$A$2:$A$100
    )
 )</f>
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q92" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -13990,7 +13984,7 @@
       <c r="AH92" s="17"/>
       <c r="AI92" s="8"/>
     </row>
-    <row r="93" spans="1:35" s="11" customFormat="1" ht="30" hidden="1" customHeight="1">
+    <row r="93" spans="1:35" s="11" customFormat="1" ht="30" customHeight="1">
       <c r="A93" s="46">
         <v>2025</v>
       </c>
@@ -14078,7 +14072,7 @@
       <c r="AH93" s="17"/>
       <c r="AI93" s="8"/>
     </row>
-    <row r="94" spans="1:35" s="11" customFormat="1" ht="30" hidden="1" customHeight="1">
+    <row r="94" spans="1:35" s="11" customFormat="1" ht="30" customHeight="1">
       <c r="A94" s="46">
         <v>2025</v>
       </c>
@@ -14172,7 +14166,7 @@
       <c r="AH94" s="17"/>
       <c r="AI94" s="8"/>
     </row>
-    <row r="95" spans="1:35" s="11" customFormat="1" ht="30" hidden="1" customHeight="1">
+    <row r="95" spans="1:35" s="11" customFormat="1" ht="30" customHeight="1">
       <c r="A95" s="46">
         <v>2025</v>
       </c>
@@ -14266,7 +14260,7 @@
       <c r="AH95" s="17"/>
       <c r="AI95" s="8"/>
     </row>
-    <row r="96" spans="1:35" s="11" customFormat="1" ht="30" hidden="1" customHeight="1">
+    <row r="96" spans="1:35" s="11" customFormat="1" ht="30" customHeight="1">
       <c r="A96" s="46">
         <v>2025</v>
       </c>
@@ -14325,7 +14319,7 @@
       Dropdown!$A$2:$A$100
    )
 )</f>
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q96" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -14356,7 +14350,7 @@
       <c r="AH96" s="17"/>
       <c r="AI96" s="8"/>
     </row>
-    <row r="97" spans="1:35" s="11" customFormat="1" ht="30" hidden="1" customHeight="1">
+    <row r="97" spans="1:35" s="11" customFormat="1" ht="30" customHeight="1">
       <c r="A97" s="46">
         <v>2025</v>
       </c>
@@ -14417,7 +14411,7 @@
       Dropdown!$A$2:$A$100
    )
 )</f>
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q97" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -14446,7 +14440,7 @@
       <c r="AH97" s="17"/>
       <c r="AI97" s="8"/>
     </row>
-    <row r="98" spans="1:35" s="11" customFormat="1" ht="30" hidden="1" customHeight="1">
+    <row r="98" spans="1:35" s="11" customFormat="1" ht="30" customHeight="1">
       <c r="A98" s="46">
         <v>2025</v>
       </c>
@@ -15909,7 +15903,7 @@
       Dropdown!$A$2:$A$100
    )
 )</f>
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="Q112" s="59" t="str">
         <f t="shared" ca="1" si="6"/>
@@ -16710,7 +16704,7 @@
       Dropdown!$A$2:$A$100
    )
 )</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q120" s="96" t="str">
         <f ca="1">IF(P120="",                                                                                                                                                                                                   "",
@@ -16810,7 +16804,7 @@
       Dropdown!$A$2:$A$100
    )
 )</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Q121" s="96" t="str">
         <f ca="1">IF(P121="",                                                                                                                                                                                                   "",
@@ -16855,7 +16849,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="122" spans="1:35" ht="20.25" hidden="1" customHeight="1">
+    <row r="122" spans="1:35" ht="20.25" customHeight="1">
       <c r="A122" s="149"/>
       <c r="B122" s="147" t="str">
         <f>IF(M122="", "", TEXT(M122, "[$-en-US]mmmm"))</f>
